--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>279</v>
+        <v>132</v>
       </c>
       <c r="F3" t="n">
-        <v>69.75</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -522,14 +522,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>132</v>
@@ -538,7 +538,7 @@
         <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>309</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>61.8</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="F7" t="n">
-        <v>57.4</v>
+        <v>57.67</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>54.29</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>380</v>
       </c>
       <c r="F9" t="n">
-        <v>53.75</v>
+        <v>54.29</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>358</v>
+        <v>215</v>
       </c>
       <c r="F10" t="n">
-        <v>51.14</v>
+        <v>53.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,13 +707,13 @@
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>304</v>
+        <v>358</v>
       </c>
       <c r="F11" t="n">
-        <v>50.67</v>
+        <v>51.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>201</v>
+        <v>304</v>
       </c>
       <c r="F12" t="n">
-        <v>50.25</v>
+        <v>50.67</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>349</v>
+        <v>201</v>
       </c>
       <c r="F13" t="n">
-        <v>49.86</v>
+        <v>50.25</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -772,7 +772,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -782,13 +782,13 @@
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -797,20 +797,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>240</v>
+        <v>349</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>49.86</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>330</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>47.14</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>330</v>
       </c>
       <c r="F17" t="n">
-        <v>45.67</v>
+        <v>47.14</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>357</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>44.62</v>
+        <v>45.67</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="F19" t="n">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>254</v>
+        <v>400</v>
       </c>
       <c r="F20" t="n">
-        <v>42.33</v>
+        <v>44.44</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>306</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>43.71</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>242</v>
+        <v>123</v>
       </c>
       <c r="F22" t="n">
-        <v>40.33</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="F23" t="n">
-        <v>40.33</v>
+        <v>40.43</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>322</v>
+        <v>242</v>
       </c>
       <c r="F24" t="n">
-        <v>40.25</v>
+        <v>40.33</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="F25" t="n">
-        <v>39.67</v>
+        <v>40.33</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>322</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>40.25</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>312</v>
+        <v>238</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>39.67</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>270</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>38.57</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>38.57</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="F31" t="n">
-        <v>34.83</v>
+        <v>36.4</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>33.67</v>
+        <v>35</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>201</v>
+        <v>70</v>
       </c>
       <c r="F33" t="n">
-        <v>33.5</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="F34" t="n">
-        <v>33.14</v>
+        <v>34.83</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="F35" t="n">
-        <v>31.4</v>
+        <v>33.67</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="F36" t="n">
-        <v>31.2</v>
+        <v>33.5</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="F37" t="n">
-        <v>30.17</v>
+        <v>31.4</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="F39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="F40" t="n">
-        <v>29.86</v>
+        <v>30.17</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1457,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F42" t="n">
-        <v>28.67</v>
+        <v>30</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="F43" t="n">
-        <v>28.17</v>
+        <v>29.86</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>196</v>
+        <v>29</v>
       </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="F45" t="n">
-        <v>27.4</v>
+        <v>28.67</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
         <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="F46" t="n">
-        <v>27.2</v>
+        <v>28.17</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,10 +1607,10 @@
         <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -1622,20 +1622,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="F48" t="n">
-        <v>26.5</v>
+        <v>27.4</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="F51" t="n">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="F52" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="F53" t="n">
-        <v>25.43</v>
+        <v>25.75</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="F54" t="n">
-        <v>25</v>
+        <v>25.67</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="F55" t="n">
-        <v>24.5</v>
+        <v>25.43</v>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="F56" t="n">
-        <v>24.12</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>7</v>
       </c>
       <c r="D57" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>49</v>
+      </c>
+      <c r="F57" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G57" t="n">
         <v>4</v>
-      </c>
-      <c r="E57" t="n">
-        <v>48</v>
-      </c>
-      <c r="F57" t="n">
-        <v>24</v>
-      </c>
-      <c r="G57" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,10 +1882,10 @@
         <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F58" t="n">
-        <v>23.25</v>
+        <v>24.12</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1907,13 +1907,13 @@
         <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="F59" t="n">
-        <v>23.14</v>
+        <v>23.25</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="F60" t="n">
-        <v>23</v>
+        <v>23.14</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>161</v>
+        <v>23</v>
       </c>
       <c r="F61" t="n">
         <v>23</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
         <v>7</v>
       </c>
       <c r="E62" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F62" t="n">
-        <v>22.43</v>
+        <v>23</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F63" t="n">
-        <v>21.5</v>
+        <v>22.43</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="F64" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="F65" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="F67" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="F80" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E81" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F81" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2472,14 +2472,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
         <v>72</v>
@@ -2488,7 +2488,7 @@
         <v>14.4</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F83" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F84" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
         <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F86" t="n">
         <v>13</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F87" t="n">
-        <v>12.57</v>
+        <v>13</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
         <v>4</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3497,11 +3497,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D123" t="n">
         <v>2</v>
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F124" t="n">
         <v>2</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3547,20 +3547,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
         <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D126" t="n">
         <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3597,14 +3597,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
         <v>1</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3672,23 +3672,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -3697,11 +3697,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -3713,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3722,14 +3722,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D134" t="n">
         <v>0</v>
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3947,11 +3947,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4172,14 +4172,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4447,11 +4447,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
@@ -4472,14 +4472,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -4522,11 +4522,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>5</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4647,11 +4647,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4672,22 +4672,122 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>7</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>6</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>7</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C170" t="n">
-        <v>7</v>
-      </c>
-      <c r="D170" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" t="n">
+      <c r="C174" t="n">
+        <v>8</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4773,17 +4873,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
@@ -4798,7 +4898,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4808,7 +4908,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F4" t="n">
         <v>14</v>
@@ -4823,7 +4923,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4833,10 +4933,10 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5048,17 +5148,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
@@ -5073,20 +5173,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5098,17 +5198,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="F16" t="n">
         <v>8</v>
@@ -5123,17 +5223,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
@@ -5148,17 +5248,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -5173,17 +5273,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>174</v>
+        <v>101</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
@@ -5198,7 +5298,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5208,7 +5308,7 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
@@ -5223,20 +5323,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="F21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -5248,17 +5348,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F22" t="n">
         <v>7</v>
@@ -5273,7 +5373,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5283,7 +5383,7 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
@@ -5298,17 +5398,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
@@ -5323,17 +5423,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="F25" t="n">
         <v>7</v>
@@ -5398,17 +5498,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
@@ -5423,17 +5523,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -5448,7 +5548,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5458,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -5473,20 +5573,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -5498,17 +5598,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="F32" t="n">
         <v>6</v>
@@ -5523,17 +5623,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
         <v>6</v>
@@ -5548,17 +5648,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="F34" t="n">
         <v>6</v>
@@ -5573,17 +5673,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F35" t="n">
         <v>6</v>
@@ -5598,17 +5698,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="F36" t="n">
         <v>6</v>
@@ -5623,17 +5723,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F37" t="n">
         <v>6</v>
@@ -5648,17 +5748,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F38" t="n">
         <v>6</v>
@@ -5673,7 +5773,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5698,17 +5798,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -5723,20 +5823,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
         <v>84</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -5748,17 +5848,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
@@ -5798,17 +5898,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
         <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -5823,17 +5923,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -5848,17 +5948,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F46" t="n">
         <v>5</v>
@@ -5873,17 +5973,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -5898,17 +5998,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
         <v>5</v>
@@ -5923,7 +6023,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5933,7 +6033,7 @@
         <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -5948,20 +6048,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -5973,17 +6073,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="F51" t="n">
         <v>4</v>
@@ -6098,7 +6198,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6108,7 +6208,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -6123,17 +6223,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -6148,17 +6248,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -6173,17 +6273,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -6198,17 +6298,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -6223,17 +6323,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -6248,17 +6348,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6273,20 +6373,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
         <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -6298,17 +6398,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -6323,17 +6423,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
@@ -6348,17 +6448,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
@@ -6373,14 +6473,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
         <v>24</v>
@@ -6398,17 +6498,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -6423,17 +6523,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
         <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -6448,17 +6548,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -6473,17 +6573,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -6498,20 +6598,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6777,7 +6877,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F6" t="n">
-        <v>58.5</v>
+        <v>59.14</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F7" t="n">
-        <v>57.67</v>
+        <v>58.5</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>346</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>57.67</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>54.29</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -697,20 +697,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>358</v>
+        <v>425</v>
       </c>
       <c r="F11" t="n">
-        <v>51.14</v>
+        <v>53.12</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="F12" t="n">
-        <v>50.67</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="F13" t="n">
-        <v>50.25</v>
+        <v>51.14</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,20 +772,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>50.67</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>349</v>
+        <v>201</v>
       </c>
       <c r="F15" t="n">
-        <v>49.86</v>
+        <v>50.25</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -822,7 +822,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -832,13 +832,13 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>330</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>47.14</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>330</v>
       </c>
       <c r="F18" t="n">
-        <v>45.67</v>
+        <v>47.14</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>270</v>
+        <v>46</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>400</v>
+        <v>137</v>
       </c>
       <c r="F20" t="n">
-        <v>44.44</v>
+        <v>45.67</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="F21" t="n">
-        <v>43.71</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>123</v>
+        <v>400</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>44.44</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="F23" t="n">
-        <v>40.43</v>
+        <v>43.71</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1032,13 +1032,13 @@
         <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>242</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
-        <v>40.33</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>121</v>
+        <v>283</v>
       </c>
       <c r="F25" t="n">
-        <v>40.33</v>
+        <v>40.43</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>322</v>
+        <v>242</v>
       </c>
       <c r="F26" t="n">
-        <v>40.25</v>
+        <v>40.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>238</v>
+        <v>121</v>
       </c>
       <c r="F27" t="n">
-        <v>39.67</v>
+        <v>40.33</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>322</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>40.25</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>312</v>
+        <v>238</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>39.67</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>270</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n">
-        <v>38.57</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>182</v>
+        <v>270</v>
       </c>
       <c r="F31" t="n">
-        <v>36.4</v>
+        <v>38.57</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="F32" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F33" t="n">
         <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="F34" t="n">
-        <v>34.83</v>
+        <v>35</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F35" t="n">
-        <v>33.67</v>
+        <v>34.83</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>201</v>
+        <v>312</v>
       </c>
       <c r="F36" t="n">
-        <v>33.5</v>
+        <v>34.67</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="F37" t="n">
-        <v>31.4</v>
+        <v>33.67</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="F38" t="n">
-        <v>31.2</v>
+        <v>33.5</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>248</v>
+        <v>157</v>
       </c>
       <c r="F39" t="n">
-        <v>31</v>
+        <v>31.4</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F40" t="n">
-        <v>30.17</v>
+        <v>31.2</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>248</v>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F42" t="n">
         <v>30</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="F43" t="n">
-        <v>29.86</v>
+        <v>30</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1522,20 +1522,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>29</v>
+        <v>209</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>29.86</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>172</v>
+        <v>262</v>
       </c>
       <c r="F45" t="n">
-        <v>28.67</v>
+        <v>29.11</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="F46" t="n">
-        <v>28.17</v>
+        <v>29</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="F47" t="n">
-        <v>28</v>
+        <v>28.17</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="F48" t="n">
-        <v>27.4</v>
+        <v>28</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="F49" t="n">
-        <v>27.2</v>
+        <v>27.57</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>189</v>
+        <v>136</v>
       </c>
       <c r="F50" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1707,13 +1707,13 @@
         <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="F51" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>188</v>
       </c>
       <c r="F52" t="n">
-        <v>26</v>
+        <v>26.86</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="F53" t="n">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="F54" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="F55" t="n">
-        <v>25.43</v>
+        <v>25.75</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F56" t="n">
-        <v>25</v>
+        <v>25.43</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>49</v>
+        <v>176</v>
       </c>
       <c r="F57" t="n">
-        <v>24.5</v>
+        <v>25.14</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,20 +1872,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="F58" t="n">
-        <v>24.12</v>
+        <v>25</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>186</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>23.25</v>
+        <v>24.5</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F60" t="n">
-        <v>23.14</v>
+        <v>24.12</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="F61" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F62" t="n">
-        <v>23</v>
+        <v>23.14</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>157</v>
+        <v>23</v>
       </c>
       <c r="F63" t="n">
-        <v>22.43</v>
+        <v>23</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F64" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="F65" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="F66" t="n">
-        <v>19.5</v>
+        <v>21.33</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="F67" t="n">
-        <v>19.4</v>
+        <v>21</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>36</v>
+        <v>162</v>
       </c>
       <c r="F68" t="n">
-        <v>18</v>
+        <v>20.25</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F69" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
         <v>36</v>
@@ -2188,7 +2188,7 @@
         <v>18</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F71" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2232,10 +2232,10 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F72" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2282,10 +2282,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F74" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F75" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="F76" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F77" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F78" t="n">
-        <v>15.75</v>
+        <v>16.2</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="F80" t="n">
-        <v>14.62</v>
+        <v>15</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="F81" t="n">
-        <v>14.6</v>
+        <v>14.62</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F82" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
         <v>72</v>
@@ -2513,7 +2513,7 @@
         <v>14.4</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F84" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F85" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F86" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
         <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F87" t="n">
         <v>13</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,14 +2647,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
         <v>12</v>
@@ -2663,7 +2663,7 @@
         <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F91" t="n">
-        <v>11.67</v>
+        <v>12</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F92" t="n">
-        <v>11.6</v>
+        <v>11.67</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F93" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,11 +2772,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="F96" t="n">
         <v>10.33</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="F97" t="n">
-        <v>10.25</v>
+        <v>10.33</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>8</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F100" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F101" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,14 +2972,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
         <v>7</v>
@@ -2988,7 +2988,7 @@
         <v>7</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F103" t="n">
         <v>7</v>
@@ -3022,17 +3022,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F104" t="n">
         <v>7</v>
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F105" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
         <v>13</v>
@@ -3088,7 +3088,7 @@
         <v>6.5</v>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E107" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F107" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F108" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E109" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F109" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,14 +3172,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
         <v>6</v>
@@ -3188,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3197,11 +3197,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F112" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F113" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F115" t="n">
         <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" t="n">
         <v>3</v>
       </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
       <c r="E116" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3347,11 +3347,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
@@ -3363,7 +3363,7 @@
         <v>4</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3372,11 +3372,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
@@ -3388,7 +3388,7 @@
         <v>4</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,20 +3397,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C121" t="n">
+        <v>8</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="n">
         <v>9</v>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="n">
-        <v>3</v>
       </c>
       <c r="F121" t="n">
         <v>3</v>
@@ -3472,11 +3472,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3522,11 +3522,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
         <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F125" t="n">
         <v>2</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -3572,20 +3572,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
         <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -3672,23 +3672,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
@@ -3738,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C133" t="n">
         <v>8</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3772,20 +3772,20 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D140" t="n">
         <v>0</v>
@@ -3947,11 +3947,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -3988,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -4072,11 +4072,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4172,11 +4172,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,11 +4247,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -4422,11 +4422,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -4522,11 +4522,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4772,22 +4772,72 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>7</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C174" t="n">
-        <v>8</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="n">
+      <c r="C176" t="n">
+        <v>8</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4848,20 +4898,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>186</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4873,17 +4923,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F3" t="n">
         <v>14</v>
@@ -4898,17 +4948,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="F4" t="n">
         <v>14</v>
@@ -4923,7 +4973,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4933,7 +4983,7 @@
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
@@ -5048,23 +5098,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5073,23 +5123,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5098,14 +5148,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>162</v>
@@ -5123,17 +5173,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
@@ -5148,17 +5198,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>177</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
@@ -5173,17 +5223,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
@@ -5198,20 +5248,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5223,17 +5273,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
@@ -5248,17 +5298,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -5273,17 +5323,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
@@ -5298,17 +5348,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
@@ -5323,17 +5373,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
@@ -5348,20 +5398,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="F22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -5373,20 +5423,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -5398,17 +5448,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
@@ -5423,17 +5473,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="F25" t="n">
         <v>7</v>
@@ -5448,7 +5498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5458,7 +5508,7 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
@@ -5473,17 +5523,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
@@ -5498,17 +5548,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
@@ -5523,17 +5573,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -5548,17 +5598,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -5573,7 +5623,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5583,7 +5633,7 @@
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -5598,20 +5648,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -5623,17 +5673,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="F33" t="n">
         <v>6</v>
@@ -5723,17 +5773,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F37" t="n">
         <v>6</v>
@@ -5748,17 +5798,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
         <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F38" t="n">
         <v>6</v>
@@ -5773,17 +5823,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F39" t="n">
         <v>6</v>
@@ -5798,17 +5848,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -5823,17 +5873,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F41" t="n">
         <v>6</v>
@@ -5848,20 +5898,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
         <v>84</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -5873,17 +5923,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
@@ -5898,17 +5948,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -5923,17 +5973,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
         <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -5948,17 +5998,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F46" t="n">
         <v>5</v>
@@ -5973,17 +6023,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -6173,20 +6223,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -6198,17 +6248,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
         <v>3</v>
@@ -6223,7 +6273,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -6233,7 +6283,7 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
@@ -6248,17 +6298,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -6273,17 +6323,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -6298,17 +6348,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -6323,17 +6373,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -6348,17 +6398,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6398,17 +6448,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>2</v>
@@ -6423,17 +6473,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="F65" t="n">
         <v>2</v>
@@ -6448,17 +6498,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>101</v>
+        <v>180</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
@@ -6548,17 +6598,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -6573,17 +6623,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -6598,17 +6648,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -6623,20 +6673,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6673,17 +6723,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -6698,17 +6748,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
@@ -6723,17 +6773,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -6748,17 +6798,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>8</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -6773,17 +6823,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="F2" t="n">
-        <v>91.5</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -497,14 +497,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>132</v>
@@ -513,7 +513,7 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F7" t="n">
-        <v>58.5</v>
+        <v>57.67</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>346</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>57.67</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>379</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>54.14</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>330</v>
+        <v>373</v>
       </c>
       <c r="F18" t="n">
-        <v>47.14</v>
+        <v>46.62</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>40.43</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="F26" t="n">
-        <v>40.33</v>
+        <v>40.43</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="F28" t="n">
-        <v>40.25</v>
+        <v>40.29</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>238</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n">
-        <v>39.67</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>309</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>38.62</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="F31" t="n">
-        <v>38.57</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>182</v>
+        <v>257</v>
       </c>
       <c r="F32" t="n">
-        <v>36.4</v>
+        <v>36.71</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>35</v>
+        <v>328</v>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>36.44</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>36.4</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>34.83</v>
+        <v>35</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>312</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
-        <v>34.67</v>
+        <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>202</v>
+        <v>70</v>
       </c>
       <c r="F37" t="n">
-        <v>33.67</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F38" t="n">
-        <v>33.5</v>
+        <v>34.83</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>157</v>
+        <v>312</v>
       </c>
       <c r="F39" t="n">
-        <v>31.4</v>
+        <v>34.67</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="F40" t="n">
-        <v>31.2</v>
+        <v>33.67</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="F41" t="n">
-        <v>31</v>
+        <v>33.5</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="F42" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="F43" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>29.86</v>
+        <v>30</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>262</v>
+        <v>150</v>
       </c>
       <c r="F45" t="n">
-        <v>29.11</v>
+        <v>30</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>29</v>
+        <v>209</v>
       </c>
       <c r="F46" t="n">
-        <v>29</v>
+        <v>29.86</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>169</v>
+        <v>262</v>
       </c>
       <c r="F47" t="n">
-        <v>28.17</v>
+        <v>29.11</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="F48" t="n">
-        <v>28</v>
+        <v>28.17</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="F49" t="n">
-        <v>27.57</v>
+        <v>28.17</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1672,20 +1672,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="F50" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" t="n">
         <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F51" t="n">
-        <v>27</v>
+        <v>27.57</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>188</v>
+        <v>136</v>
       </c>
       <c r="F52" t="n">
-        <v>26.86</v>
+        <v>27.2</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="F53" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="F54" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="F55" t="n">
-        <v>25.75</v>
+        <v>26.86</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,13 +1832,13 @@
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="F56" t="n">
-        <v>25.43</v>
+        <v>26.5</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>25.14</v>
+        <v>26</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>49</v>
+        <v>178</v>
       </c>
       <c r="F59" t="n">
-        <v>24.5</v>
+        <v>25.43</v>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F60" t="n">
-        <v>24.12</v>
+        <v>25.14</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="F61" t="n">
-        <v>23.25</v>
+        <v>25</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,13 +1982,13 @@
         <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F62" t="n">
-        <v>23.14</v>
+        <v>24.12</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="F63" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F64" t="n">
-        <v>23</v>
+        <v>23.14</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F65" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="F66" t="n">
-        <v>21.33</v>
+        <v>21.5</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2107,13 +2107,13 @@
         <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="F67" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F68" t="n">
-        <v>20.25</v>
+        <v>21</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="F69" t="n">
-        <v>19.5</v>
+        <v>20.25</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F70" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F85" t="n">
-        <v>14</v>
+        <v>13.33</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2622,17 +2622,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
         <v>13</v>
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="F92" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="F93" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2772,11 +2772,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F95" t="n">
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="F97" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="F98" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D157" t="n">
         <v>1</v>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4908,10 +4908,10 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4923,20 +4923,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>186</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4998,20 +4998,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5033,7 +5033,7 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
@@ -5098,17 +5098,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
@@ -5123,23 +5123,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5148,23 +5148,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
@@ -5198,17 +5198,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
@@ -5248,17 +5248,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
@@ -5273,20 +5273,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -5298,20 +5298,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -5323,17 +5323,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5508,7 +5508,7 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5608,7 +5608,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5658,7 +5658,7 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F32" t="n">
         <v>7</v>
@@ -5673,20 +5673,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
         <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -5698,17 +5698,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
         <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="F34" t="n">
         <v>6</v>
@@ -5923,17 +5923,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
@@ -5948,17 +5948,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -5973,17 +5973,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
         <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F46" t="n">
         <v>5</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -6058,7 +6058,7 @@
         <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F48" t="n">
         <v>5</v>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6108,7 +6108,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -6123,20 +6123,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>66</v>
+        <v>154</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -6148,20 +6148,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
         <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F53" t="n">
         <v>4</v>
@@ -6198,17 +6198,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="F54" t="n">
         <v>4</v>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
         <v>4</v>
@@ -6248,20 +6248,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -6273,20 +6273,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -6298,17 +6298,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F58" t="n">
         <v>3</v>
@@ -6323,17 +6323,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -6348,17 +6348,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -6373,17 +6373,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6423,17 +6423,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -6448,20 +6448,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -6473,20 +6473,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
@@ -6523,17 +6523,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
@@ -6548,17 +6548,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
         <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6608,7 +6608,7 @@
         <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -6673,17 +6673,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6708,10 +6708,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
         <v>3</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>61.8</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -547,20 +547,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>309</v>
+        <v>414</v>
       </c>
       <c r="F5" t="n">
-        <v>61.8</v>
+        <v>59.14</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="F6" t="n">
-        <v>59.14</v>
+        <v>57.67</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>346</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>57.67</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>379</v>
+        <v>219</v>
       </c>
       <c r="F9" t="n">
-        <v>54.14</v>
+        <v>54.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>215</v>
+        <v>379</v>
       </c>
       <c r="F10" t="n">
-        <v>53.75</v>
+        <v>54.14</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -707,10 +707,10 @@
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="F11" t="n">
-        <v>53.12</v>
+        <v>54.12</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>53.75</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -747,20 +747,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>358</v>
+        <v>425</v>
       </c>
       <c r="F13" t="n">
-        <v>51.14</v>
+        <v>53.12</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="F14" t="n">
-        <v>50.67</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>50.25</v>
+        <v>50.67</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>50.67</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="F20" t="n">
-        <v>45.67</v>
+        <v>45.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -947,20 +947,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>270</v>
+        <v>137</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>45.67</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>400</v>
+        <v>270</v>
       </c>
       <c r="F22" t="n">
-        <v>44.44</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>306</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>43.71</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>283</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>40.43</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,20 +1072,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>283</v>
+        <v>404</v>
       </c>
       <c r="F26" t="n">
-        <v>40.43</v>
+        <v>40.4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F30" t="n">
-        <v>38.62</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>38.62</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>257</v>
+        <v>76</v>
       </c>
       <c r="F32" t="n">
-        <v>36.71</v>
+        <v>38</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>328</v>
+        <v>257</v>
       </c>
       <c r="F33" t="n">
-        <v>36.44</v>
+        <v>36.71</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>182</v>
+        <v>328</v>
       </c>
       <c r="F34" t="n">
-        <v>36.4</v>
+        <v>36.44</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
         <v>7</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>156</v>
+        <v>290</v>
       </c>
       <c r="F42" t="n">
-        <v>31.2</v>
+        <v>32.22</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>248</v>
+        <v>156</v>
       </c>
       <c r="F43" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="F48" t="n">
-        <v>28.17</v>
+        <v>29</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="F49" t="n">
-        <v>28.17</v>
+        <v>28.86</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="F50" t="n">
-        <v>28</v>
+        <v>28.17</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
         <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F51" t="n">
-        <v>27.57</v>
+        <v>28</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="F52" t="n">
-        <v>27.2</v>
+        <v>27.57</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="F53" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="F54" t="n">
         <v>27</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,10 +1807,10 @@
         <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F55" t="n">
-        <v>26.86</v>
+        <v>27</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,13 +1832,13 @@
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="F56" t="n">
-        <v>26.5</v>
+        <v>26.86</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="F57" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="F58" t="n">
-        <v>25.75</v>
+        <v>26.12</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>178</v>
+        <v>26</v>
       </c>
       <c r="F59" t="n">
-        <v>25.43</v>
+        <v>26</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c r="F60" t="n">
-        <v>25.14</v>
+        <v>25.75</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F61" t="n">
-        <v>25</v>
+        <v>25.43</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,13 +1982,13 @@
         <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F62" t="n">
-        <v>24.12</v>
+        <v>25.14</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="F63" t="n">
-        <v>23.25</v>
+        <v>25</v>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,13 +2032,13 @@
         <v>8</v>
       </c>
       <c r="E64" t="n">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F64" t="n">
-        <v>23.14</v>
+        <v>24.12</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2057,13 +2057,13 @@
         <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="F65" t="n">
-        <v>23</v>
+        <v>23.25</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2082,13 +2082,13 @@
         <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F66" t="n">
-        <v>21.5</v>
+        <v>23.14</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="F67" t="n">
-        <v>21.33</v>
+        <v>23</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
         <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2157,10 +2157,10 @@
         <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F69" t="n">
-        <v>20.25</v>
+        <v>21.5</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="F70" t="n">
-        <v>18.67</v>
+        <v>21.33</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="F71" t="n">
-        <v>18</v>
+        <v>20.25</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F72" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F73" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F75" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F76" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F77" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F78" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2397,20 +2397,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F79" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="F81" t="n">
-        <v>14.62</v>
+        <v>15</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F103" t="n">
         <v>7</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -3022,17 +3022,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F104" t="n">
         <v>7</v>
@@ -3047,17 +3047,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>7</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F105" t="n">
         <v>7</v>
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>7</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F106" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
         <v>13</v>
@@ -3113,7 +3113,7 @@
         <v>6.5</v>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
         <v>6</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
         <v>4</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
         <v>1</v>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -4422,11 +4422,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -4497,14 +4497,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -4597,14 +4597,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4722,11 +4722,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4797,11 +4797,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -4822,22 +4822,47 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C176" t="n">
-        <v>8</v>
-      </c>
-      <c r="D176" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0</v>
-      </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="n">
+      <c r="C177" t="n">
+        <v>8</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4852,7 +4877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4923,17 +4948,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
@@ -4948,7 +4973,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4958,10 +4983,10 @@
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5077,13 +5102,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -5273,17 +5298,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
@@ -5298,17 +5323,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F18" t="n">
         <v>9</v>
@@ -5323,17 +5348,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="F19" t="n">
         <v>8</v>
@@ -5348,17 +5373,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
@@ -5373,17 +5398,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
@@ -5398,17 +5423,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
@@ -5423,17 +5448,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
@@ -5448,20 +5473,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5473,17 +5498,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F25" t="n">
         <v>7</v>
@@ -5498,17 +5523,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
@@ -5523,7 +5548,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5533,7 +5558,7 @@
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
@@ -5548,17 +5573,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
@@ -5573,17 +5598,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -5598,17 +5623,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -5623,7 +5648,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5633,7 +5658,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -5648,17 +5673,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
         <v>7</v>
       </c>
       <c r="E32" t="n">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="F32" t="n">
         <v>7</v>
@@ -5673,7 +5698,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -5683,7 +5708,7 @@
         <v>7</v>
       </c>
       <c r="E33" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F33" t="n">
         <v>7</v>
@@ -5698,20 +5723,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -6073,17 +6098,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -6098,17 +6123,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -6123,7 +6148,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6133,7 +6158,7 @@
         <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -6148,17 +6173,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6173,20 +6198,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -6198,17 +6223,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="F54" t="n">
         <v>4</v>
@@ -6273,17 +6298,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
@@ -6298,20 +6323,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -6323,17 +6348,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="F59" t="n">
         <v>3</v>
@@ -6348,17 +6373,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
@@ -6373,7 +6398,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -6383,7 +6408,7 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F61" t="n">
         <v>3</v>
@@ -6398,17 +6423,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6423,17 +6448,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -6448,17 +6473,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -6473,17 +6498,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -6498,20 +6523,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -6523,17 +6548,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
@@ -6548,17 +6573,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -6573,17 +6598,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -6598,17 +6623,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D70" t="n">
         <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -6623,7 +6648,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -6633,7 +6658,7 @@
         <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -6648,17 +6673,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -6673,17 +6698,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -6698,7 +6723,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6708,7 +6733,7 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -6723,20 +6748,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6748,20 +6773,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6773,17 +6798,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -6798,17 +6823,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
         <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -6823,17 +6848,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -6848,17 +6873,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -6873,7 +6898,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6883,7 +6908,7 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -6898,17 +6923,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -6923,17 +6948,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -6948,22 +6973,47 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>9</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>260</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>52</v>
+        <v>50.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>297</v>
       </c>
       <c r="F15" t="n">
-        <v>50.67</v>
+        <v>49.5</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>304</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>50.67</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>373</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>46.62</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>373</v>
+        <v>229</v>
       </c>
       <c r="F18" t="n">
-        <v>46.62</v>
+        <v>45.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45.67</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="F20" t="n">
-        <v>45.8</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>137</v>
+        <v>315</v>
       </c>
       <c r="F21" t="n">
-        <v>45.67</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>270</v>
+        <v>123</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="F23" t="n">
         <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>283</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40.43</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>283</v>
+        <v>404</v>
       </c>
       <c r="F25" t="n">
-        <v>40.43</v>
+        <v>40.4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>404</v>
+        <v>121</v>
       </c>
       <c r="F26" t="n">
-        <v>40.4</v>
+        <v>40.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>121</v>
+        <v>282</v>
       </c>
       <c r="F27" t="n">
-        <v>40.33</v>
+        <v>40.29</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>282</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>40.29</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>38.62</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>309</v>
+        <v>76</v>
       </c>
       <c r="F31" t="n">
-        <v>38.62</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>76</v>
+        <v>257</v>
       </c>
       <c r="F32" t="n">
-        <v>38</v>
+        <v>36.71</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>257</v>
+        <v>328</v>
       </c>
       <c r="F33" t="n">
-        <v>36.71</v>
+        <v>36.44</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>328</v>
+        <v>35</v>
       </c>
       <c r="F34" t="n">
-        <v>36.44</v>
+        <v>35</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,11 +1297,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="F36" t="n">
         <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
         <v>8</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,13 +1607,13 @@
         <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="F47" t="n">
-        <v>29.11</v>
+        <v>29.12</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="F48" t="n">
-        <v>29</v>
+        <v>29.11</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>28.86</v>
+        <v>29</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="F50" t="n">
-        <v>28.17</v>
+        <v>28.86</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="F51" t="n">
-        <v>28</v>
+        <v>28.17</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
         <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F52" t="n">
-        <v>27.57</v>
+        <v>28</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="F53" t="n">
-        <v>27.2</v>
+        <v>27.57</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="F54" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="F55" t="n">
         <v>27</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,10 +1832,10 @@
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F56" t="n">
-        <v>26.86</v>
+        <v>27</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="F61" t="n">
-        <v>25.43</v>
+        <v>25</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,13 +1982,13 @@
         <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="F62" t="n">
-        <v>25.14</v>
+        <v>24.12</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="F63" t="n">
-        <v>25</v>
+        <v>24.12</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>193</v>
+        <v>47</v>
       </c>
       <c r="F64" t="n">
-        <v>24.12</v>
+        <v>23.5</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="F69" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="F70" t="n">
-        <v>21.33</v>
+        <v>21.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2207,13 +2207,13 @@
         <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="F71" t="n">
-        <v>20.25</v>
+        <v>20.86</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>9</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E72" t="n">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="F72" t="n">
-        <v>18.67</v>
+        <v>20.33</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F73" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F74" t="n">
         <v>18</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F75" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2322,14 +2322,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
         <v>35</v>
@@ -2338,7 +2338,7 @@
         <v>17.5</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F78" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F79" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F80" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F81" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F82" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E83" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F83" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -2522,14 +2522,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
         <v>72</v>
@@ -2538,7 +2538,7 @@
         <v>14.4</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="F85" t="n">
-        <v>13.33</v>
+        <v>14.4</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F86" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F87" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F88" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
         <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="F89" t="n">
         <v>13</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,11 +2772,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F95" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F96" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="F97" t="n">
-        <v>10.25</v>
+        <v>10.33</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F100" t="n">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F101" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F102" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E103" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F103" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3022,20 +3022,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F104" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D105" t="n">
         <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F105" t="n">
         <v>7</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F106" t="n">
         <v>7</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F107" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D108" t="n">
         <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F108" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F109" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
         <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F111" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -3222,14 +3222,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E112" t="n">
         <v>6</v>
@@ -3238,7 +3238,7 @@
         <v>6</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F113" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>8</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,20 +3347,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,20 +3422,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F120" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3447,20 +3447,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
         <v>4</v>
       </c>
-      <c r="E121" t="n">
-        <v>9</v>
-      </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F123" t="n">
         <v>3</v>
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
         <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F126" t="n">
         <v>2</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D127" t="n">
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3622,23 +3622,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -3688,7 +3688,7 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="n">
         <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D134" t="n">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D136" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4797,11 +4797,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4847,22 +4847,72 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
+          <t>Vijaykumar Vyshak</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>7</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C177" t="n">
-        <v>8</v>
-      </c>
-      <c r="D177" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" t="n">
-        <v>0</v>
-      </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="n">
+      <c r="C179" t="n">
+        <v>8</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4877,7 +4927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4948,20 +4998,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4973,17 +5023,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F4" t="n">
         <v>15</v>
@@ -4998,20 +5048,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5098,17 +5148,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -5123,7 +5173,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5133,10 +5183,10 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5148,17 +5198,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>125</v>
+        <v>198</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -5173,23 +5223,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -5198,23 +5248,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -5223,17 +5273,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
@@ -5248,17 +5298,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="F15" t="n">
         <v>9</v>
@@ -5273,17 +5323,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
@@ -5298,7 +5348,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5308,7 +5358,7 @@
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
@@ -5323,17 +5373,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="F18" t="n">
         <v>9</v>
@@ -5348,20 +5398,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5373,17 +5423,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="F20" t="n">
         <v>8</v>
@@ -5398,17 +5448,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
@@ -5423,17 +5473,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
@@ -5448,17 +5498,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
@@ -5473,17 +5523,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
@@ -5498,20 +5548,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -5523,17 +5573,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
@@ -5548,17 +5598,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="F27" t="n">
         <v>7</v>
@@ -5573,7 +5623,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5583,7 +5633,7 @@
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F28" t="n">
         <v>7</v>
@@ -5598,17 +5648,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -5623,17 +5673,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -6327,13 +6377,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6427,13 +6477,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6448,17 +6498,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -6473,17 +6523,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -6498,17 +6548,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -6523,17 +6573,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -6548,20 +6598,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -6573,17 +6623,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n">
         <v>2</v>
@@ -6598,17 +6648,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>180</v>
+        <v>101</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
@@ -6677,13 +6727,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -6798,17 +6848,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -6823,17 +6873,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -6848,17 +6898,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -6873,17 +6923,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -6898,17 +6948,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -6923,17 +6973,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -6948,17 +6998,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -6973,17 +7023,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -6998,22 +7048,47 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>Deepak Chahar</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>39</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>Donavon Ferreira</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>9</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="C86" t="n">
+        <v>9</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
         <v>6</v>
       </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="n">
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>309</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>61.8</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>414</v>
+        <v>237</v>
       </c>
       <c r="F5" t="n">
-        <v>59.14</v>
+        <v>59.25</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>346</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>57.67</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>219</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>54.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>54.67</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>219</v>
+        <v>379</v>
       </c>
       <c r="F9" t="n">
-        <v>54.75</v>
+        <v>54.14</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,13 +682,13 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>379</v>
+        <v>433</v>
       </c>
       <c r="F10" t="n">
-        <v>54.14</v>
+        <v>54.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="F11" t="n">
-        <v>54.12</v>
+        <v>53.12</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>215</v>
+        <v>361</v>
       </c>
       <c r="F12" t="n">
-        <v>53.75</v>
+        <v>51.57</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>425</v>
+        <v>152</v>
       </c>
       <c r="F13" t="n">
-        <v>53.12</v>
+        <v>50.67</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F14" t="n">
-        <v>50.67</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>373</v>
+        <v>440</v>
       </c>
       <c r="F17" t="n">
-        <v>46.62</v>
+        <v>48.89</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="F20" t="n">
         <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>404</v>
       </c>
       <c r="F24" t="n">
-        <v>40.43</v>
+        <v>40.4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>404</v>
+        <v>121</v>
       </c>
       <c r="F25" t="n">
-        <v>40.4</v>
+        <v>40.33</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>121</v>
+        <v>282</v>
       </c>
       <c r="F26" t="n">
-        <v>40.33</v>
+        <v>40.29</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>282</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>40.29</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="F28" t="n">
         <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38.57</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>309</v>
+        <v>385</v>
       </c>
       <c r="F30" t="n">
-        <v>38.62</v>
+        <v>38.5</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>37.22</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="F33" t="n">
-        <v>36.44</v>
+        <v>35.62</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="F34" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>312</v>
+        <v>209</v>
       </c>
       <c r="F39" t="n">
-        <v>34.67</v>
+        <v>34.83</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="F41" t="n">
         <v>33.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>290</v>
+        <v>201</v>
       </c>
       <c r="F42" t="n">
-        <v>32.22</v>
+        <v>33.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>156</v>
+        <v>323</v>
       </c>
       <c r="F43" t="n">
-        <v>31.2</v>
+        <v>32.3</v>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="F44" t="n">
-        <v>30</v>
+        <v>32.22</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
         <v>8</v>
       </c>
       <c r="E45" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F45" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G45" t="n">
         <v>3</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>29.86</v>
+        <v>30</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>233</v>
+        <v>150</v>
       </c>
       <c r="F47" t="n">
-        <v>29.12</v>
+        <v>30</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1632,13 +1632,13 @@
         <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="F48" t="n">
-        <v>29.11</v>
+        <v>29.12</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1707,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="F51" t="n">
-        <v>28.17</v>
+        <v>28.43</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
         <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F52" t="n">
-        <v>28</v>
+        <v>27.57</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="F53" t="n">
-        <v>27.57</v>
+        <v>27.2</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="F54" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>27</v>
+        <v>189</v>
       </c>
       <c r="F55" t="n">
         <v>27</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1832,13 +1832,13 @@
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="F56" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,10 +1857,10 @@
         <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F57" t="n">
-        <v>26.5</v>
+        <v>26.12</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>26.12</v>
+        <v>26</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F59" t="n">
         <v>26</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="F61" t="n">
-        <v>25</v>
+        <v>25.62</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,20 +1972,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="F62" t="n">
-        <v>24.12</v>
+        <v>25</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -1997,14 +1997,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E63" t="n">
         <v>193</v>
@@ -2013,7 +2013,7 @@
         <v>24.12</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E64" t="n">
-        <v>47</v>
+        <v>193</v>
       </c>
       <c r="F64" t="n">
-        <v>23.5</v>
+        <v>24.12</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="F65" t="n">
-        <v>23.25</v>
+        <v>23.5</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="F66" t="n">
-        <v>23.14</v>
+        <v>23</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F67" t="n">
         <v>23</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="F69" t="n">
-        <v>22.4</v>
+        <v>21.5</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2182,13 +2182,13 @@
         <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F70" t="n">
-        <v>21.5</v>
+        <v>20.86</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="F71" t="n">
-        <v>20.86</v>
+        <v>20.33</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>183</v>
+        <v>40</v>
       </c>
       <c r="F72" t="n">
-        <v>20.33</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="F73" t="n">
-        <v>18.67</v>
+        <v>19</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F74" t="n">
-        <v>18</v>
+        <v>18.67</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -2297,20 +2297,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="F75" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F76" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F78" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D80" t="n">
         <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F80" t="n">
-        <v>16.2</v>
+        <v>16.75</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>8</v>
+      </c>
+      <c r="D81" t="n">
         <v>6</v>
       </c>
-      <c r="D81" t="n">
-        <v>4</v>
-      </c>
       <c r="E81" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F81" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F82" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F85" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="F87" t="n">
-        <v>13.33</v>
+        <v>14.4</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F88" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F89" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F90" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E91" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F91" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F92" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F93" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F96" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F97" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F98" t="n">
-        <v>10.25</v>
+        <v>10.83</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F100" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E101" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="F101" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3022,20 +3022,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="F104" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3047,20 +3047,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E107" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F107" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C109" t="n">
+        <v>9</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="n">
         <v>7</v>
       </c>
-      <c r="D109" t="n">
-        <v>5</v>
-      </c>
-      <c r="E109" t="n">
-        <v>13</v>
-      </c>
       <c r="F109" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E110" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F110" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F111" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C112" t="n">
+        <v>7</v>
+      </c>
+      <c r="D112" t="n">
         <v>5</v>
       </c>
-      <c r="D112" t="n">
-        <v>3</v>
-      </c>
       <c r="E112" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F112" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3272,20 +3272,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E114" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -3297,14 +3297,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
         <v>6</v>
@@ -3313,7 +3313,7 @@
         <v>6</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F116" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3347,23 +3347,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F118" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>9</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3422,20 +3422,20 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F120" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3472,20 +3472,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F122" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3497,20 +3497,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3547,20 +3547,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
         <v>4</v>
       </c>
-      <c r="D126" t="n">
-        <v>2</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2</v>
-      </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3626,16 +3626,16 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F129" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3672,23 +3672,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -3722,23 +3722,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -3813,7 +3813,7 @@
         <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3872,23 +3872,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3897,20 +3897,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -3922,23 +3922,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3947,23 +3947,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -3972,23 +3972,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4072,11 +4072,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -4272,11 +4272,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -4347,11 +4347,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4397,14 +4397,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,14 +4497,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -4647,11 +4647,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C172" t="n">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>5</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
@@ -4847,11 +4847,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -4872,11 +4872,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -4897,22 +4897,97 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>8</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>7</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C179" t="n">
-        <v>8</v>
-      </c>
-      <c r="D179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
+      <c r="C182" t="n">
+        <v>9</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4927,7 +5002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5023,7 +5098,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5033,10 +5108,10 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5048,17 +5123,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
@@ -5073,20 +5148,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5148,17 +5223,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -5173,17 +5248,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>222</v>
       </c>
       <c r="F10" t="n">
         <v>11</v>
@@ -5198,20 +5273,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5223,20 +5298,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5248,23 +5323,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -5273,20 +5348,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5298,20 +5373,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5323,7 +5398,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5333,10 +5408,10 @@
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5348,20 +5423,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -5373,23 +5448,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="F18" t="n">
         <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -5398,17 +5473,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F19" t="n">
         <v>9</v>
@@ -5423,7 +5498,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5433,10 +5508,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -5448,20 +5523,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -5473,20 +5548,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -5498,20 +5573,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -5523,17 +5598,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
@@ -5548,17 +5623,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
@@ -5573,7 +5648,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5583,10 +5658,10 @@
         <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5598,20 +5673,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5623,20 +5698,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -5648,17 +5723,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="F29" t="n">
         <v>7</v>
@@ -5673,17 +5748,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -5698,17 +5773,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -5723,17 +5798,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="F32" t="n">
         <v>7</v>
@@ -5748,17 +5823,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F33" t="n">
         <v>7</v>
@@ -5773,17 +5848,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="F34" t="n">
         <v>7</v>
@@ -5798,20 +5873,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -5823,20 +5898,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -5848,17 +5923,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F37" t="n">
         <v>6</v>
@@ -5873,17 +5948,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="F38" t="n">
         <v>6</v>
@@ -5898,17 +5973,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="F39" t="n">
         <v>6</v>
@@ -5923,17 +5998,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -5948,17 +6023,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="F41" t="n">
         <v>6</v>
@@ -5973,17 +6048,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F42" t="n">
         <v>6</v>
@@ -5998,20 +6073,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -6023,20 +6098,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -6048,20 +6123,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>72</v>
+      </c>
+      <c r="F45" t="n">
         <v>6</v>
-      </c>
-      <c r="E45" t="n">
-        <v>91</v>
-      </c>
-      <c r="F45" t="n">
-        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -6073,20 +6148,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -6098,17 +6173,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -6123,17 +6198,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F48" t="n">
         <v>5</v>
@@ -6148,17 +6223,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -6173,17 +6248,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -6198,17 +6273,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -6223,7 +6298,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6233,7 +6308,7 @@
         <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6248,17 +6323,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
         <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6273,20 +6348,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -6298,17 +6373,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="F55" t="n">
         <v>4</v>
@@ -6323,17 +6398,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F56" t="n">
         <v>4</v>
@@ -6348,17 +6423,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
@@ -6373,17 +6448,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6398,20 +6473,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -6598,17 +6673,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -6623,20 +6698,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -6673,17 +6748,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -6698,17 +6773,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
         <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -6723,17 +6798,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -6748,17 +6823,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -6773,17 +6848,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -6798,17 +6873,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -6823,17 +6898,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -6848,20 +6923,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6873,17 +6948,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
@@ -6952,7 +7027,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
@@ -6973,17 +7048,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -6998,17 +7073,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -7023,17 +7098,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7048,17 +7123,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -7073,22 +7148,47 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>Deepak Chahar</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>39</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>Donavon Ferreira</t>
         </is>
       </c>
-      <c r="C86" t="n">
-        <v>9</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="C87" t="n">
+        <v>9</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
         <v>6</v>
       </c>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" t="n">
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F7" t="n">
-        <v>54.75</v>
+        <v>55.25</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,13 +632,13 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>328</v>
+        <v>219</v>
       </c>
       <c r="F8" t="n">
-        <v>54.67</v>
+        <v>54.75</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="F9" t="n">
-        <v>54.14</v>
+        <v>54.67</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>433</v>
+        <v>380</v>
       </c>
       <c r="F10" t="n">
-        <v>54.12</v>
+        <v>54.29</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,20 +697,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="F11" t="n">
-        <v>53.12</v>
+        <v>54.14</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>361</v>
+        <v>433</v>
       </c>
       <c r="F12" t="n">
-        <v>51.57</v>
+        <v>54.12</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="F13" t="n">
-        <v>50.67</v>
+        <v>53.12</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>361</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>51.57</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>297</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>49.5</v>
+        <v>50.67</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>440</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>48.89</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="F18" t="n">
-        <v>45.8</v>
+        <v>48.89</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="F19" t="n">
-        <v>45.67</v>
+        <v>45.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>335</v>
+        <v>75</v>
       </c>
       <c r="F31" t="n">
-        <v>37.22</v>
+        <v>37.5</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="F32" t="n">
-        <v>36.71</v>
+        <v>37.22</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="F33" t="n">
-        <v>35.62</v>
+        <v>36.71</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="F34" t="n">
-        <v>35.4</v>
+        <v>35.62</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="F35" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
         <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>70</v>
+        <v>245</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="F38" t="n">
-        <v>34.83</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1397,14 +1397,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
         <v>209</v>
@@ -1413,7 +1413,7 @@
         <v>34.83</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F40" t="n">
-        <v>33.67</v>
+        <v>34.83</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="F41" t="n">
-        <v>33.5</v>
+        <v>33.67</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="F42" t="n">
         <v>33.5</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>323</v>
+        <v>201</v>
       </c>
       <c r="F43" t="n">
-        <v>32.3</v>
+        <v>33.5</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>290</v>
+        <v>323</v>
       </c>
       <c r="F44" t="n">
-        <v>32.22</v>
+        <v>32.3</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>156</v>
+        <v>290</v>
       </c>
       <c r="F45" t="n">
-        <v>31.2</v>
+        <v>32.22</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>256</v>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
         <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F47" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G47" t="n">
         <v>3</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>233</v>
+        <v>30</v>
       </c>
       <c r="F48" t="n">
-        <v>29.12</v>
+        <v>30</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F49" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="F50" t="n">
-        <v>28.86</v>
+        <v>29</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F51" t="n">
-        <v>28.43</v>
+        <v>28.86</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>193</v>
+        <v>57</v>
       </c>
       <c r="F52" t="n">
-        <v>27.57</v>
+        <v>28.5</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>136</v>
+        <v>256</v>
       </c>
       <c r="F53" t="n">
-        <v>27.2</v>
+        <v>28.44</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>27</v>
+        <v>199</v>
       </c>
       <c r="F54" t="n">
-        <v>27</v>
+        <v>28.43</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="F55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="F56" t="n">
-        <v>26.5</v>
+        <v>27.57</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>209</v>
+        <v>136</v>
       </c>
       <c r="F57" t="n">
-        <v>26.12</v>
+        <v>27.2</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
         <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="F59" t="n">
-        <v>26</v>
+        <v>26.12</v>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="F60" t="n">
-        <v>25.75</v>
+        <v>26</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E61" t="n">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="F61" t="n">
-        <v>25.62</v>
+        <v>26</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="F62" t="n">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F63" t="n">
-        <v>24.12</v>
+        <v>25.62</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,10 +2032,10 @@
         <v>9</v>
       </c>
       <c r="E64" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="F64" t="n">
-        <v>24.12</v>
+        <v>25.5</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F65" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="F68" t="n">
-        <v>22.4</v>
+        <v>22.67</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="F69" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2182,13 +2182,13 @@
         <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="F70" t="n">
-        <v>20.86</v>
+        <v>21.5</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E71" t="n">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F71" t="n">
-        <v>20.33</v>
+        <v>20.86</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E73" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="F73" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>9</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="F74" t="n">
-        <v>18.67</v>
+        <v>19</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="F75" t="n">
-        <v>18.33</v>
+        <v>18.67</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="F76" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F77" t="n">
         <v>18</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E82" t="n">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="F82" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F84" t="n">
         <v>15</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2563,7 +2563,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2597,14 +2597,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
         <v>72</v>
@@ -2613,7 +2613,7 @@
         <v>14.4</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F88" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F89" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
         <v>4</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>13.17</v>
+        <v>13.33</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E92" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="F92" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
@@ -2747,14 +2747,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
         <v>39</v>
@@ -2763,7 +2763,7 @@
         <v>13</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F94" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F96" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F98" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F99" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F100" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F101" t="n">
-        <v>10.25</v>
+        <v>10.83</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>3</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E103" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="F104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -3057,13 +3057,13 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E106" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F106" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
         <v>8</v>
       </c>
-      <c r="D107" t="n">
-        <v>6</v>
-      </c>
-      <c r="E107" t="n">
-        <v>31</v>
-      </c>
       <c r="F107" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
         <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F108" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F110" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C111" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="n">
         <v>7</v>
-      </c>
-      <c r="D111" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" t="n">
-        <v>14</v>
       </c>
       <c r="F111" t="n">
         <v>7</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
         <v>5</v>
       </c>
       <c r="E112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F112" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G112" t="n">
         <v>3</v>
@@ -3247,20 +3247,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F113" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E114" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F114" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
         <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E116" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
         <v>6</v>
@@ -3363,7 +3363,7 @@
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>6</v>
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F119" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F120" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3447,20 +3447,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3472,20 +3472,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E122" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F122" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F123" t="n">
         <v>5</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3522,20 +3522,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3547,20 +3547,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -3572,11 +3572,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F127" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3622,20 +3622,20 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
         <v>4</v>
       </c>
-      <c r="D128" t="n">
-        <v>3</v>
-      </c>
-      <c r="E128" t="n">
-        <v>10</v>
-      </c>
       <c r="F128" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3672,23 +3672,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C130" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" t="n">
         <v>10</v>
       </c>
-      <c r="D130" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" t="n">
-        <v>3</v>
-      </c>
       <c r="F130" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C131" t="n">
+        <v>9</v>
+      </c>
+      <c r="D131" t="n">
         <v>4</v>
       </c>
-      <c r="D131" t="n">
-        <v>2</v>
-      </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3722,23 +3722,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
@@ -3763,7 +3763,7 @@
         <v>2</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D134" t="n">
         <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D136" t="n">
         <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -3888,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -3897,23 +3897,23 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -3947,23 +3947,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
         <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -3972,11 +3972,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -3997,23 +3997,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4022,23 +4022,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -4072,11 +4072,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -4172,11 +4172,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -4272,11 +4272,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -4297,11 +4297,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -4322,11 +4322,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,11 +4422,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -4647,11 +4647,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4847,14 +4847,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4897,14 +4897,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4947,11 +4947,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -4972,22 +4972,97 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
+          <t>Suyash Sharma</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>8</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>7</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C182" t="n">
-        <v>9</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" t="n">
+      <c r="C185" t="n">
+        <v>9</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5002,7 +5077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5177,13 +5252,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
@@ -5198,17 +5273,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
@@ -5223,20 +5298,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5248,7 +5323,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5273,17 +5348,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="F11" t="n">
         <v>11</v>
@@ -5298,17 +5373,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -5348,23 +5423,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5373,17 +5448,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
@@ -5398,17 +5473,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -5423,17 +5498,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -5448,23 +5523,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5623,17 +5698,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
@@ -5648,17 +5723,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
@@ -5673,17 +5748,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
@@ -5698,17 +5773,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
@@ -5723,7 +5798,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5733,10 +5808,10 @@
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -5748,17 +5823,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="F30" t="n">
         <v>7</v>
@@ -5773,17 +5848,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -6048,17 +6123,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F42" t="n">
         <v>6</v>
@@ -6073,17 +6148,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
         <v>6</v>
@@ -6098,14 +6173,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
         <v>126</v>
@@ -6123,17 +6198,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
@@ -6148,17 +6223,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F46" t="n">
         <v>6</v>
@@ -6173,20 +6248,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
         <v>84</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -6198,17 +6273,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F48" t="n">
         <v>5</v>
@@ -6223,17 +6298,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -6323,17 +6398,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6348,17 +6423,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
         <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -6373,20 +6448,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -6577,13 +6652,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E63" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -6673,17 +6748,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -6698,17 +6773,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -6723,20 +6798,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -6748,17 +6823,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F70" t="n">
         <v>2</v>
@@ -6773,17 +6848,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -6798,17 +6873,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
         <v>4</v>
       </c>
       <c r="E72" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F72" t="n">
         <v>2</v>
@@ -6823,17 +6898,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -6848,17 +6923,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -6873,17 +6948,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -6898,17 +6973,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -6923,17 +6998,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -6948,20 +7023,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6973,17 +7048,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F79" t="n">
         <v>1</v>
@@ -6998,7 +7073,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7008,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -7023,17 +7098,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
         <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -7048,17 +7123,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -7073,17 +7148,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -7098,17 +7173,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7123,17 +7198,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -7148,17 +7223,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7173,22 +7248,72 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>Deepak Chahar</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>63</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>Donavon Ferreira</t>
         </is>
       </c>
-      <c r="C87" t="n">
-        <v>9</v>
-      </c>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="C88" t="n">
+        <v>9</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
         <v>6</v>
       </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>18</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>402</v>
+      </c>
+      <c r="F6" t="n">
+        <v>57.43</v>
+      </c>
+      <c r="G6" t="n">
         <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>56</v>
-      </c>
-      <c r="F6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>221</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>55.25</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F8" t="n">
-        <v>54.75</v>
+        <v>55.25</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="F12" t="n">
-        <v>54.12</v>
+        <v>53.12</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>425</v>
+        <v>361</v>
       </c>
       <c r="F13" t="n">
-        <v>53.12</v>
+        <v>51.57</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>361</v>
+        <v>257</v>
       </c>
       <c r="F14" t="n">
-        <v>51.57</v>
+        <v>51.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>445</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>49.44</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>440</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>48.89</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>229</v>
+        <v>440</v>
       </c>
       <c r="F19" t="n">
-        <v>45.8</v>
+        <v>48.89</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,20 +922,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>315</v>
+        <v>229</v>
       </c>
       <c r="F20" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
         <v>8</v>
       </c>
-      <c r="D22" t="n">
-        <v>7</v>
-      </c>
       <c r="E22" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
         <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>404</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>121</v>
+        <v>404</v>
       </c>
       <c r="F25" t="n">
-        <v>40.33</v>
+        <v>40.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>282</v>
+        <v>121</v>
       </c>
       <c r="F26" t="n">
-        <v>40.29</v>
+        <v>40.33</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>40.29</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>312</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
         <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="F29" t="n">
-        <v>38.57</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>385</v>
+        <v>270</v>
       </c>
       <c r="F30" t="n">
-        <v>38.5</v>
+        <v>38.57</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="F31" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>335</v>
+        <v>75</v>
       </c>
       <c r="F32" t="n">
-        <v>37.22</v>
+        <v>37.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>257</v>
+        <v>335</v>
       </c>
       <c r="F33" t="n">
-        <v>36.71</v>
+        <v>37.22</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
         <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="F34" t="n">
-        <v>35.62</v>
+        <v>36.71</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>354</v>
+        <v>285</v>
       </c>
       <c r="F35" t="n">
-        <v>35.4</v>
+        <v>35.62</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
+        <v>354</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>35.4</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1397,14 +1397,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
         <v>209</v>
@@ -1413,7 +1413,7 @@
         <v>34.83</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F40" t="n">
-        <v>34.83</v>
+        <v>33.67</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>202</v>
+        <v>268</v>
       </c>
       <c r="F41" t="n">
-        <v>33.67</v>
+        <v>33.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>268</v>
+        <v>201</v>
       </c>
       <c r="F42" t="n">
         <v>33.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>201</v>
+        <v>323</v>
       </c>
       <c r="F43" t="n">
-        <v>33.5</v>
+        <v>32.3</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="F44" t="n">
-        <v>32.3</v>
+        <v>32.22</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,13 +1557,13 @@
         <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F45" t="n">
-        <v>32.22</v>
+        <v>32</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1582,10 +1582,10 @@
         <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F46" t="n">
-        <v>32</v>
+        <v>31.38</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F49" t="n">
         <v>30</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>150</v>
+      </c>
+      <c r="F50" t="n">
+        <v>30</v>
+      </c>
+      <c r="G50" t="n">
         <v>3</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" t="n">
-        <v>58</v>
-      </c>
-      <c r="F50" t="n">
-        <v>29</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>202</v>
+        <v>57</v>
       </c>
       <c r="F51" t="n">
-        <v>28.86</v>
+        <v>28.5</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="F52" t="n">
-        <v>28.5</v>
+        <v>28.44</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1757,13 +1757,13 @@
         <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="F53" t="n">
-        <v>28.44</v>
+        <v>28.43</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1782,13 +1782,13 @@
         <v>9</v>
       </c>
       <c r="E54" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="F54" t="n">
-        <v>28.43</v>
+        <v>28</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="F55" t="n">
-        <v>28</v>
+        <v>27.57</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E56" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="F56" t="n">
-        <v>27.57</v>
+        <v>27.2</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="F57" t="n">
-        <v>27.2</v>
+        <v>27.12</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="F59" t="n">
-        <v>26.12</v>
+        <v>26</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F60" t="n">
         <v>26</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="F61" t="n">
-        <v>26</v>
+        <v>25.75</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="F62" t="n">
-        <v>25.75</v>
+        <v>25.62</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,10 +2007,10 @@
         <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F63" t="n">
-        <v>25.62</v>
+        <v>25.5</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2032,13 +2032,13 @@
         <v>9</v>
       </c>
       <c r="E64" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="F64" t="n">
-        <v>25.5</v>
+        <v>25.33</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>207</v>
+        <v>72</v>
       </c>
       <c r="F66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="F67" t="n">
         <v>23</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="F68" t="n">
-        <v>22.67</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,20 +2147,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="F69" t="n">
-        <v>22.4</v>
+        <v>22.67</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
         <v>4</v>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F87" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2622,14 +2622,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
         <v>72</v>
@@ -2638,7 +2638,7 @@
         <v>14.4</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F89" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
         <v>8</v>
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F109" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F110" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
         <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C112" t="n">
         <v>10</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F112" t="n">
         <v>7</v>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E113" t="n">
         <v>14</v>
@@ -3263,7 +3263,7 @@
         <v>7</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>7</v>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F114" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C115" t="n">
+        <v>7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>5</v>
+      </c>
+      <c r="E115" t="n">
+        <v>13</v>
+      </c>
+      <c r="F115" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G115" t="n">
         <v>3</v>
-      </c>
-      <c r="D115" t="n">
-        <v>3</v>
-      </c>
-      <c r="E115" t="n">
-        <v>19</v>
-      </c>
-      <c r="F115" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F116" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E121" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F121" t="n">
         <v>5.5</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F122" t="n">
         <v>5.5</v>
@@ -3497,20 +3497,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F123" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D125" t="n">
         <v>3</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D131" t="n">
         <v>4</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D133" t="n">
         <v>2</v>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D136" t="n">
         <v>2</v>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4526,10 +4526,10 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
@@ -5373,17 +5373,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5408,7 +5408,7 @@
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
@@ -5423,23 +5423,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5448,20 +5448,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5473,23 +5473,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -5498,17 +5498,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -5548,20 +5548,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5573,17 +5573,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F20" t="n">
         <v>9</v>
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="F21" t="n">
         <v>9</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F22" t="n">
         <v>9</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>195</v>
+        <v>132</v>
       </c>
       <c r="F23" t="n">
         <v>9</v>
@@ -5673,20 +5673,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5698,17 +5698,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="F25" t="n">
         <v>8</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
@@ -5748,17 +5748,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5833,10 +5833,10 @@
         <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5848,17 +5848,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="F32" t="n">
         <v>7</v>
@@ -5898,17 +5898,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F33" t="n">
         <v>7</v>
@@ -5923,17 +5923,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="F34" t="n">
         <v>7</v>
@@ -5948,17 +5948,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="F35" t="n">
         <v>7</v>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -5983,7 +5983,7 @@
         <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F36" t="n">
         <v>7</v>
@@ -5998,20 +5998,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -6323,17 +6323,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -6348,17 +6348,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -6373,17 +6373,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6473,17 +6473,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="F56" t="n">
         <v>4</v>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
@@ -6523,17 +6523,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6548,17 +6548,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -6573,20 +6573,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -6598,20 +6598,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E61" t="n">
-        <v>48</v>
+        <v>124</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -6673,17 +6673,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E65" t="n">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>59.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>237</v>
+        <v>402</v>
       </c>
       <c r="F5" t="n">
-        <v>59.25</v>
+        <v>57.43</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>402</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>57.43</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>55.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>221</v>
+        <v>494</v>
       </c>
       <c r="F8" t="n">
-        <v>55.25</v>
+        <v>54.89</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>328</v>
+        <v>380</v>
       </c>
       <c r="F9" t="n">
-        <v>54.67</v>
+        <v>54.29</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F10" t="n">
-        <v>54.29</v>
+        <v>54.14</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +697,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F11" t="n">
-        <v>54.14</v>
+        <v>53.86</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>425</v>
+        <v>257</v>
       </c>
       <c r="F12" t="n">
-        <v>53.12</v>
+        <v>51.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>361</v>
+        <v>152</v>
       </c>
       <c r="F13" t="n">
-        <v>51.57</v>
+        <v>50.67</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>257</v>
+        <v>445</v>
       </c>
       <c r="F14" t="n">
-        <v>51.4</v>
+        <v>49.44</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>50.67</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>333</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>47.57</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F17" t="n">
-        <v>49.44</v>
+        <v>47.5</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>229</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>45.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -897,20 +897,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>440</v>
+        <v>364</v>
       </c>
       <c r="F19" t="n">
-        <v>48.89</v>
+        <v>45.5</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="F20" t="n">
-        <v>45.8</v>
+        <v>44.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>378</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>249</v>
+        <v>378</v>
       </c>
       <c r="F22" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
         <v>8</v>
       </c>
-      <c r="D23" t="n">
-        <v>7</v>
-      </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>249</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>404</v>
+        <v>41</v>
       </c>
       <c r="F25" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>121</v>
+        <v>404</v>
       </c>
       <c r="F26" t="n">
-        <v>40.33</v>
+        <v>40.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>282</v>
+        <v>121</v>
       </c>
       <c r="F27" t="n">
-        <v>40.29</v>
+        <v>40.33</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>40.29</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>312</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="F30" t="n">
-        <v>38.57</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>257</v>
+        <v>409</v>
       </c>
       <c r="F34" t="n">
-        <v>36.71</v>
+        <v>37.18</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
         <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="F35" t="n">
-        <v>35.62</v>
+        <v>36.71</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>354</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
-        <v>35.4</v>
+        <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>34.83</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>70</v>
+        <v>202</v>
       </c>
       <c r="F38" t="n">
-        <v>35</v>
+        <v>33.67</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="F39" t="n">
-        <v>34.83</v>
+        <v>33.5</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,10 +1432,10 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F40" t="n">
-        <v>33.67</v>
+        <v>33.5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>268</v>
+        <v>361</v>
       </c>
       <c r="F41" t="n">
-        <v>33.5</v>
+        <v>32.82</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>201</v>
+        <v>290</v>
       </c>
       <c r="F42" t="n">
-        <v>33.5</v>
+        <v>32.22</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>323</v>
+        <v>256</v>
       </c>
       <c r="F43" t="n">
-        <v>32.3</v>
+        <v>32</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F44" t="n">
-        <v>32.22</v>
+        <v>31.78</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="F45" t="n">
-        <v>32</v>
+        <v>31.71</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>9</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E55" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="F55" t="n">
-        <v>27.57</v>
+        <v>27.2</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="F56" t="n">
-        <v>27.2</v>
+        <v>27.12</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="F57" t="n">
-        <v>27.12</v>
+        <v>27</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F59" t="n">
         <v>26</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="F60" t="n">
-        <v>26</v>
+        <v>25.75</v>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="F61" t="n">
-        <v>25.75</v>
+        <v>25.62</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1982,10 +1982,10 @@
         <v>9</v>
       </c>
       <c r="E62" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F62" t="n">
-        <v>25.62</v>
+        <v>25.5</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2007,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="F63" t="n">
-        <v>25.5</v>
+        <v>25.33</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="F64" t="n">
-        <v>25.33</v>
+        <v>25</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F65" t="n">
-        <v>25</v>
+        <v>24.67</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
         <v>8</v>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>16.11</v>
+        <v>16.33</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="F83" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -3301,7 +3301,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" t="n">
         <v>5</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D123" t="n">
         <v>4</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D136" t="n">
         <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -3888,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
         <v>1</v>
@@ -3913,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
@@ -3947,23 +3947,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -3972,23 +3972,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3997,14 +3997,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -4013,7 +4013,7 @@
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -5077,7 +5077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5198,20 +5198,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5233,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="F6" t="n">
         <v>15</v>
@@ -5473,23 +5473,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5498,23 +5498,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -5573,11 +5573,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
@@ -5586,7 +5586,7 @@
         <v>186</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F21" t="n">
         <v>9</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="F22" t="n">
         <v>9</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F23" t="n">
         <v>9</v>
@@ -5698,20 +5698,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" t="n">
         <v>8</v>
       </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
       <c r="E25" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="F26" t="n">
         <v>8</v>
@@ -5748,17 +5748,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
@@ -5848,20 +5848,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -5873,20 +5873,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -5898,17 +5898,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="F33" t="n">
         <v>7</v>
@@ -5923,17 +5923,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="F34" t="n">
         <v>7</v>
@@ -5948,17 +5948,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F35" t="n">
         <v>7</v>
@@ -5973,17 +5973,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
         <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="F36" t="n">
         <v>7</v>
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
@@ -6023,20 +6023,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -6048,20 +6048,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="n">
+        <v>138</v>
+      </c>
+      <c r="F39" t="n">
         <v>7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>97</v>
-      </c>
-      <c r="F39" t="n">
-        <v>6</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="F41" t="n">
         <v>6</v>
@@ -6148,17 +6148,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="F43" t="n">
         <v>6</v>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
@@ -6198,14 +6198,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
         <v>126</v>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
@@ -6523,17 +6523,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6548,17 +6548,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -6598,17 +6598,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
@@ -6623,20 +6623,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E66" t="n">
-        <v>144</v>
+        <v>222</v>
       </c>
       <c r="F66" t="n">
         <v>3</v>
@@ -6748,17 +6748,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -6798,17 +6798,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -6823,20 +6823,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -6848,17 +6848,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="F71" t="n">
         <v>2</v>
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D84" t="n">
         <v>3</v>
@@ -7223,17 +7223,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7248,17 +7248,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -7273,17 +7273,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7298,22 +7298,47 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>9</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>6</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>Will Jacks</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="C90" t="n">
         <v>3</v>
       </c>
-      <c r="D89" t="n">
-        <v>2</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" t="n">
         <v>18</v>
       </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>121</v>
+        <v>363</v>
       </c>
       <c r="F27" t="n">
         <v>40.33</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>282</v>
+        <v>121</v>
       </c>
       <c r="F28" t="n">
-        <v>40.29</v>
+        <v>40.33</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>40.29</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>312</v>
+        <v>39</v>
       </c>
       <c r="F30" t="n">
         <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,13 +1207,13 @@
         <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="F31" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>75</v>
+        <v>385</v>
       </c>
       <c r="F32" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>335</v>
+        <v>75</v>
       </c>
       <c r="F33" t="n">
-        <v>37.22</v>
+        <v>37.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="F34" t="n">
-        <v>37.18</v>
+        <v>37.22</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>257</v>
+        <v>409</v>
       </c>
       <c r="F35" t="n">
-        <v>36.71</v>
+        <v>37.18</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
+        <v>257</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>36.71</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>34.83</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F38" t="n">
-        <v>33.67</v>
+        <v>34.83</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="F39" t="n">
-        <v>33.5</v>
+        <v>33.67</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="F40" t="n">
         <v>33.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>361</v>
+        <v>201</v>
       </c>
       <c r="F41" t="n">
-        <v>32.82</v>
+        <v>33.5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="F42" t="n">
-        <v>32.22</v>
+        <v>32.82</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="F43" t="n">
-        <v>32</v>
+        <v>32.22</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="F44" t="n">
-        <v>31.78</v>
+        <v>32</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
         <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="F45" t="n">
-        <v>31.71</v>
+        <v>31.78</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="F46" t="n">
-        <v>31.38</v>
+        <v>31.71</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="F47" t="n">
-        <v>31.2</v>
+        <v>31.38</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F48" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="F49" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F50" t="n">
         <v>30</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>150</v>
+      </c>
+      <c r="F51" t="n">
+        <v>30</v>
+      </c>
+      <c r="G51" t="n">
         <v>3</v>
-      </c>
-      <c r="D51" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" t="n">
-        <v>57</v>
-      </c>
-      <c r="F51" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="F52" t="n">
-        <v>28.44</v>
+        <v>28.5</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
         <v>9</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D57" t="n">
         <v>3</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D62" t="n">
         <v>9</v>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D75" t="n">
         <v>5</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="F79" t="n">
-        <v>17.5</v>
+        <v>17.67</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F80" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F82" t="n">
-        <v>16.33</v>
+        <v>16.75</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="F83" t="n">
-        <v>16.11</v>
+        <v>16.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D84" t="n">
         <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2588,7 +2588,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F87" t="n">
         <v>15</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F88" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2647,14 +2647,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
         <v>72</v>
@@ -2663,7 +2663,7 @@
         <v>14.4</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="F90" t="n">
-        <v>13.33</v>
+        <v>14.4</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -2697,11 +2697,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
         <v>4</v>
@@ -2722,23 +2722,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
-        <v>13.17</v>
+        <v>13.33</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2747,20 +2747,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="F93" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G93" t="n">
         <v>2</v>
@@ -2772,14 +2772,14 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
         <v>39</v>
@@ -2788,7 +2788,7 @@
         <v>13</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F95" t="n">
         <v>13</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,11 +2847,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2913,7 +2913,7 @@
         <v>11</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>11</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F101" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F102" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F103" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E104" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,14 +3047,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="F106" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3097,17 +3097,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="F107" t="n">
         <v>9</v>
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
         <v>8</v>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F111" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D112" t="n">
         <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C113" t="n">
         <v>10</v>
       </c>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F113" t="n">
         <v>7</v>
       </c>
       <c r="G113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3272,14 +3272,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E114" t="n">
         <v>14</v>
@@ -3288,7 +3288,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F115" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" t="n">
+        <v>13</v>
+      </c>
+      <c r="F116" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G116" t="n">
         <v>3</v>
-      </c>
-      <c r="D116" t="n">
-        <v>3</v>
-      </c>
-      <c r="E116" t="n">
-        <v>19</v>
-      </c>
-      <c r="F116" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,23 +3347,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
         <v>3</v>
       </c>
       <c r="E117" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
         <v>6</v>
@@ -3388,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -3397,11 +3397,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
         <v>1</v>
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>6</v>
@@ -3447,20 +3447,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F121" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E122" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F122" t="n">
         <v>5.5</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>9</v>
       </c>
       <c r="D123" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F123" t="n">
         <v>5.5</v>
@@ -3522,20 +3522,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F124" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F125" t="n">
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C126" t="n">
+        <v>10</v>
+      </c>
+      <c r="D126" t="n">
         <v>3</v>
       </c>
-      <c r="D126" t="n">
-        <v>1</v>
-      </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
         <v>1</v>
@@ -3613,7 +3613,7 @@
         <v>4</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>4</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -3647,20 +3647,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F129" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3672,20 +3672,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F130" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3722,17 +3722,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C132" t="n">
         <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E132" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F132" t="n">
         <v>3</v>
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D134" t="n">
         <v>2</v>
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
@@ -3813,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -3838,7 +3838,7 @@
         <v>2</v>
       </c>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D137" t="n">
         <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -3872,23 +3872,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>1</v>
@@ -3913,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
@@ -3938,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -3947,11 +3947,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -3972,23 +3972,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4047,23 +4047,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4072,11 +4072,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4247,11 +4247,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4272,11 +4272,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -4297,14 +4297,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -4447,11 +4447,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,14 +4497,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -4522,11 +4522,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4597,14 +4597,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4647,11 +4647,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4947,11 +4947,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -4972,11 +4972,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -5047,22 +5047,47 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C185" t="n">
-        <v>10</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" t="n">
+      <c r="C186" t="n">
+        <v>10</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5127,13 +5152,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
@@ -5252,7 +5277,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -5523,17 +5548,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -5548,7 +5573,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5558,7 +5583,7 @@
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -5573,17 +5598,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
@@ -5598,11 +5623,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -5611,7 +5636,7 @@
         <v>186</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -5623,17 +5648,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F22" t="n">
         <v>9</v>
@@ -5648,17 +5673,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="F23" t="n">
         <v>9</v>
@@ -5752,7 +5777,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
         <v>9</v>
@@ -5777,13 +5802,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
@@ -5977,13 +6002,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F36" t="n">
         <v>7</v>
@@ -6077,13 +6102,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F40" t="n">
         <v>6</v>
@@ -6452,13 +6477,13 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>10</v>
+      </c>
+      <c r="D55" t="n">
         <v>9</v>
       </c>
-      <c r="D55" t="n">
-        <v>8</v>
-      </c>
       <c r="E55" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6752,7 +6777,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" t="n">
         <v>6</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>192</v>
+        <v>237</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>59.25</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
       <c r="E4" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F4" t="n">
-        <v>59.25</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -672,7 +672,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -682,10 +682,10 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F10" t="n">
-        <v>54.14</v>
+        <v>53.86</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>377</v>
+        <v>152</v>
       </c>
       <c r="F11" t="n">
-        <v>53.86</v>
+        <v>50.67</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>257</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>51.4</v>
+        <v>49</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>152</v>
+        <v>333</v>
       </c>
       <c r="F13" t="n">
-        <v>50.67</v>
+        <v>47.57</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -772,20 +772,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="F14" t="n">
-        <v>49.44</v>
+        <v>47.5</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>379</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>47.38</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>333</v>
+        <v>468</v>
       </c>
       <c r="F16" t="n">
-        <v>47.57</v>
+        <v>46.8</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>475</v>
+        <v>229</v>
       </c>
       <c r="F17" t="n">
-        <v>47.5</v>
+        <v>45.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
         <v>9</v>
       </c>
-      <c r="D18" t="n">
-        <v>7</v>
-      </c>
       <c r="E18" t="n">
-        <v>229</v>
+        <v>364</v>
       </c>
       <c r="F18" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>364</v>
+        <v>178</v>
       </c>
       <c r="F19" t="n">
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>178</v>
+        <v>259</v>
       </c>
       <c r="F20" t="n">
-        <v>44.5</v>
+        <v>43.17</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>249</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
         <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>404</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>40.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>404</v>
+        <v>121</v>
       </c>
       <c r="F26" t="n">
-        <v>40.4</v>
+        <v>40.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,20 +1097,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="F27" t="n">
-        <v>40.33</v>
+        <v>39.75</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
-        <v>121</v>
+        <v>316</v>
       </c>
       <c r="F28" t="n">
-        <v>40.33</v>
+        <v>39.5</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>282</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n">
-        <v>40.29</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="F30" t="n">
         <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,13 +1207,13 @@
         <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>312</v>
+        <v>385</v>
       </c>
       <c r="F31" t="n">
-        <v>39</v>
+        <v>38.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E32" t="n">
-        <v>385</v>
+        <v>75</v>
       </c>
       <c r="F32" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>75</v>
+        <v>335</v>
       </c>
       <c r="F33" t="n">
-        <v>37.5</v>
+        <v>37.22</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>335</v>
+        <v>409</v>
       </c>
       <c r="F34" t="n">
-        <v>37.22</v>
+        <v>37.18</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>409</v>
+        <v>367</v>
       </c>
       <c r="F35" t="n">
-        <v>37.18</v>
+        <v>36.7</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F36" t="n">
-        <v>36.71</v>
+        <v>36</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>209</v>
+        <v>35</v>
       </c>
       <c r="F38" t="n">
-        <v>34.83</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F39" t="n">
-        <v>33.67</v>
+        <v>34.83</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>268</v>
+        <v>202</v>
       </c>
       <c r="F40" t="n">
-        <v>33.5</v>
+        <v>33.67</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>361</v>
+        <v>232</v>
       </c>
       <c r="F42" t="n">
-        <v>32.82</v>
+        <v>33.14</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="F43" t="n">
-        <v>32.22</v>
+        <v>32.82</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>32.22</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="F45" t="n">
-        <v>31.78</v>
+        <v>32</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
         <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="F46" t="n">
-        <v>31.71</v>
+        <v>31.78</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,20 +1597,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="F47" t="n">
-        <v>31.38</v>
+        <v>31.71</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E48" t="n">
-        <v>156</v>
+        <v>251</v>
       </c>
       <c r="F48" t="n">
-        <v>31.2</v>
+        <v>31.38</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F49" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="F50" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
         <v>30</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>9</v>
+      </c>
+      <c r="D52" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>150</v>
+      </c>
+      <c r="F52" t="n">
+        <v>30</v>
+      </c>
+      <c r="G52" t="n">
         <v>3</v>
-      </c>
-      <c r="D52" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" t="n">
-        <v>57</v>
-      </c>
-      <c r="F52" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="F53" t="n">
-        <v>28.43</v>
+        <v>29.89</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F54" t="n">
-        <v>28</v>
+        <v>29.5</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="F55" t="n">
-        <v>27.2</v>
+        <v>28.5</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F56" t="n">
-        <v>27.12</v>
+        <v>28.12</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>27</v>
+        <v>278</v>
       </c>
       <c r="F57" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="G57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>27.75</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="F59" t="n">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="G59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="F60" t="n">
-        <v>25.75</v>
+        <v>27</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="F61" t="n">
-        <v>25.62</v>
+        <v>26.33</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="F62" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E63" t="n">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="F63" t="n">
-        <v>25.33</v>
+        <v>26</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>25.75</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E65" t="n">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="F65" t="n">
-        <v>24.67</v>
+        <v>25</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="F66" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="F67" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>24.22</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2157,10 +2157,10 @@
         <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F69" t="n">
-        <v>22.67</v>
+        <v>23</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F70" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>146</v>
+        <v>68</v>
       </c>
       <c r="F71" t="n">
-        <v>20.86</v>
+        <v>22.67</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E72" t="n">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>22.67</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="F73" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
         <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="F74" t="n">
-        <v>19</v>
+        <v>20.86</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F75" t="n">
-        <v>18.67</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="F76" t="n">
-        <v>18.33</v>
+        <v>19.5</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="F77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="F78" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="F79" t="n">
-        <v>17.67</v>
+        <v>18</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F81" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F83" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F84" t="n">
-        <v>16.33</v>
+        <v>16.4</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D85" t="n">
         <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="F86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2597,11 +2597,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -2613,7 +2613,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F88" t="n">
         <v>15</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="F89" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F90" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E91" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="F91" t="n">
-        <v>13.33</v>
+        <v>14.4</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E92" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="F92" t="n">
-        <v>13.33</v>
+        <v>14.4</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>13.17</v>
+        <v>13.33</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="F94" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
@@ -2797,14 +2797,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
         <v>39</v>
@@ -2813,7 +2813,7 @@
         <v>13</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2913,7 +2913,7 @@
         <v>11</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>11</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F101" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E102" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F102" t="n">
-        <v>10.83</v>
+        <v>10.75</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3097,17 +3097,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F107" t="n">
         <v>9</v>
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F109" t="n">
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E118" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F118" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
         <v>6</v>
@@ -3413,7 +3413,7 @@
         <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>6</v>
@@ -3472,20 +3472,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F122" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D123" t="n">
         <v>2</v>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D132" t="n">
         <v>4</v>
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C137" t="n">
         <v>9</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F137" t="n">
         <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3872,23 +3872,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D138" t="n">
         <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F138" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D145" t="n">
         <v>2</v>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
@@ -5102,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5158,7 +5158,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5208,7 +5208,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F4" t="n">
         <v>16</v>
@@ -5223,17 +5223,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
@@ -5248,20 +5248,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5273,20 +5273,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -5298,20 +5298,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -5323,17 +5323,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F9" t="n">
         <v>12</v>
@@ -5348,20 +5348,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5408,7 +5408,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F12" t="n">
         <v>11</v>
@@ -5423,17 +5423,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="F14" t="n">
         <v>11</v>
@@ -5498,17 +5498,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
@@ -5523,23 +5523,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -5573,23 +5573,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
@@ -5648,20 +5648,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
         <v>186</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -5673,20 +5673,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5708,7 +5708,7 @@
         <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
@@ -5748,20 +5748,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5773,20 +5773,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>168</v>
+      </c>
+      <c r="F27" t="n">
         <v>9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>210</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
@@ -5848,11 +5848,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -5898,17 +5898,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -5933,10 +5933,10 @@
         <v>4</v>
       </c>
       <c r="E33" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -5948,17 +5948,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F34" t="n">
         <v>7</v>
@@ -5973,17 +5973,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="F35" t="n">
         <v>7</v>
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>191</v>
+        <v>132</v>
       </c>
       <c r="F36" t="n">
         <v>7</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F38" t="n">
         <v>7</v>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="F39" t="n">
         <v>7</v>
@@ -6098,20 +6098,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -6123,20 +6123,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
+        <v>198</v>
+      </c>
+      <c r="F41" t="n">
         <v>7</v>
-      </c>
-      <c r="E41" t="n">
-        <v>97</v>
-      </c>
-      <c r="F41" t="n">
-        <v>6</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -6373,17 +6373,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6673,20 +6673,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6773,17 +6773,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="F67" t="n">
         <v>3</v>
@@ -6798,17 +6798,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -6823,17 +6823,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -6923,17 +6923,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -6948,17 +6948,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -6973,17 +6973,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -7023,17 +7023,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7048,17 +7048,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -7083,10 +7083,10 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -7098,17 +7098,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
@@ -7123,17 +7123,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -7148,17 +7148,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -7173,17 +7173,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -7208,7 +7208,7 @@
         <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7223,17 +7223,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -7248,17 +7248,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7273,17 +7273,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7323,17 +7323,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7348,22 +7348,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>6</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>Will Jacks</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="C91" t="n">
         <v>3</v>
       </c>
-      <c r="D90" t="n">
-        <v>2</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
         <v>18</v>
       </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>55.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>221</v>
+        <v>494</v>
       </c>
       <c r="F7" t="n">
-        <v>55.25</v>
+        <v>54.89</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>494</v>
+        <v>380</v>
       </c>
       <c r="F8" t="n">
-        <v>54.89</v>
+        <v>54.29</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F9" t="n">
-        <v>54.29</v>
+        <v>53.86</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>377</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>53.86</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>152</v>
+        <v>333</v>
       </c>
       <c r="F11" t="n">
-        <v>50.67</v>
+        <v>47.57</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>475</v>
       </c>
       <c r="F12" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>333</v>
+        <v>190</v>
       </c>
       <c r="F13" t="n">
-        <v>47.57</v>
+        <v>47.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>475</v>
+        <v>379</v>
       </c>
       <c r="F14" t="n">
-        <v>47.5</v>
+        <v>47.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>379</v>
+        <v>468</v>
       </c>
       <c r="F15" t="n">
-        <v>47.38</v>
+        <v>46.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F16" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
         <v>9</v>
       </c>
-      <c r="D17" t="n">
-        <v>7</v>
-      </c>
       <c r="E17" t="n">
-        <v>229</v>
+        <v>364</v>
       </c>
       <c r="F17" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>364</v>
+        <v>178</v>
       </c>
       <c r="F18" t="n">
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>178</v>
+        <v>259</v>
       </c>
       <c r="F19" t="n">
-        <v>44.5</v>
+        <v>43.17</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>43.17</v>
+        <v>42.5</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F21" t="n">
-        <v>42.5</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>378</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="F23" t="n">
         <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40.33</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="F25" t="n">
-        <v>40.4</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>121</v>
+        <v>440</v>
       </c>
       <c r="F26" t="n">
-        <v>40.33</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1172,20 +1172,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>10</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>312</v>
+        <v>233</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>38.83</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>385</v>
+        <v>75</v>
       </c>
       <c r="F31" t="n">
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>75</v>
+        <v>409</v>
       </c>
       <c r="F32" t="n">
-        <v>37.5</v>
+        <v>37.18</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,13 +1257,13 @@
         <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="F33" t="n">
-        <v>37.22</v>
+        <v>36.7</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>409</v>
+        <v>252</v>
       </c>
       <c r="F34" t="n">
-        <v>37.18</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>367</v>
+        <v>71</v>
       </c>
       <c r="F35" t="n">
-        <v>36.7</v>
+        <v>35.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="F36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>35</v>
+        <v>315</v>
       </c>
       <c r="F38" t="n">
         <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>209</v>
+        <v>348</v>
       </c>
       <c r="F39" t="n">
-        <v>34.83</v>
+        <v>34.8</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="F44" t="n">
-        <v>32.22</v>
+        <v>32</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="F45" t="n">
-        <v>32</v>
+        <v>31.78</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
         <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>286</v>
+        <v>222</v>
       </c>
       <c r="F46" t="n">
-        <v>31.78</v>
+        <v>31.71</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="F47" t="n">
-        <v>31.71</v>
+        <v>31.4</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="F50" t="n">
-        <v>30.6</v>
+        <v>30.67</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>153</v>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F52" t="n">
         <v>30</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>269</v>
+        <v>150</v>
       </c>
       <c r="F53" t="n">
-        <v>29.89</v>
+        <v>30</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1782,13 +1782,13 @@
         <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>236</v>
+        <v>269</v>
       </c>
       <c r="F54" t="n">
-        <v>29.5</v>
+        <v>29.89</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="F55" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>225</v>
+        <v>57</v>
       </c>
       <c r="F56" t="n">
-        <v>28.12</v>
+        <v>28.5</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,13 +1857,13 @@
         <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="F57" t="n">
-        <v>27.8</v>
+        <v>28.12</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E58" t="n">
-        <v>111</v>
+        <v>278</v>
       </c>
       <c r="F58" t="n">
-        <v>27.75</v>
+        <v>27.8</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="F59" t="n">
-        <v>27.2</v>
+        <v>27.75</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="F60" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="F61" t="n">
-        <v>26.33</v>
+        <v>27</v>
       </c>
       <c r="G61" t="n">
         <v>3</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="F62" t="n">
-        <v>26</v>
+        <v>26.33</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F63" t="n">
         <v>26</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F66" t="n">
-        <v>25</v>
+        <v>24.67</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="F67" t="n">
-        <v>24.67</v>
+        <v>24.22</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2132,10 +2132,10 @@
         <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F68" t="n">
-        <v>24.22</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F69" t="n">
         <v>23</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="F70" t="n">
-        <v>23</v>
+        <v>22.67</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="F71" t="n">
         <v>22.67</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="F72" t="n">
-        <v>22.67</v>
+        <v>21.5</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2257,13 +2257,13 @@
         <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="F73" t="n">
-        <v>21.5</v>
+        <v>20.86</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E74" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="F74" t="n">
-        <v>20.86</v>
+        <v>19.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D75" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" t="n">
+        <v>95</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19</v>
+      </c>
+      <c r="G75" t="n">
         <v>3</v>
-      </c>
-      <c r="E75" t="n">
-        <v>40</v>
-      </c>
-      <c r="F75" t="n">
-        <v>20</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2332,10 +2332,10 @@
         <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="F76" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="F77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,20 +2372,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F80" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="F81" t="n">
-        <v>17.5</v>
+        <v>16.75</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="F82" t="n">
-        <v>17</v>
+        <v>16.4</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>16.75</v>
+        <v>16.33</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F84" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
         <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F85" t="n">
-        <v>16.33</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="F86" t="n">
-        <v>16</v>
+        <v>15.67</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="F92" t="n">
-        <v>14.4</v>
+        <v>13.33</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F93" t="n">
-        <v>13.33</v>
+        <v>13.17</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="F94" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F95" t="n">
         <v>13</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E96" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="F96" t="n">
         <v>13</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2882,10 +2882,10 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2913,7 +2913,7 @@
         <v>11</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>11</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>8</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F101" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F102" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
         <v>43</v>
@@ -3013,7 +3013,7 @@
         <v>10.75</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F104" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F105" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>10</v>
@@ -3088,7 +3088,7 @@
         <v>10</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
         <v>8</v>
-      </c>
-      <c r="E109" t="n">
-        <v>64</v>
       </c>
       <c r="F109" t="n">
         <v>8</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E110" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="F110" t="n">
         <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F111" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F112" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>10</v>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F114" t="n">
         <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E117" t="n">
         <v>19</v>
@@ -3363,7 +3363,7 @@
         <v>6.33</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D118" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E118" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F118" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E119" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F119" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,14 +3422,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E120" t="n">
         <v>6</v>
@@ -3438,7 +3438,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>6</v>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
         <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F123" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3522,17 +3522,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F124" t="n">
         <v>5.5</v>
@@ -3547,20 +3547,20 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F125" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F126" t="n">
         <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C127" t="n">
+        <v>10</v>
+      </c>
+      <c r="D127" t="n">
         <v>3</v>
       </c>
-      <c r="D127" t="n">
-        <v>1</v>
-      </c>
       <c r="E127" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F127" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
@@ -3638,7 +3638,7 @@
         <v>4</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>4</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3672,20 +3672,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F130" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3697,20 +3697,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F131" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3722,23 +3722,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -3747,17 +3747,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F133" t="n">
         <v>3</v>
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3797,11 +3797,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D135" t="n">
         <v>2</v>
@@ -3822,14 +3822,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -3838,7 +3838,7 @@
         <v>2</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F137" t="n">
         <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
@@ -3888,7 +3888,7 @@
         <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3897,20 +3897,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -3922,20 +3922,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D140" t="n">
         <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G140" t="n">
         <v>2</v>
@@ -3947,11 +3947,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
         <v>1</v>
@@ -3988,7 +3988,7 @@
         <v>1</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -4022,23 +4022,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C145" t="n">
         <v>10</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4063,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4072,23 +4072,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4172,11 +4172,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4947,14 +4947,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -4972,11 +4972,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -4997,11 +4997,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -5047,14 +5047,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -5072,22 +5072,47 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>3</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C186" t="n">
-        <v>10</v>
-      </c>
-      <c r="D186" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="n">
+      <c r="C187" t="n">
+        <v>10</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5148,20 +5173,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5173,7 +5198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5183,7 +5208,7 @@
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="F3" t="n">
         <v>17</v>
@@ -5198,7 +5223,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5208,10 +5233,10 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5223,7 +5248,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5233,7 +5258,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
@@ -5273,17 +5298,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="F7" t="n">
         <v>15</v>
@@ -5298,20 +5323,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -5323,20 +5348,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5348,17 +5373,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="F10" t="n">
         <v>12</v>
@@ -5373,20 +5398,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5398,20 +5423,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5573,7 +5598,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5583,13 +5608,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5598,23 +5623,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -5623,17 +5648,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
@@ -5648,17 +5673,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
@@ -5673,17 +5698,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
@@ -5698,20 +5723,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5723,17 +5748,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="F25" t="n">
         <v>9</v>
@@ -5748,17 +5773,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
@@ -5773,17 +5798,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F27" t="n">
         <v>9</v>
@@ -5798,20 +5823,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>195</v>
+      </c>
+      <c r="F28" t="n">
         <v>9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>178</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -5823,20 +5848,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -5848,17 +5873,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
@@ -5873,17 +5898,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -5898,17 +5923,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
         <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
@@ -5923,17 +5948,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
@@ -5948,20 +5973,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -5973,20 +5998,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="F35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -5998,20 +6023,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>96</v>
+      </c>
+      <c r="F36" t="n">
         <v>8</v>
-      </c>
-      <c r="E36" t="n">
-        <v>132</v>
-      </c>
-      <c r="F36" t="n">
-        <v>7</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -6023,17 +6048,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="F37" t="n">
         <v>7</v>
@@ -6048,17 +6073,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="F38" t="n">
         <v>7</v>
@@ -6327,7 +6352,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
         <v>3</v>
@@ -6523,17 +6548,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
@@ -6548,17 +6573,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6573,17 +6598,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -6598,17 +6623,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -6623,17 +6648,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
@@ -6698,20 +6723,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -6723,17 +6748,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -7148,17 +7173,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -7173,17 +7198,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -7198,17 +7223,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7352,13 +7377,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="F3" t="n">
-        <v>59.25</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>59.25</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>402</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>57.43</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>221</v>
+        <v>494</v>
       </c>
       <c r="F6" t="n">
-        <v>55.25</v>
+        <v>54.89</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>494</v>
+        <v>377</v>
       </c>
       <c r="F7" t="n">
-        <v>54.89</v>
+        <v>53.86</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="F8" t="n">
-        <v>54.29</v>
+        <v>53.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>377</v>
+        <v>98</v>
       </c>
       <c r="F9" t="n">
-        <v>53.86</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>243</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>333</v>
+        <v>382</v>
       </c>
       <c r="F11" t="n">
-        <v>47.57</v>
+        <v>47.75</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>475</v>
+        <v>333</v>
       </c>
       <c r="F12" t="n">
-        <v>47.5</v>
+        <v>47.57</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>190</v>
+        <v>475</v>
       </c>
       <c r="F13" t="n">
         <v>47.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>379</v>
+        <v>190</v>
       </c>
       <c r="F14" t="n">
-        <v>47.38</v>
+        <v>47.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>462</v>
+        <v>232</v>
       </c>
       <c r="F16" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>364</v>
+        <v>462</v>
       </c>
       <c r="F17" t="n">
-        <v>45.5</v>
+        <v>46.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>178</v>
+        <v>364</v>
       </c>
       <c r="F18" t="n">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>259</v>
+        <v>178</v>
       </c>
       <c r="F19" t="n">
-        <v>43.17</v>
+        <v>44.5</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>85</v>
+        <v>259</v>
       </c>
       <c r="F20" t="n">
-        <v>42.5</v>
+        <v>43.17</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>379</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>42.11</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E23" t="n">
-        <v>246</v>
+        <v>123</v>
       </c>
       <c r="F23" t="n">
         <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>40.33</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>440</v>
+        <v>121</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>40.33</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>318</v>
+        <v>440</v>
       </c>
       <c r="F27" t="n">
-        <v>39.75</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>316</v>
+        <v>440</v>
       </c>
       <c r="F28" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
         <v>3</v>
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>75</v>
+        <v>409</v>
       </c>
       <c r="F31" t="n">
-        <v>37.5</v>
+        <v>37.18</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>409</v>
+        <v>328</v>
       </c>
       <c r="F32" t="n">
-        <v>37.18</v>
+        <v>36.44</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
         <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="F33" t="n">
-        <v>36.7</v>
+        <v>36.22</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>35.25</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>315</v>
+        <v>35</v>
       </c>
       <c r="F38" t="n">
         <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,13 +1407,13 @@
         <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="F39" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>202</v>
+        <v>348</v>
       </c>
       <c r="F40" t="n">
-        <v>33.67</v>
+        <v>34.8</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>201</v>
+        <v>377</v>
       </c>
       <c r="F41" t="n">
-        <v>33.5</v>
+        <v>34.27</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>232</v>
+        <v>34</v>
       </c>
       <c r="F42" t="n">
-        <v>33.14</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1507,13 +1507,13 @@
         <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>361</v>
+        <v>303</v>
       </c>
       <c r="F43" t="n">
-        <v>32.82</v>
+        <v>33.67</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="F44" t="n">
-        <v>32</v>
+        <v>33.67</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>286</v>
+        <v>201</v>
       </c>
       <c r="F45" t="n">
-        <v>31.78</v>
+        <v>33.5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F46" t="n">
-        <v>31.71</v>
+        <v>33.14</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>314</v>
+        <v>165</v>
       </c>
       <c r="F47" t="n">
-        <v>31.4</v>
+        <v>33</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="F48" t="n">
-        <v>31.38</v>
+        <v>32.82</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="F49" t="n">
-        <v>31.2</v>
+        <v>32.56</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
         <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>92</v>
+        <v>286</v>
       </c>
       <c r="F50" t="n">
-        <v>30.67</v>
+        <v>31.78</v>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="F51" t="n">
-        <v>30.6</v>
+        <v>31.71</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>30</v>
+        <v>314</v>
       </c>
       <c r="F52" t="n">
-        <v>30</v>
+        <v>31.4</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
         <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F53" t="n">
-        <v>30</v>
+        <v>31.2</v>
       </c>
       <c r="G53" t="n">
         <v>3</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>269</v>
+        <v>92</v>
       </c>
       <c r="F54" t="n">
-        <v>29.89</v>
+        <v>30.67</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E55" t="n">
-        <v>236</v>
+        <v>92</v>
       </c>
       <c r="F55" t="n">
-        <v>29.5</v>
+        <v>30.67</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,13 +1857,13 @@
         <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F57" t="n">
-        <v>28.12</v>
+        <v>29.89</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>278</v>
+        <v>173</v>
       </c>
       <c r="F58" t="n">
-        <v>27.8</v>
+        <v>28.83</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E59" t="n">
-        <v>111</v>
+        <v>251</v>
       </c>
       <c r="F59" t="n">
-        <v>27.75</v>
+        <v>27.89</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="F60" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="F61" t="n">
-        <v>27</v>
+        <v>27.75</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="F62" t="n">
-        <v>26.33</v>
+        <v>27.5</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>136</v>
       </c>
       <c r="F63" t="n">
-        <v>26</v>
+        <v>27.2</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E64" t="n">
-        <v>103</v>
+        <v>261</v>
       </c>
       <c r="F64" t="n">
-        <v>25.75</v>
+        <v>26.1</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="F65" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
         <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="F66" t="n">
-        <v>24.67</v>
+        <v>25.75</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E67" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F67" t="n">
-        <v>24.22</v>
+        <v>25.67</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="F69" t="n">
-        <v>23</v>
+        <v>24.67</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E70" t="n">
-        <v>68</v>
+        <v>218</v>
       </c>
       <c r="F70" t="n">
-        <v>22.67</v>
+        <v>24.22</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2207,10 +2207,10 @@
         <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F71" t="n">
-        <v>22.67</v>
+        <v>23</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F72" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="F73" t="n">
-        <v>20.86</v>
+        <v>22.33</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -2272,20 +2272,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="F74" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D75" t="n">
         <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="F75" t="n">
-        <v>19</v>
+        <v>20.86</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="F76" t="n">
-        <v>18.3</v>
+        <v>20.75</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="F77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2372,17 +2372,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F78" t="n">
         <v>18</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F79" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,20 +2422,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E80" t="n">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F80" t="n">
-        <v>17</v>
+        <v>17.73</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F81" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F83" t="n">
-        <v>16.33</v>
+        <v>16.75</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E84" t="n">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="F84" t="n">
-        <v>16</v>
+        <v>16.73</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E85" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F85" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F86" t="n">
-        <v>15.67</v>
+        <v>16.33</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -2632,13 +2632,13 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F89" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2672,20 +2672,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F90" t="n">
-        <v>15</v>
+        <v>15.67</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -2697,20 +2697,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F91" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>13.33</v>
+        <v>15</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F93" t="n">
-        <v>13.17</v>
+        <v>14.8</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F94" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F95" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F96" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E97" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F97" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="F98" t="n">
-        <v>12</v>
+        <v>13.17</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F99" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="F100" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F101" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,20 +2972,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F102" t="n">
-        <v>10.83</v>
+        <v>12</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F103" t="n">
-        <v>10.75</v>
+        <v>11</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F104" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F105" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F106" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
         <v>10</v>
@@ -3113,7 +3113,7 @@
         <v>10</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F109" t="n">
-        <v>8</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3172,20 +3172,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3197,14 +3197,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
         <v>8</v>
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F112" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -3272,11 +3272,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D114" t="n">
         <v>2</v>
@@ -3288,7 +3288,7 @@
         <v>7</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C115" t="n">
+        <v>11</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="n">
         <v>7</v>
-      </c>
-      <c r="D115" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" t="n">
-        <v>14</v>
       </c>
       <c r="F115" t="n">
         <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F116" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3347,20 +3347,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E117" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F117" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="G117" t="n">
         <v>3</v>
@@ -3372,14 +3372,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E118" t="n">
         <v>19</v>
@@ -3388,7 +3388,7 @@
         <v>6.33</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F119" t="n">
-        <v>6.29</v>
+        <v>6.33</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E120" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="F120" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F121" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C122" t="n">
+        <v>7</v>
+      </c>
+      <c r="D122" t="n">
         <v>4</v>
-      </c>
-      <c r="D122" t="n">
-        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>6</v>
@@ -3488,7 +3488,7 @@
         <v>6</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
         <v>6</v>
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F124" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F125" t="n">
         <v>5.5</v>
@@ -3572,20 +3572,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E126" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F127" t="n">
         <v>5</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3622,23 +3622,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C128" t="n">
+        <v>11</v>
+      </c>
+      <c r="D128" t="n">
         <v>3</v>
       </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -3647,11 +3647,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>4</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3672,11 +3672,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
@@ -3688,7 +3688,7 @@
         <v>4</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3697,20 +3697,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F131" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3722,20 +3722,20 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F132" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F133" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3772,17 +3772,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F134" t="n">
         <v>3</v>
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3822,20 +3822,20 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136" t="n">
         <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>2</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D137" t="n">
         <v>2</v>
@@ -3872,14 +3872,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
@@ -3888,7 +3888,7 @@
         <v>2</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -3897,23 +3897,23 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
         <v>2</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
@@ -3938,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3947,20 +3947,20 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
@@ -3972,20 +3972,20 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D142" t="n">
         <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
         <v>2</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D143" t="n">
         <v>1</v>
@@ -4022,23 +4022,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
         <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -4072,23 +4072,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D146" t="n">
         <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -4097,23 +4097,23 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -4122,23 +4122,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4147,14 +4147,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4172,11 +4172,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -4247,11 +4247,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4347,11 +4347,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -4572,11 +4572,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
         <v>2</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -4722,11 +4722,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
@@ -4772,11 +4772,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5183,10 +5183,10 @@
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5198,20 +5198,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -5223,20 +5223,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
@@ -5348,20 +5348,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5373,20 +5373,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5402,16 +5402,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5423,17 +5423,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
@@ -5448,20 +5448,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -5473,20 +5473,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5702,13 +5702,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -5748,20 +5748,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -6048,20 +6048,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="F38" t="n">
         <v>7</v>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="F39" t="n">
         <v>7</v>
@@ -6123,17 +6123,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="F40" t="n">
         <v>7</v>
@@ -6148,17 +6148,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
         <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="F41" t="n">
         <v>7</v>
@@ -6173,20 +6173,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -6198,17 +6198,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>212</v>
+        <v>90</v>
       </c>
       <c r="F43" t="n">
         <v>6</v>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
@@ -6248,17 +6248,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
@@ -6273,17 +6273,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="F46" t="n">
         <v>6</v>
@@ -6298,17 +6298,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="F47" t="n">
         <v>6</v>
@@ -6323,20 +6323,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -6348,20 +6348,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E49" t="n">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -6373,20 +6373,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
         <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -6423,17 +6423,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6448,17 +6448,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6473,17 +6473,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6523,20 +6523,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -6548,20 +6548,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
@@ -6598,17 +6598,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
@@ -6673,17 +6673,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F62" t="n">
         <v>4</v>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -6748,20 +6748,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -6773,20 +6773,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>10</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>222</v>
+        <v>72</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -6823,17 +6823,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>168</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
@@ -6848,17 +6848,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6883,7 +6883,7 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -6908,10 +6908,10 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -6923,20 +6923,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6948,17 +6948,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="F73" t="n">
         <v>2</v>
@@ -6973,17 +6973,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -7033,7 +7033,7 @@
         <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -7048,17 +7048,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7073,17 +7073,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7098,17 +7098,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7133,10 +7133,10 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7148,17 +7148,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
@@ -7173,17 +7173,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -7198,17 +7198,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -7223,17 +7223,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7248,17 +7248,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -7273,17 +7273,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -7323,17 +7323,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7348,17 +7348,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7398,14 +7398,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>18</v>
@@ -7414,6 +7414,31 @@
         <v>1</v>
       </c>
       <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>30</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>494</v>
+        <v>392</v>
       </c>
       <c r="F6" t="n">
-        <v>54.89</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -597,20 +597,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>377</v>
+        <v>494</v>
       </c>
       <c r="F7" t="n">
-        <v>53.86</v>
+        <v>54.89</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>243</v>
+        <v>415</v>
       </c>
       <c r="F10" t="n">
-        <v>48.6</v>
+        <v>51.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>382</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
-        <v>47.75</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="F12" t="n">
-        <v>47.57</v>
+        <v>48.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,20 +747,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>475</v>
+        <v>382</v>
       </c>
       <c r="F13" t="n">
-        <v>47.5</v>
+        <v>47.75</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>190</v>
+        <v>475</v>
       </c>
       <c r="F14" t="n">
         <v>47.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>468</v>
+        <v>190</v>
       </c>
       <c r="F15" t="n">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>364</v>
+        <v>174</v>
       </c>
       <c r="F18" t="n">
-        <v>45.5</v>
+        <v>43.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>178</v>
+        <v>477</v>
       </c>
       <c r="F19" t="n">
-        <v>44.5</v>
+        <v>43.36</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,13 +932,13 @@
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="F20" t="n">
-        <v>43.17</v>
+        <v>42.44</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>85</v>
+        <v>379</v>
       </c>
       <c r="F21" t="n">
-        <v>42.5</v>
+        <v>42.11</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>379</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>42.11</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>123</v>
+        <v>246</v>
       </c>
       <c r="F23" t="n">
         <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40.33</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1057,13 +1057,13 @@
         <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>121</v>
+        <v>440</v>
       </c>
       <c r="F26" t="n">
-        <v>40.33</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>440</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>440</v>
+        <v>233</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>38.83</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>271</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38.71</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>233</v>
+        <v>409</v>
       </c>
       <c r="F30" t="n">
-        <v>38.83</v>
+        <v>37.18</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>409</v>
+        <v>328</v>
       </c>
       <c r="F31" t="n">
-        <v>37.18</v>
+        <v>36.44</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1232,10 +1232,10 @@
         <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F32" t="n">
-        <v>36.44</v>
+        <v>36.22</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="F33" t="n">
-        <v>36.22</v>
+        <v>36</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="F34" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>342</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="F43" t="n">
-        <v>33.67</v>
+        <v>34</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="F44" t="n">
         <v>33.67</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,10 +1557,10 @@
         <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F45" t="n">
-        <v>33.5</v>
+        <v>33.67</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="F46" t="n">
-        <v>33.14</v>
+        <v>33.5</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="F47" t="n">
-        <v>33</v>
+        <v>33.14</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c r="F48" t="n">
-        <v>32.82</v>
+        <v>33</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1657,13 +1657,13 @@
         <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="F49" t="n">
-        <v>32.56</v>
+        <v>32.82</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="F50" t="n">
-        <v>31.78</v>
+        <v>32.56</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>269</v>
       </c>
       <c r="F56" t="n">
-        <v>30</v>
+        <v>29.89</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="F57" t="n">
-        <v>29.89</v>
+        <v>28.83</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1872,20 +1872,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E58" t="n">
-        <v>173</v>
+        <v>251</v>
       </c>
       <c r="F58" t="n">
-        <v>28.83</v>
+        <v>27.89</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F59" t="n">
-        <v>27.89</v>
+        <v>27.8</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>278</v>
+        <v>110</v>
       </c>
       <c r="F60" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="F61" t="n">
-        <v>27.75</v>
+        <v>27.2</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F62" t="n">
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,20 +1997,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E63" t="n">
-        <v>136</v>
+        <v>261</v>
       </c>
       <c r="F63" t="n">
-        <v>27.2</v>
+        <v>26.1</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>261</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="F65" t="n">
-        <v>26</v>
+        <v>25.75</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="F66" t="n">
-        <v>25.75</v>
+        <v>25.67</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F67" t="n">
-        <v>25.67</v>
+        <v>25</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>24.22</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="F69" t="n">
-        <v>24.67</v>
+        <v>23</v>
       </c>
       <c r="G69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>218</v>
+        <v>161</v>
       </c>
       <c r="F70" t="n">
-        <v>24.22</v>
+        <v>23</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
-        <v>207</v>
+        <v>67</v>
       </c>
       <c r="F71" t="n">
-        <v>23</v>
+        <v>22.33</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F72" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,20 +2247,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="F73" t="n">
-        <v>22.33</v>
+        <v>20.86</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="F74" t="n">
-        <v>21.5</v>
+        <v>20.75</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D75" t="n">
         <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="F75" t="n">
-        <v>20.86</v>
+        <v>19</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2322,20 +2322,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D76" t="n">
         <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F76" t="n">
-        <v>20.75</v>
+        <v>18.5</v>
       </c>
       <c r="G76" t="n">
         <v>3</v>
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="F77" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2388,7 +2388,7 @@
         <v>18</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>35</v>
@@ -2463,7 +2463,7 @@
         <v>17.5</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F82" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F83" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="F84" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E85" t="n">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="F85" t="n">
-        <v>16.4</v>
+        <v>16.73</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F86" t="n">
-        <v>16.33</v>
+        <v>16.4</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F87" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
         <v>16</v>
@@ -2638,7 +2638,7 @@
         <v>16</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F90" t="n">
-        <v>15.67</v>
+        <v>16</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F91" t="n">
-        <v>15</v>
+        <v>15.67</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>15</v>
@@ -2738,7 +2738,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F93" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="F94" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2797,20 +2797,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F95" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2832,10 +2832,10 @@
         <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F96" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="F97" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E98" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="F98" t="n">
-        <v>13.17</v>
+        <v>14</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F99" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>10</v>
+      </c>
+      <c r="D100" t="n">
         <v>8</v>
       </c>
-      <c r="D100" t="n">
-        <v>7</v>
-      </c>
       <c r="E100" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F100" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E101" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F101" t="n">
         <v>13</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E102" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F103" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E104" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F104" t="n">
-        <v>10.83</v>
+        <v>12.5</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F105" t="n">
-        <v>10.75</v>
+        <v>12</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F106" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F107" t="n">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F108" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,20 +3147,20 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E109" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="F109" t="n">
-        <v>9.109999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D110" t="n">
         <v>2</v>
       </c>
       <c r="E110" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -3207,13 +3207,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E112" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F112" t="n">
-        <v>8</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -3257,10 +3257,10 @@
         <v>2</v>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F113" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3272,23 +3272,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -3297,20 +3297,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D115" t="n">
         <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F115" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -3322,20 +3322,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
         <v>2</v>
       </c>
       <c r="E116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F116" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3347,23 +3347,23 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F117" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>11</v>
       </c>
       <c r="D118" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F118" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="G118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,20 +3397,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F119" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D120" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E120" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="F120" t="n">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F121" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3472,20 +3472,20 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D122" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E122" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F122" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G122" t="n">
         <v>3</v>
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F123" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E124" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F124" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E125" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F125" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F126" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3622,23 +3622,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F128" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3647,20 +3647,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F129" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3672,23 +3672,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3722,23 +3722,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F132" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3747,20 +3747,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
         <v>4</v>
       </c>
-      <c r="D133" t="n">
-        <v>3</v>
-      </c>
-      <c r="E133" t="n">
-        <v>10</v>
-      </c>
       <c r="F133" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F134" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C135" t="n">
+        <v>4</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3</v>
+      </c>
+      <c r="E135" t="n">
         <v>10</v>
       </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>3</v>
-      </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E136" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F136" t="n">
         <v>3</v>
       </c>
       <c r="G136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3872,20 +3872,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D138" t="n">
         <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G138" t="n">
         <v>2</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D139" t="n">
         <v>2</v>
@@ -3922,14 +3922,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
@@ -3938,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -3947,23 +3947,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F141" t="n">
         <v>2</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -3988,7 +3988,7 @@
         <v>2</v>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,20 +3997,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C143" t="n">
         <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -4022,20 +4022,20 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
         <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G144" t="n">
         <v>2</v>
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
@@ -4072,23 +4072,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D146" t="n">
         <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D147" t="n">
         <v>1</v>
@@ -4122,23 +4122,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
         <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" t="n">
         <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -4147,23 +4147,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4172,23 +4172,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,14 +4497,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -4597,14 +4597,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4847,11 +4847,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -4972,14 +4972,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -4997,11 +4997,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -5022,11 +5022,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -5047,14 +5047,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -5072,11 +5072,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -5097,22 +5097,97 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>8</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C187" t="n">
-        <v>10</v>
-      </c>
-      <c r="D187" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="n">
+      <c r="C190" t="n">
+        <v>11</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5127,7 +5202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5398,17 +5473,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -5423,20 +5498,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5448,7 +5523,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5458,7 +5533,7 @@
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -5473,17 +5548,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
@@ -5498,20 +5573,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>156</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5523,17 +5598,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
@@ -5548,17 +5623,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
@@ -5652,7 +5727,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -5902,13 +5977,13 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
         <v>9</v>
       </c>
-      <c r="D31" t="n">
-        <v>8</v>
-      </c>
       <c r="E31" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -5977,7 +6052,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
         <v>9</v>
@@ -6227,13 +6302,13 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="D44" t="n">
-        <v>9</v>
-      </c>
       <c r="E44" t="n">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
@@ -6273,17 +6348,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="F46" t="n">
         <v>6</v>
@@ -6298,17 +6373,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F47" t="n">
         <v>6</v>
@@ -6323,17 +6398,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="F48" t="n">
         <v>6</v>
@@ -6348,17 +6423,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F49" t="n">
         <v>6</v>
@@ -6373,17 +6448,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -6398,20 +6473,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
         <v>84</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -6423,17 +6498,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6448,17 +6523,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6473,17 +6548,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -6498,17 +6573,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6523,17 +6598,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -6548,17 +6623,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6573,20 +6648,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -6598,17 +6673,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -6623,17 +6698,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -6648,17 +6723,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
@@ -6673,17 +6748,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="F62" t="n">
         <v>4</v>
@@ -6698,17 +6773,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
@@ -6723,17 +6798,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -6748,17 +6823,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -6773,17 +6848,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E66" t="n">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -6798,17 +6873,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
         <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F67" t="n">
         <v>4</v>
@@ -6823,20 +6898,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -6848,17 +6923,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>246</v>
+        <v>30</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
@@ -6873,17 +6948,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>66</v>
+        <v>246</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -6998,17 +7073,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -7023,17 +7098,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -7048,7 +7123,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -7058,7 +7133,7 @@
         <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7073,17 +7148,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7098,17 +7173,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -7123,7 +7198,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -7133,7 +7208,7 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -7148,20 +7223,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -7173,7 +7248,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Yash Thakur</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -7183,10 +7258,10 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7198,20 +7273,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7223,17 +7298,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -7248,7 +7323,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -7258,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F85" t="n">
         <v>1</v>
@@ -7273,17 +7348,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7298,17 +7373,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -7323,17 +7398,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7348,17 +7423,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7373,17 +7448,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7398,14 +7473,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>18</v>
@@ -7423,22 +7498,97 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>10</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>12</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ben Dwarshuis</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>24</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Raj Angad Bawa</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>18</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>Will Jacks</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="C95" t="n">
         <v>4</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D95" t="n">
         <v>3</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E95" t="n">
         <v>30</v>
       </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -607,13 +607,13 @@
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>494</v>
+        <v>430</v>
       </c>
       <c r="F7" t="n">
-        <v>54.89</v>
+        <v>53.75</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>430</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
-        <v>53.75</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>415</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>51.88</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -672,20 +672,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>415</v>
+        <v>508</v>
       </c>
       <c r="F10" t="n">
-        <v>51.88</v>
+        <v>50.8</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>475</v>
+        <v>190</v>
       </c>
       <c r="F14" t="n">
         <v>47.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="F15" t="n">
-        <v>47.5</v>
+        <v>46.4</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>232</v>
+        <v>481</v>
       </c>
       <c r="F16" t="n">
-        <v>46.4</v>
+        <v>43.73</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>462</v>
+        <v>174</v>
       </c>
       <c r="F17" t="n">
-        <v>46.2</v>
+        <v>43.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>174</v>
+        <v>477</v>
       </c>
       <c r="F18" t="n">
-        <v>43.5</v>
+        <v>43.36</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="F19" t="n">
-        <v>43.36</v>
+        <v>42.45</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>379</v>
+        <v>296</v>
       </c>
       <c r="F21" t="n">
-        <v>42.11</v>
+        <v>42.29</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>379</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>42.11</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>246</v>
+        <v>501</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>41.75</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
-        <v>40.33</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>440</v>
+        <v>121</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>40.33</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>409</v>
+        <v>328</v>
       </c>
       <c r="F30" t="n">
-        <v>37.18</v>
+        <v>36.44</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,10 +1207,10 @@
         <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F31" t="n">
-        <v>36.44</v>
+        <v>36.22</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>326</v>
+        <v>252</v>
       </c>
       <c r="F32" t="n">
-        <v>36.22</v>
+        <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>252</v>
+        <v>179</v>
       </c>
       <c r="F33" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>179</v>
+        <v>71</v>
       </c>
       <c r="F34" t="n">
-        <v>35.8</v>
+        <v>35.5</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="F35" t="n">
-        <v>35.5</v>
+        <v>35.25</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="F36" t="n">
-        <v>35.25</v>
+        <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,13 +1432,13 @@
         <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="F40" t="n">
-        <v>34.8</v>
+        <v>34.27</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1447,20 +1447,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="F41" t="n">
-        <v>34.27</v>
+        <v>34.2</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>342</v>
+        <v>34</v>
       </c>
       <c r="F42" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>34</v>
+        <v>303</v>
       </c>
       <c r="F43" t="n">
-        <v>34</v>
+        <v>33.67</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>303</v>
+        <v>202</v>
       </c>
       <c r="F44" t="n">
         <v>33.67</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1557,10 +1557,10 @@
         <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F45" t="n">
-        <v>33.67</v>
+        <v>33.5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F46" t="n">
-        <v>33.5</v>
+        <v>33.14</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>232</v>
+        <v>165</v>
       </c>
       <c r="F47" t="n">
-        <v>33.14</v>
+        <v>33</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>165</v>
+        <v>293</v>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>32.56</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E49" t="n">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="F49" t="n">
-        <v>32.82</v>
+        <v>32.27</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>293</v>
+        <v>96</v>
       </c>
       <c r="F50" t="n">
-        <v>32.56</v>
+        <v>32</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>222</v>
+        <v>314</v>
       </c>
       <c r="F51" t="n">
-        <v>31.71</v>
+        <v>31.4</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>314</v>
+        <v>156</v>
       </c>
       <c r="F52" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>156</v>
+        <v>92</v>
       </c>
       <c r="F53" t="n">
-        <v>31.2</v>
+        <v>30.67</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>92</v>
+        <v>361</v>
       </c>
       <c r="F54" t="n">
-        <v>30.67</v>
+        <v>30.08</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="F55" t="n">
-        <v>30.67</v>
+        <v>29.89</v>
       </c>
       <c r="G55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>269</v>
+        <v>173</v>
       </c>
       <c r="F56" t="n">
-        <v>29.89</v>
+        <v>28.83</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="F57" t="n">
-        <v>28.83</v>
+        <v>28</v>
       </c>
       <c r="G57" t="n">
         <v>2</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="F75" t="n">
-        <v>19</v>
+        <v>19.33</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F76" t="n">
         <v>18.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E77" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F77" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="F78" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2397,17 +2397,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F79" t="n">
         <v>18</v>
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2457,10 +2457,10 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F81" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>11</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E82" t="n">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="F82" t="n">
-        <v>17.5</v>
+        <v>17.73</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F83" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F84" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="F85" t="n">
-        <v>16.73</v>
+        <v>17</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,20 +2572,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E86" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F86" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>11</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E87" t="n">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="F87" t="n">
-        <v>16.33</v>
+        <v>16.73</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E88" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="F88" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>16</v>
+        <v>16.33</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,14 +2672,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
         <v>16</v>
@@ -2688,7 +2688,7 @@
         <v>16</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F91" t="n">
-        <v>15.67</v>
+        <v>16</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2732,10 +2732,10 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F96" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F97" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="F98" t="n">
         <v>14</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F99" t="n">
-        <v>13.33</v>
+        <v>14</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>13.17</v>
+        <v>13.33</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>10</v>
       </c>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E101" t="n">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="F101" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G101" t="n">
         <v>2</v>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="F102" t="n">
         <v>13</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E103" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F103" t="n">
         <v>13</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F104" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E105" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="F105" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F106" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F107" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F108" t="n">
-        <v>10.75</v>
+        <v>10.83</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F109" t="n">
-        <v>10.33</v>
+        <v>10.75</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,23 +3172,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F110" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3197,14 +3197,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
         <v>10</v>
@@ -3213,7 +3213,7 @@
         <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F122" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3497,14 +3497,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E123" t="n">
         <v>19</v>
@@ -3513,7 +3513,7 @@
         <v>6.33</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E124" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F124" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="G124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C125" t="n">
+        <v>11</v>
+      </c>
+      <c r="D125" t="n">
         <v>7</v>
       </c>
-      <c r="D125" t="n">
-        <v>4</v>
-      </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F125" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -3572,14 +3572,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E126" t="n">
         <v>6</v>
@@ -3588,7 +3588,7 @@
         <v>6</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -3597,14 +3597,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
         <v>6</v>
@@ -3622,23 +3622,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F128" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F129" t="n">
         <v>5.5</v>
@@ -3672,20 +3672,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E130" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F130" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F131" t="n">
         <v>5</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3722,20 +3722,20 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D138" t="n">
         <v>2</v>
@@ -3888,7 +3888,7 @@
         <v>3</v>
       </c>
       <c r="G138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3897,20 +3897,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D139" t="n">
         <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G139" t="n">
         <v>2</v>
@@ -3922,11 +3922,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
         <v>2</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -3988,7 +3988,7 @@
         <v>2</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F143" t="n">
         <v>2</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
@@ -4022,23 +4022,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F144" t="n">
         <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4047,23 +4047,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -4088,7 +4088,7 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -4122,23 +4122,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
         <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4147,23 +4147,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -4172,14 +4172,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4222,11 +4222,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4297,11 +4297,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -4322,11 +4322,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,11 +4422,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4472,14 +4472,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -4497,14 +4497,14 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -4672,14 +4672,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C173" t="n">
         <v>5</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4772,11 +4772,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4797,11 +4797,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -5273,20 +5273,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5308,10 +5308,10 @@
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5348,17 +5348,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
@@ -5373,20 +5373,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -5448,20 +5448,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5473,17 +5473,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -5498,17 +5498,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>
@@ -5523,20 +5523,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5558,10 +5558,10 @@
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5573,20 +5573,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5598,20 +5598,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5623,20 +5623,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5658,10 +5658,10 @@
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -5673,20 +5673,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>110</v>
+        <v>204</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5698,23 +5698,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5723,23 +5723,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -5748,17 +5748,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="F25" t="n">
         <v>10</v>
@@ -5848,20 +5848,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>258</v>
+        <v>114</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="F27" t="n">
         <v>9</v>
@@ -5898,17 +5898,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
@@ -5923,17 +5923,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
@@ -5948,20 +5948,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>168</v>
+      </c>
+      <c r="F30" t="n">
         <v>9</v>
-      </c>
-      <c r="E30" t="n">
-        <v>156</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -5973,17 +5973,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
         <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -5998,17 +5998,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>121</v>
+        <v>202</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
@@ -6048,17 +6048,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -6123,17 +6123,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -6227,13 +6227,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="F41" t="n">
         <v>7</v>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -6523,17 +6523,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6548,17 +6548,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6598,17 +6598,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -6623,17 +6623,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E58" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -6673,20 +6673,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86" t="n">
         <v>4</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>71.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>237</v>
+        <v>132</v>
       </c>
       <c r="F4" t="n">
-        <v>59.25</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -572,20 +572,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>392</v>
+        <v>484</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>53.78</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -622,20 +622,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>508</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>50.8</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="F9" t="n">
-        <v>51.88</v>
+        <v>49.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>508</v>
+        <v>98</v>
       </c>
       <c r="F10" t="n">
-        <v>50.8</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>436</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>48.44</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -722,20 +722,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>243</v>
+        <v>430</v>
       </c>
       <c r="F12" t="n">
-        <v>48.6</v>
+        <v>47.78</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>382</v>
+        <v>190</v>
       </c>
       <c r="F13" t="n">
-        <v>47.75</v>
+        <v>47.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="F14" t="n">
-        <v>47.5</v>
+        <v>44.67</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>232</v>
+        <v>439</v>
       </c>
       <c r="F15" t="n">
-        <v>46.4</v>
+        <v>43.9</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="F20" t="n">
-        <v>42.44</v>
+        <v>42.29</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -947,7 +947,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -957,13 +957,13 @@
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>296</v>
+        <v>501</v>
       </c>
       <c r="F21" t="n">
-        <v>42.29</v>
+        <v>41.75</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>379</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>42.11</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>501</v>
+        <v>121</v>
       </c>
       <c r="F23" t="n">
-        <v>41.75</v>
+        <v>40.33</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>440</v>
       </c>
       <c r="F24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>40.33</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
         <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>440</v>
+        <v>234</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>233</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>38.83</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="F28" t="n">
-        <v>38.83</v>
+        <v>38.71</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>271</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>38.71</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>328</v>
+        <v>114</v>
       </c>
       <c r="F30" t="n">
-        <v>36.44</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="F31" t="n">
-        <v>36.22</v>
+        <v>36.7</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
         <v>6</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="F36" t="n">
         <v>35</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>420</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>35</v>
+        <v>315</v>
       </c>
       <c r="F38" t="n">
         <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1407,13 +1407,13 @@
         <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="F39" t="n">
-        <v>35</v>
+        <v>34.27</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,13 +1432,13 @@
         <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>377</v>
+        <v>340</v>
       </c>
       <c r="F40" t="n">
-        <v>34.27</v>
+        <v>34</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>342</v>
+        <v>34</v>
       </c>
       <c r="F41" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>337</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>33.7</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>303</v>
+        <v>202</v>
       </c>
       <c r="F43" t="n">
         <v>33.67</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E44" t="n">
-        <v>202</v>
+        <v>336</v>
       </c>
       <c r="F44" t="n">
-        <v>33.67</v>
+        <v>33.6</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>232</v>
+        <v>364</v>
       </c>
       <c r="F46" t="n">
-        <v>33.14</v>
+        <v>33.09</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="F47" t="n">
         <v>33</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>293</v>
+        <v>165</v>
       </c>
       <c r="F48" t="n">
-        <v>32.56</v>
+        <v>33</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>355</v>
+        <v>228</v>
       </c>
       <c r="F49" t="n">
-        <v>32.27</v>
+        <v>32.57</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>96</v>
+        <v>293</v>
       </c>
       <c r="F50" t="n">
-        <v>32</v>
+        <v>32.56</v>
       </c>
       <c r="G50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>314</v>
+        <v>355</v>
       </c>
       <c r="F51" t="n">
-        <v>31.4</v>
+        <v>32.27</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E52" t="n">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>31.2</v>
+        <v>32</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E53" t="n">
-        <v>92</v>
+        <v>314</v>
       </c>
       <c r="F53" t="n">
-        <v>30.67</v>
+        <v>31.4</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
-        <v>361</v>
+        <v>156</v>
       </c>
       <c r="F54" t="n">
-        <v>30.08</v>
+        <v>31.2</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="F55" t="n">
-        <v>29.89</v>
+        <v>31.2</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>173</v>
+        <v>92</v>
       </c>
       <c r="F56" t="n">
-        <v>28.83</v>
+        <v>30.67</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="F57" t="n">
-        <v>28</v>
+        <v>30.67</v>
       </c>
       <c r="G57" t="n">
         <v>2</v>
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="F58" t="n">
-        <v>27.89</v>
+        <v>30.08</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="F59" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="F60" t="n">
-        <v>27.5</v>
+        <v>28.83</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C61" t="n">
+        <v>11</v>
+      </c>
+      <c r="D61" t="n">
         <v>10</v>
       </c>
-      <c r="D61" t="n">
-        <v>6</v>
-      </c>
       <c r="E61" t="n">
-        <v>136</v>
+        <v>224</v>
       </c>
       <c r="F61" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E62" t="n">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>27.89</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E63" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="F63" t="n">
-        <v>26.1</v>
+        <v>27.8</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="F64" t="n">
-        <v>26</v>
+        <v>27.5</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D65" t="n">
         <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="F65" t="n">
-        <v>25.75</v>
+        <v>27.2</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="F66" t="n">
-        <v>25.67</v>
+        <v>27</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>225</v>
+        <v>26</v>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E68" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="F68" t="n">
-        <v>24.22</v>
+        <v>25.67</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E69" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="F69" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2182,13 +2182,13 @@
         <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="F70" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2197,20 +2197,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E71" t="n">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="F71" t="n">
-        <v>22.33</v>
+        <v>23.7</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" t="n">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="F72" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F73" t="n">
-        <v>20.86</v>
+        <v>23</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="F74" t="n">
-        <v>20.75</v>
+        <v>21.5</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="F75" t="n">
-        <v>19.33</v>
+        <v>20.86</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>11</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7</v>
+      </c>
+      <c r="E76" t="n">
+        <v>83</v>
+      </c>
+      <c r="F76" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="G76" t="n">
         <v>3</v>
-      </c>
-      <c r="D76" t="n">
-        <v>2</v>
-      </c>
-      <c r="E76" t="n">
-        <v>37</v>
-      </c>
-      <c r="F76" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="F77" t="n">
-        <v>18.5</v>
+        <v>19.33</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F78" t="n">
         <v>18.5</v>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F79" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2438,7 +2438,7 @@
         <v>18</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F81" t="n">
         <v>18</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,20 +2472,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="F82" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E83" t="n">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="F83" t="n">
-        <v>17.5</v>
+        <v>17.73</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>35</v>
@@ -2538,7 +2538,7 @@
         <v>17.5</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F86" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="F87" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E88" t="n">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="F88" t="n">
-        <v>16.4</v>
+        <v>16.73</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F89" t="n">
-        <v>16.33</v>
+        <v>16.4</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E93" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F93" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Vishnu Vinod</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -2822,20 +2822,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C96" t="n">
+        <v>8</v>
+      </c>
+      <c r="D96" t="n">
         <v>5</v>
       </c>
-      <c r="D96" t="n">
-        <v>2</v>
-      </c>
       <c r="E96" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="F96" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2847,20 +2847,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F97" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2907,10 +2907,10 @@
         <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F99" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="F100" t="n">
-        <v>13.33</v>
+        <v>14.17</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="F101" t="n">
-        <v>13.17</v>
+        <v>14</v>
       </c>
       <c r="G101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E102" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F102" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C103" t="n">
+        <v>10</v>
+      </c>
+      <c r="D103" t="n">
         <v>8</v>
       </c>
-      <c r="D103" t="n">
-        <v>7</v>
-      </c>
       <c r="E103" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F103" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E104" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F104" t="n">
         <v>13</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -3047,20 +3047,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E105" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F105" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -3072,20 +3072,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F106" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="F107" t="n">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E108" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F108" t="n">
-        <v>10.83</v>
+        <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>10.75</v>
+        <v>12</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3172,20 +3172,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E110" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F110" t="n">
-        <v>10.33</v>
+        <v>10.83</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3197,20 +3197,20 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E111" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F111" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E112" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="F112" t="n">
-        <v>9.109999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E113" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F113" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -3272,20 +3272,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -3297,23 +3297,23 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
         <v>2</v>
       </c>
       <c r="E115" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F115" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3322,23 +3322,23 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F116" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -3357,13 +3357,13 @@
         <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F118" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C119" t="n">
+        <v>6</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="n">
         <v>7</v>
-      </c>
-      <c r="D119" t="n">
-        <v>2</v>
-      </c>
-      <c r="E119" t="n">
-        <v>14</v>
       </c>
       <c r="F119" t="n">
         <v>7</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3447,20 +3447,20 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F121" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3472,14 +3472,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E122" t="n">
         <v>13</v>
@@ -3488,7 +3488,7 @@
         <v>6.5</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F123" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="G123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3522,20 +3522,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F124" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>11</v>
       </c>
       <c r="D125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F125" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3572,23 +3572,23 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F126" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E127" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F127" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E128" t="n">
         <v>6</v>
@@ -3638,7 +3638,7 @@
         <v>6</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129">
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F129" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -3672,23 +3672,23 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F130" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -3697,20 +3697,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F131" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3722,23 +3722,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F132" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C134" t="n">
+        <v>11</v>
+      </c>
+      <c r="D134" t="n">
         <v>3</v>
       </c>
-      <c r="D134" t="n">
-        <v>2</v>
-      </c>
       <c r="E134" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F134" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C135" t="n">
         <v>4</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F135" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -3847,23 +3847,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C137" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" t="n">
         <v>10</v>
       </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="n">
-        <v>3</v>
-      </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -3872,17 +3872,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E138" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F138" t="n">
         <v>3</v>
@@ -3897,14 +3897,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
@@ -3913,7 +3913,7 @@
         <v>3</v>
       </c>
       <c r="G139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -3922,23 +3922,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" t="n">
         <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3957,10 +3957,10 @@
         <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G141" t="n">
         <v>2</v>
@@ -3972,11 +3972,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D142" t="n">
         <v>2</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D143" t="n">
         <v>2</v>
@@ -4022,23 +4022,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F144" t="n">
         <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D145" t="n">
         <v>2</v>
@@ -4072,20 +4072,20 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -4097,20 +4097,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D147" t="n">
         <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G147" t="n">
         <v>2</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D148" t="n">
         <v>1</v>
@@ -4147,23 +4147,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D149" t="n">
         <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4172,11 +4172,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
         <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -4222,23 +4222,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4247,23 +4247,23 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4272,14 +4272,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4297,11 +4297,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D155" t="n">
         <v>0</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -4447,11 +4447,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4472,14 +4472,14 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4522,11 +4522,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D164" t="n">
         <v>1</v>
@@ -4547,11 +4547,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4647,11 +4647,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4672,14 +4672,14 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -4722,11 +4722,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
         <v>1</v>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
         <v>2</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D176" t="n">
         <v>0</v>
@@ -4847,11 +4847,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -4872,14 +4872,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -4947,11 +4947,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -4972,14 +4972,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -5022,14 +5022,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -5047,11 +5047,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -5072,11 +5072,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -5097,14 +5097,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -5122,11 +5122,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -5147,11 +5147,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -5172,22 +5172,97 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>8</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C190" t="n">
-        <v>11</v>
-      </c>
-      <c r="D190" t="n">
-        <v>0</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" t="n">
+      <c r="C193" t="n">
+        <v>12</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5202,7 +5277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5252,16 +5327,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5373,17 +5448,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -5398,20 +5473,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -5423,20 +5498,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5448,17 +5523,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
@@ -5473,20 +5548,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -5498,17 +5573,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>264</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>
@@ -5523,17 +5598,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
@@ -5552,13 +5627,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
@@ -5648,17 +5723,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>156</v>
+        <v>234</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -5673,17 +5748,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
@@ -5698,7 +5773,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5708,10 +5783,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -5723,23 +5798,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5748,23 +5823,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="F22" t="n">
         <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -5773,17 +5848,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="F23" t="n">
         <v>10</v>
@@ -5798,17 +5873,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -5823,17 +5898,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="F25" t="n">
         <v>10</v>
@@ -5873,20 +5948,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>258</v>
+        <v>108</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -5898,17 +5973,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>161</v>
+        <v>258</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
@@ -5923,17 +5998,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
         <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F29" t="n">
         <v>9</v>
@@ -5948,17 +6023,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F30" t="n">
         <v>9</v>
@@ -5973,20 +6048,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>161</v>
+      </c>
+      <c r="F31" t="n">
         <v>9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>156</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -5998,20 +6073,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>10</v>
       </c>
       <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>195</v>
+      </c>
+      <c r="F32" t="n">
         <v>9</v>
-      </c>
-      <c r="E32" t="n">
-        <v>202</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6023,20 +6098,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6048,17 +6123,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
@@ -6073,17 +6148,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
@@ -6098,17 +6173,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -6123,17 +6198,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -6148,20 +6223,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -6173,20 +6248,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -6198,17 +6273,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="F40" t="n">
         <v>7</v>
@@ -6223,17 +6298,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="F41" t="n">
         <v>7</v>
@@ -6248,17 +6323,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="F42" t="n">
         <v>7</v>
@@ -6273,20 +6348,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -6298,7 +6373,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -6308,10 +6383,10 @@
         <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>236</v>
+        <v>198</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -6323,17 +6398,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
@@ -6348,17 +6423,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="F46" t="n">
         <v>6</v>
@@ -6373,17 +6448,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="F47" t="n">
         <v>6</v>
@@ -6398,17 +6473,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F48" t="n">
         <v>6</v>
@@ -6423,17 +6498,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>148</v>
       </c>
       <c r="F49" t="n">
         <v>6</v>
@@ -6448,17 +6523,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -6473,17 +6548,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -6623,17 +6698,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6648,17 +6723,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -6673,17 +6748,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E59" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
@@ -6698,20 +6773,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E60" t="n">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -6723,17 +6798,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
@@ -6748,17 +6823,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F62" t="n">
         <v>4</v>
@@ -6773,17 +6848,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
@@ -6798,17 +6873,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -6823,17 +6898,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -6848,17 +6923,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -6877,13 +6952,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E67" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F67" t="n">
         <v>4</v>
@@ -6898,17 +6973,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F68" t="n">
         <v>4</v>
@@ -6923,20 +6998,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E69" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -6948,17 +7023,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>246</v>
+        <v>30</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -6973,17 +7048,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>87</v>
+        <v>270</v>
       </c>
       <c r="F71" t="n">
         <v>3</v>
@@ -7048,14 +7123,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" t="n">
         <v>24</v>
@@ -7073,14 +7148,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" t="n">
         <v>24</v>
@@ -7098,17 +7173,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -7123,17 +7198,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7148,17 +7223,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7173,17 +7248,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -7198,17 +7273,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -7223,17 +7298,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -7248,17 +7323,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -7273,17 +7348,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -7298,20 +7373,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Yash Thakur</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7323,20 +7398,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7348,17 +7423,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -7373,17 +7448,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
         <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -7398,17 +7473,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7423,17 +7498,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7448,17 +7523,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7473,17 +7548,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -7498,17 +7573,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -7523,17 +7598,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -7548,17 +7623,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -7577,18 +7652,43 @@
         </is>
       </c>
       <c r="C95" t="n">
+        <v>5</v>
+      </c>
+      <c r="D95" t="n">
         <v>4</v>
       </c>
-      <c r="D95" t="n">
-        <v>3</v>
-      </c>
       <c r="E95" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ben Dwarshuis</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>24</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>71.5</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>286</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>71.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>430</v>
+        <v>508</v>
       </c>
       <c r="F7" t="n">
-        <v>53.75</v>
+        <v>50.8</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,13 +632,13 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>508</v>
+        <v>450</v>
       </c>
       <c r="F8" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>98</v>
+        <v>436</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>48.44</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F11" t="n">
-        <v>48.44</v>
+        <v>47.78</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>430</v>
+        <v>190</v>
       </c>
       <c r="F12" t="n">
-        <v>47.78</v>
+        <v>47.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="F13" t="n">
-        <v>47.5</v>
+        <v>44.67</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>197</v>
       </c>
       <c r="F25" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="F26" t="n">
         <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F27" t="n">
-        <v>38.83</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>271</v>
+        <v>467</v>
       </c>
       <c r="F28" t="n">
-        <v>38.71</v>
+        <v>38.92</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>38</v>
+        <v>233</v>
       </c>
       <c r="F29" t="n">
-        <v>38</v>
+        <v>38.83</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>114</v>
+        <v>271</v>
       </c>
       <c r="F30" t="n">
-        <v>38</v>
+        <v>38.71</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>367</v>
+        <v>38</v>
       </c>
       <c r="F31" t="n">
-        <v>36.7</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>252</v>
+        <v>114</v>
       </c>
       <c r="F32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" t="n">
         <v>11</v>
       </c>
-      <c r="D33" t="n">
-        <v>8</v>
-      </c>
       <c r="E33" t="n">
-        <v>179</v>
+        <v>367</v>
       </c>
       <c r="F33" t="n">
-        <v>35.8</v>
+        <v>36.7</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="F34" t="n">
-        <v>35.5</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25</v>
+        <v>35.8</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>420</v>
+        <v>71</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>35.25</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>315</v>
+        <v>420</v>
       </c>
       <c r="F38" t="n">
         <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>377</v>
+        <v>35</v>
       </c>
       <c r="F39" t="n">
-        <v>34.27</v>
+        <v>35</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1432,13 +1432,13 @@
         <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="F40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="F41" t="n">
-        <v>34</v>
+        <v>34.86</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1472,20 +1472,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
         <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F42" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="F43" t="n">
-        <v>33.67</v>
+        <v>34</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>336</v>
+        <v>169</v>
       </c>
       <c r="F44" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>201</v>
+        <v>337</v>
       </c>
       <c r="F45" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>364</v>
+        <v>202</v>
       </c>
       <c r="F46" t="n">
-        <v>33.09</v>
+        <v>33.67</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E47" t="n">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="F47" t="n">
-        <v>33</v>
+        <v>33.6</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>228</v>
+        <v>364</v>
       </c>
       <c r="F49" t="n">
-        <v>32.57</v>
+        <v>33.09</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,13 +1682,13 @@
         <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="F50" t="n">
-        <v>32.56</v>
+        <v>33</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>355</v>
+        <v>228</v>
       </c>
       <c r="F51" t="n">
-        <v>32.27</v>
+        <v>32.57</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>96</v>
+        <v>355</v>
       </c>
       <c r="F52" t="n">
-        <v>32</v>
+        <v>32.27</v>
       </c>
       <c r="G52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
-        <v>314</v>
+        <v>96</v>
       </c>
       <c r="F53" t="n">
-        <v>31.4</v>
+        <v>32</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E54" t="n">
-        <v>156</v>
+        <v>314</v>
       </c>
       <c r="F54" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>361</v>
+        <v>306</v>
       </c>
       <c r="F58" t="n">
-        <v>30.08</v>
+        <v>30.6</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E59" t="n">
-        <v>29</v>
+        <v>361</v>
       </c>
       <c r="F59" t="n">
-        <v>29</v>
+        <v>30.08</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="F60" t="n">
-        <v>28.83</v>
+        <v>29</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D62" t="n">
         <v>11</v>
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="F64" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
         <v>6</v>
       </c>
       <c r="E65" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F65" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E67" t="n">
-        <v>26</v>
+        <v>231</v>
       </c>
       <c r="F67" t="n">
-        <v>26</v>
+        <v>25.67</v>
       </c>
       <c r="G67" t="n">
         <v>2</v>
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D68" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F68" t="n">
-        <v>25.67</v>
+        <v>25</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E69" t="n">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>123</v>
+        <v>237</v>
       </c>
       <c r="F70" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>237</v>
+        <v>116</v>
       </c>
       <c r="F71" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E77" t="n">
-        <v>58</v>
+        <v>216</v>
       </c>
       <c r="F77" t="n">
-        <v>19.33</v>
+        <v>19.64</v>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F78" t="n">
-        <v>18.5</v>
+        <v>19.33</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="F79" t="n">
         <v>18.5</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E80" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F80" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2463,7 +2463,7 @@
         <v>18</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="F83" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E84" t="n">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="F84" t="n">
-        <v>17.5</v>
+        <v>17.73</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,14 +2547,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>35</v>
@@ -2563,7 +2563,7 @@
         <v>17.5</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F86" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F87" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D88" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="F88" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D89" t="n">
         <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F89" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2697,14 +2697,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>16</v>
@@ -2713,7 +2713,7 @@
         <v>16</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2722,11 +2722,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="F93" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F94" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="G94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -2797,14 +2797,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vishnu Vinod</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
         <v>15</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Vishnu Vinod</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E99" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F99" t="n">
-        <v>14.4</v>
+        <v>14.17</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="F100" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C101" t="n">
+        <v>10</v>
+      </c>
+      <c r="D101" t="n">
         <v>4</v>
       </c>
-      <c r="D101" t="n">
-        <v>2</v>
-      </c>
       <c r="E101" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F101" t="n">
-        <v>14</v>
+        <v>13.33</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F102" t="n">
-        <v>13.33</v>
+        <v>13.17</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D127" t="n">
         <v>7</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D134" t="n">
         <v>3</v>
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -4597,14 +4597,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>5</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4847,11 +4847,11 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -4872,11 +4872,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -4897,11 +4897,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -4922,14 +4922,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -4947,14 +4947,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -4972,11 +4972,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -5022,14 +5022,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -5047,14 +5047,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -5072,11 +5072,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -5122,11 +5122,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -5147,11 +5147,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -5197,11 +5197,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -5222,14 +5222,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -5247,22 +5247,72 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>1</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C193" t="n">
-        <v>12</v>
-      </c>
-      <c r="D193" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
+      <c r="C195" t="n">
+        <v>12</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5277,7 +5327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5377,13 +5427,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="F4" t="n">
         <v>19</v>
@@ -5398,17 +5448,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
@@ -5423,7 +5473,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5433,7 +5483,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
@@ -5677,13 +5727,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
@@ -5898,17 +5948,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>228</v>
+        <v>282</v>
       </c>
       <c r="F25" t="n">
         <v>10</v>
@@ -5923,17 +5973,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -5948,17 +5998,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -5973,20 +6023,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>258</v>
+        <v>108</v>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -6598,17 +6648,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -6623,17 +6673,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -6648,17 +6698,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6673,17 +6723,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -6698,17 +6748,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6723,17 +6773,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -6748,17 +6798,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>191</v>
+        <v>100</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
@@ -6773,17 +6823,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
@@ -6798,20 +6848,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -6823,20 +6873,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>9</v>
+      </c>
+      <c r="E62" t="n">
+        <v>201</v>
+      </c>
+      <c r="F62" t="n">
         <v>5</v>
-      </c>
-      <c r="D62" t="n">
-        <v>5</v>
-      </c>
-      <c r="E62" t="n">
-        <v>102</v>
-      </c>
-      <c r="F62" t="n">
-        <v>4</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -6848,17 +6898,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
@@ -6873,17 +6923,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -6898,17 +6948,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -6923,17 +6973,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E66" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -7023,17 +7073,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
@@ -7048,17 +7098,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="F71" t="n">
         <v>3</v>
@@ -7073,17 +7123,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E72" t="n">
-        <v>58</v>
+        <v>270</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
@@ -7098,20 +7148,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -7123,17 +7173,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -7148,14 +7198,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>24</v>
@@ -7173,14 +7223,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
         <v>24</v>
@@ -7198,17 +7248,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7223,17 +7273,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7248,17 +7298,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -7273,17 +7323,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -7298,17 +7348,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -7323,17 +7373,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -7348,17 +7398,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -7373,17 +7423,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -7398,17 +7448,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Yash Thakur</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -7423,20 +7473,20 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7448,17 +7498,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
         <v>1</v>
@@ -7473,17 +7523,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7498,17 +7548,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7523,17 +7573,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7548,17 +7598,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -7573,17 +7623,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -7598,17 +7648,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D93" t="n">
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -7623,17 +7673,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -7648,17 +7698,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -7673,22 +7723,72 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>12</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" t="n">
+        <v>36</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>Ben Dwarshuis</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
         <v>24</v>
       </c>
-      <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" t="n">
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>134</v>
+        <v>554</v>
       </c>
       <c r="F13" t="n">
-        <v>44.67</v>
+        <v>46.17</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>268</v>
+        <v>552</v>
       </c>
       <c r="F14" t="n">
-        <v>44.67</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>439</v>
+        <v>134</v>
       </c>
       <c r="F15" t="n">
-        <v>43.9</v>
+        <v>44.67</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>481</v>
+        <v>268</v>
       </c>
       <c r="F16" t="n">
-        <v>43.73</v>
+        <v>44.67</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>174</v>
+        <v>439</v>
       </c>
       <c r="F17" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -872,7 +872,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -882,10 +882,10 @@
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F18" t="n">
-        <v>43.36</v>
+        <v>43.73</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>467</v>
+        <v>174</v>
       </c>
       <c r="F19" t="n">
-        <v>42.45</v>
+        <v>43.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,13 +932,13 @@
         <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>296</v>
+        <v>477</v>
       </c>
       <c r="F20" t="n">
-        <v>42.29</v>
+        <v>43.36</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>501</v>
+        <v>296</v>
       </c>
       <c r="F21" t="n">
-        <v>41.75</v>
+        <v>42.29</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>41</v>
+        <v>422</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>41</v>
       </c>
       <c r="F23" t="n">
-        <v>40.33</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>440</v>
+        <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>40.33</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1047,23 +1047,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>197</v>
+        <v>321</v>
       </c>
       <c r="F25" t="n">
-        <v>39.4</v>
+        <v>40.12</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>440</v>
       </c>
       <c r="F26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>234</v>
+        <v>316</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>467</v>
+        <v>197</v>
       </c>
       <c r="F28" t="n">
-        <v>38.92</v>
+        <v>39.4</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>233</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n">
-        <v>38.83</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,13 +1182,13 @@
         <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="F30" t="n">
-        <v>38.71</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>38.92</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>114</v>
+        <v>233</v>
       </c>
       <c r="F32" t="n">
-        <v>38</v>
+        <v>38.83</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1257,13 +1257,13 @@
         <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>367</v>
+        <v>271</v>
       </c>
       <c r="F33" t="n">
-        <v>36.7</v>
+        <v>38.71</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>252</v>
+        <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="F35" t="n">
-        <v>35.8</v>
+        <v>38</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>367</v>
       </c>
       <c r="F36" t="n">
-        <v>35.5</v>
+        <v>36.7</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="F37" t="n">
-        <v>35.25</v>
+        <v>36</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>420</v>
+        <v>179</v>
       </c>
       <c r="F38" t="n">
-        <v>35</v>
+        <v>35.8</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="F39" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1422,20 +1422,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>315</v>
+        <v>141</v>
       </c>
       <c r="F40" t="n">
-        <v>35</v>
+        <v>35.25</v>
       </c>
       <c r="G40" t="n">
         <v>2</v>
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>244</v>
+        <v>420</v>
       </c>
       <c r="F41" t="n">
-        <v>34.86</v>
+        <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1472,20 +1472,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>340</v>
+        <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>34</v>
+        <v>315</v>
       </c>
       <c r="F43" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1532,13 +1532,13 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>169</v>
+        <v>244</v>
       </c>
       <c r="F44" t="n">
-        <v>33.8</v>
+        <v>34.86</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>337</v>
+        <v>412</v>
       </c>
       <c r="F45" t="n">
-        <v>33.7</v>
+        <v>34.33</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="F46" t="n">
-        <v>33.67</v>
+        <v>34</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>336</v>
+        <v>169</v>
       </c>
       <c r="F47" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>201</v>
+        <v>337</v>
       </c>
       <c r="F48" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>364</v>
+        <v>202</v>
       </c>
       <c r="F49" t="n">
-        <v>33.09</v>
+        <v>33.67</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="F50" t="n">
-        <v>33</v>
+        <v>33.6</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="F51" t="n">
-        <v>32.57</v>
+        <v>33.5</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F52" t="n">
-        <v>32.27</v>
+        <v>33.09</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E53" t="n">
-        <v>96</v>
+        <v>314</v>
       </c>
       <c r="F53" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="G53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F54" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>312</v>
+        <v>92</v>
       </c>
       <c r="F55" t="n">
-        <v>31.2</v>
+        <v>30.67</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -1822,11 +1822,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>5</v>
@@ -1847,20 +1847,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>92</v>
+        <v>306</v>
       </c>
       <c r="F57" t="n">
-        <v>30.67</v>
+        <v>30.6</v>
       </c>
       <c r="G57" t="n">
         <v>2</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1882,13 +1882,13 @@
         <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>306</v>
+        <v>361</v>
       </c>
       <c r="F58" t="n">
-        <v>30.6</v>
+        <v>30.08</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="F59" t="n">
-        <v>30.08</v>
+        <v>29</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="F60" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -1947,20 +1947,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C61" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" t="n">
         <v>11</v>
       </c>
-      <c r="D61" t="n">
-        <v>10</v>
-      </c>
       <c r="E61" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="F61" t="n">
-        <v>28</v>
+        <v>27.89</v>
       </c>
       <c r="G61" t="n">
         <v>2</v>
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F62" t="n">
-        <v>27.89</v>
+        <v>27.8</v>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="F63" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,20 +2022,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
         <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F64" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -2047,23 +2047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="F65" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2072,20 +2072,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>26</v>
+        <v>231</v>
       </c>
       <c r="F66" t="n">
-        <v>26</v>
+        <v>25.67</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E67" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="F67" t="n">
-        <v>25.67</v>
+        <v>25</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="F68" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" t="n">
+        <v>98</v>
+      </c>
+      <c r="F69" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G69" t="n">
         <v>7</v>
-      </c>
-      <c r="E69" t="n">
-        <v>123</v>
-      </c>
-      <c r="F69" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>237</v>
+        <v>116</v>
       </c>
       <c r="F70" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E71" t="n">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="F71" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -2222,23 +2222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F72" t="n">
         <v>23</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="F73" t="n">
-        <v>23</v>
+        <v>22.82</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
         <v>5</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="F79" t="n">
         <v>18.5</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="F80" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2463,7 +2463,7 @@
         <v>18</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F82" t="n">
         <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E83" t="n">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>17.73</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="F84" t="n">
-        <v>17.73</v>
+        <v>17.5</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,14 +2547,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
         <v>35</v>
@@ -2563,7 +2563,7 @@
         <v>17.5</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F86" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F87" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C88" t="n">
+        <v>9</v>
+      </c>
+      <c r="D88" t="n">
         <v>6</v>
       </c>
-      <c r="D88" t="n">
-        <v>5</v>
-      </c>
       <c r="E88" t="n">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F88" t="n">
-        <v>16.75</v>
+        <v>16.5</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
         <v>6</v>
       </c>
       <c r="E89" t="n">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F89" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="F90" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -2697,14 +2697,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>16</v>
@@ -2713,7 +2713,7 @@
         <v>16</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2722,11 +2722,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C93" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" t="n">
+        <v>76</v>
+      </c>
+      <c r="F93" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G93" t="n">
         <v>3</v>
-      </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" t="n">
-        <v>16</v>
-      </c>
-      <c r="F93" t="n">
-        <v>16</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2772,23 +2772,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2797,14 +2797,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Vishnu Vinod</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>15</v>
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vishnu Vinod</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F96" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2847,11 +2847,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
@@ -2872,20 +2872,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E98" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="F98" t="n">
-        <v>14.5</v>
+        <v>14.17</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="F99" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -2922,20 +2922,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="n">
         <v>4</v>
       </c>
-      <c r="D100" t="n">
-        <v>2</v>
-      </c>
       <c r="E100" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F100" t="n">
-        <v>14</v>
+        <v>13.33</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -2947,23 +2947,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E101" t="n">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F101" t="n">
-        <v>13.33</v>
+        <v>13.17</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2972,14 +2972,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E102" t="n">
         <v>79</v>
@@ -2988,7 +2988,7 @@
         <v>13.17</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -2997,20 +2997,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="F103" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="G103" t="n">
         <v>2</v>
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F104" t="n">
         <v>13</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F105" t="n">
         <v>13</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E106" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F106" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F107" t="n">
-        <v>12.75</v>
+        <v>12.67</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D131" t="n">
         <v>2</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D171" t="n">
         <v>0</v>
@@ -4722,11 +4722,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4747,14 +4747,14 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4847,14 +4847,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -4872,11 +4872,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D178" t="n">
         <v>0</v>
@@ -4897,11 +4897,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -4922,11 +4922,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -4947,14 +4947,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4997,11 +4997,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -5122,11 +5122,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -5147,11 +5147,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -5197,11 +5197,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -5222,14 +5222,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -5272,11 +5272,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -5297,22 +5297,47 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>1</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C195" t="n">
-        <v>12</v>
-      </c>
-      <c r="D195" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" t="n">
+      <c r="C196" t="n">
+        <v>12</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5327,7 +5352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5402,13 +5427,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="F3" t="n">
         <v>21</v>
@@ -5448,7 +5473,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5458,7 +5483,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
@@ -5473,17 +5498,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
@@ -5502,13 +5527,13 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
         <v>11</v>
       </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
       <c r="E7" t="n">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -5573,17 +5598,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
@@ -5598,17 +5623,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
@@ -5623,20 +5648,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -5648,17 +5673,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
@@ -5673,17 +5698,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>276</v>
+        <v>158</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
@@ -5698,17 +5723,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -5723,20 +5748,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5748,17 +5773,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>180</v>
+        <v>264</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
@@ -5773,20 +5798,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -5923,17 +5948,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>174</v>
+        <v>282</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
@@ -5948,17 +5973,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="F25" t="n">
         <v>10</v>
@@ -5973,17 +5998,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -6223,17 +6248,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -6248,17 +6273,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
         <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -6698,17 +6723,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>62</v>
+        <v>192</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6723,17 +6748,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -6823,17 +6848,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>191</v>
+        <v>102</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
@@ -6848,17 +6873,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="F61" t="n">
         <v>5</v>
@@ -6873,17 +6898,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E62" t="n">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="F62" t="n">
         <v>5</v>
@@ -6898,20 +6923,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>201</v>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -6923,17 +6948,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -6948,17 +6973,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -6973,17 +6998,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -6998,17 +7023,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E67" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F67" t="n">
         <v>4</v>
@@ -7552,7 +7577,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D89" t="n">
         <v>4</v>
@@ -7623,17 +7648,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -7648,17 +7673,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -7673,7 +7698,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -7683,7 +7708,7 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -7698,17 +7723,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -7723,17 +7748,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -7748,17 +7773,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -7773,22 +7798,72 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>12</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" t="n">
+        <v>36</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>Ben Dwarshuis</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
         <v>24</v>
       </c>
-      <c r="F98" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G196"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,23 +472,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Venkatesh Iyer</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>71.5</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>71.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>484</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>53.78</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,23 +597,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>508</v>
+        <v>542</v>
       </c>
       <c r="F7" t="n">
-        <v>50.8</v>
+        <v>54.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -622,7 +622,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -632,13 +632,13 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,20 +647,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>396</v>
+        <v>450</v>
       </c>
       <c r="F9" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F10" t="n">
-        <v>48.44</v>
+        <v>47.78</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>430</v>
+        <v>190</v>
       </c>
       <c r="F11" t="n">
-        <v>47.78</v>
+        <v>47.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>190</v>
+        <v>473</v>
       </c>
       <c r="F12" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -847,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="F17" t="n">
-        <v>43.9</v>
+        <v>44.42</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>481</v>
+        <v>397</v>
       </c>
       <c r="F18" t="n">
-        <v>43.73</v>
+        <v>44.11</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>174</v>
+        <v>481</v>
       </c>
       <c r="F19" t="n">
-        <v>43.5</v>
+        <v>43.73</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>477</v>
+        <v>296</v>
       </c>
       <c r="F20" t="n">
-        <v>43.36</v>
+        <v>42.29</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>296</v>
+        <v>422</v>
       </c>
       <c r="F21" t="n">
-        <v>42.29</v>
+        <v>42.2</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -972,7 +972,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -982,13 +982,13 @@
         <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>422</v>
+        <v>486</v>
       </c>
       <c r="F22" t="n">
-        <v>42.2</v>
+        <v>40.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Venkatesh Iyer</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40.33</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>121</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>40.33</v>
+        <v>40.12</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>321</v>
+        <v>441</v>
       </c>
       <c r="F25" t="n">
-        <v>40.12</v>
+        <v>40.09</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>440</v>
+        <v>316</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>316</v>
+        <v>197</v>
       </c>
       <c r="F27" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>467</v>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>38.92</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>234</v>
+        <v>412</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>37.45</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>467</v>
+        <v>262</v>
       </c>
       <c r="F31" t="n">
-        <v>38.92</v>
+        <v>37.43</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1222,20 +1222,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>233</v>
+        <v>149</v>
       </c>
       <c r="F32" t="n">
-        <v>38.83</v>
+        <v>37.25</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>271</v>
+        <v>183</v>
       </c>
       <c r="F33" t="n">
-        <v>38.71</v>
+        <v>36.6</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>38</v>
+        <v>216</v>
       </c>
       <c r="F34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1297,20 +1297,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="F35" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>367</v>
+        <v>141</v>
       </c>
       <c r="F36" t="n">
-        <v>36.7</v>
+        <v>35.25</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>252</v>
+        <v>420</v>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="F38" t="n">
-        <v>35.8</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="F39" t="n">
-        <v>35.5</v>
+        <v>34.86</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="F40" t="n">
-        <v>35.25</v>
+        <v>34.38</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F41" t="n">
-        <v>35</v>
+        <v>34.33</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F42" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43" t="n">
-        <v>315</v>
+        <v>169</v>
       </c>
       <c r="F43" t="n">
-        <v>35</v>
+        <v>33.8</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E44" t="n">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="F44" t="n">
-        <v>34.86</v>
+        <v>33.7</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>412</v>
+        <v>202</v>
       </c>
       <c r="F45" t="n">
-        <v>34.33</v>
+        <v>33.67</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>34</v>
+        <v>336</v>
       </c>
       <c r="F46" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="F47" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1622,20 +1622,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E48" t="n">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="F48" t="n">
-        <v>33.7</v>
+        <v>33.36</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -1647,23 +1647,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="F49" t="n">
-        <v>33.67</v>
+        <v>33.29</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1682,10 +1682,10 @@
         <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="F50" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -1697,23 +1697,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>201</v>
+        <v>312</v>
       </c>
       <c r="F51" t="n">
-        <v>33.5</v>
+        <v>31.2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -1722,23 +1722,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E52" t="n">
-        <v>364</v>
+        <v>92</v>
       </c>
       <c r="F52" t="n">
-        <v>33.09</v>
+        <v>30.67</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1747,23 +1747,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>314</v>
+        <v>92</v>
       </c>
       <c r="F53" t="n">
-        <v>31.4</v>
+        <v>30.67</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>312</v>
+        <v>153</v>
       </c>
       <c r="F54" t="n">
-        <v>31.2</v>
+        <v>30.6</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
@@ -1797,20 +1797,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>92</v>
+        <v>306</v>
       </c>
       <c r="F55" t="n">
-        <v>30.67</v>
+        <v>30.6</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E56" t="n">
-        <v>92</v>
+        <v>364</v>
       </c>
       <c r="F56" t="n">
-        <v>30.67</v>
+        <v>30.33</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1857,13 +1857,13 @@
         <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>306</v>
+        <v>361</v>
       </c>
       <c r="F57" t="n">
-        <v>30.6</v>
+        <v>30.08</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="F58" t="n">
-        <v>30.08</v>
+        <v>29</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="F59" t="n">
-        <v>29</v>
+        <v>28.67</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D66" t="n">
         <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="F66" t="n">
-        <v>25.67</v>
+        <v>25.8</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E67" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F67" t="n">
-        <v>25</v>
+        <v>25.67</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2122,20 +2122,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="F68" t="n">
-        <v>24.6</v>
+        <v>25.33</v>
       </c>
       <c r="G68" t="n">
         <v>2</v>
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E69" t="n">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="F69" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E70" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F70" t="n">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E71" t="n">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="F71" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F72" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="F73" t="n">
-        <v>22.82</v>
+        <v>23</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E74" t="n">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="F74" t="n">
-        <v>21.5</v>
+        <v>22.82</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F75" t="n">
-        <v>20.86</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E76" t="n">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="F76" t="n">
-        <v>20.75</v>
+        <v>21.5</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2347,20 +2347,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E77" t="n">
-        <v>216</v>
+        <v>146</v>
       </c>
       <c r="F77" t="n">
-        <v>19.64</v>
+        <v>20.86</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="n">
         <v>7</v>
       </c>
-      <c r="D78" t="n">
-        <v>5</v>
-      </c>
       <c r="E78" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F78" t="n">
-        <v>19.33</v>
+        <v>20.75</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="F79" t="n">
-        <v>18.5</v>
+        <v>19.64</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F80" t="n">
-        <v>18</v>
+        <v>19.33</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="F81" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F82" t="n">
         <v>18</v>
@@ -2497,23 +2497,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>195</v>
+        <v>18</v>
       </c>
       <c r="F83" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2532,10 +2532,10 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F84" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2547,23 +2547,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D85" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E85" t="n">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="F85" t="n">
-        <v>17.5</v>
+        <v>17.73</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F86" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F87" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="F88" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -2647,20 +2647,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F89" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E90" t="n">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="F91" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>16</v>
@@ -2738,7 +2738,7 @@
         <v>16</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="F93" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="F98" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -2897,23 +2897,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E99" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F99" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D104" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F104" t="n">
         <v>13</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E105" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F105" t="n">
         <v>13</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -3072,23 +3072,23 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F106" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -3097,23 +3097,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F107" t="n">
-        <v>12.67</v>
+        <v>12.75</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -3122,23 +3122,23 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E108" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F108" t="n">
-        <v>12.5</v>
+        <v>12.67</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D113" t="n">
         <v>10</v>
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F119" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3422,11 +3422,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D120" t="n">
         <v>2</v>
@@ -3438,7 +3438,7 @@
         <v>7</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F121" t="n">
         <v>7</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E122" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F122" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -3497,20 +3497,20 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D123" t="n">
         <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F123" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3522,14 +3522,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E124" t="n">
         <v>13</v>
@@ -3538,7 +3538,7 @@
         <v>6.5</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F125" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3747,11 +3747,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -3763,7 +3763,7 @@
         <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F134" t="n">
         <v>5</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3797,20 +3797,20 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -3822,23 +3822,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F136" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -3847,20 +3847,20 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Ravi Singh</t>
         </is>
       </c>
       <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
         <v>4</v>
       </c>
-      <c r="D137" t="n">
-        <v>3</v>
-      </c>
-      <c r="E137" t="n">
-        <v>10</v>
-      </c>
       <c r="F137" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -3872,23 +3872,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -3897,23 +3897,23 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C139" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" t="n">
         <v>10</v>
       </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="n">
-        <v>3</v>
-      </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -3922,17 +3922,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E140" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F140" t="n">
         <v>3</v>
@@ -3947,14 +3947,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>3</v>
@@ -3963,7 +3963,7 @@
         <v>3</v>
       </c>
       <c r="G141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -3972,23 +3972,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D142" t="n">
         <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -3997,20 +3997,20 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D143" t="n">
         <v>2</v>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G143" t="n">
         <v>2</v>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -4038,7 +4038,7 @@
         <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4047,11 +4047,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D145" t="n">
         <v>2</v>
@@ -4072,23 +4072,23 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
         <v>2</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D147" t="n">
         <v>2</v>
@@ -4122,23 +4122,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C148" t="n">
         <v>12</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -4147,23 +4147,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -4172,23 +4172,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4263,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4272,20 +4272,20 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4297,23 +4297,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -4322,23 +4322,23 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Akash Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4572,11 +4572,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D168" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -4722,11 +4722,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4772,14 +4772,14 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="C174" t="n">
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -4797,14 +4797,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -4822,11 +4822,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -4897,14 +4897,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -4922,11 +4922,11 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -4947,11 +4947,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -4972,14 +4972,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -4997,11 +4997,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -5047,11 +5047,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
         <v>0</v>
@@ -5122,14 +5122,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -5147,11 +5147,11 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D189" t="n">
         <v>0</v>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -5197,11 +5197,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -5222,11 +5222,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -5272,11 +5272,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Tripurana Vijay</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -5322,22 +5322,97 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
+          <t>Varun Chakravarthy</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>9</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>4</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C196" t="n">
-        <v>12</v>
-      </c>
-      <c r="D196" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
+      <c r="C199" t="n">
+        <v>13</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5352,7 +5427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5402,16 +5477,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -5473,7 +5548,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5483,10 +5558,10 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5498,17 +5573,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F6" t="n">
         <v>16</v>
@@ -5523,17 +5598,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -5548,17 +5623,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
@@ -5573,20 +5648,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5648,17 +5723,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
@@ -5673,20 +5748,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -5698,17 +5773,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>158</v>
+        <v>258</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
@@ -5723,17 +5798,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>276</v>
+        <v>158</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -5798,17 +5873,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="F18" t="n">
         <v>12</v>
@@ -5823,20 +5898,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -5848,7 +5923,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5858,10 +5933,10 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -5873,17 +5948,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
@@ -5898,23 +5973,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>120</v>
+        <v>185</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5923,20 +5998,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>228</v>
+      </c>
+      <c r="F23" t="n">
         <v>11</v>
-      </c>
-      <c r="E23" t="n">
-        <v>216</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -5948,23 +6023,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>282</v>
+        <v>120</v>
       </c>
       <c r="F24" t="n">
         <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -5973,17 +6048,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="F25" t="n">
         <v>10</v>
@@ -5998,17 +6073,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -6023,17 +6098,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>114</v>
+        <v>282</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -6048,17 +6123,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>108</v>
+        <v>246</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
@@ -6073,20 +6148,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
+        <v>9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>198</v>
+      </c>
+      <c r="F29" t="n">
         <v>10</v>
-      </c>
-      <c r="E29" t="n">
-        <v>204</v>
-      </c>
-      <c r="F29" t="n">
-        <v>9</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -6098,20 +6173,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -6123,20 +6198,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6148,20 +6223,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>108</v>
+      </c>
+      <c r="F32" t="n">
         <v>10</v>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="n">
-        <v>195</v>
-      </c>
-      <c r="F32" t="n">
-        <v>9</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6173,17 +6248,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="F33" t="n">
         <v>9</v>
@@ -6198,20 +6273,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>114</v>
+      </c>
+      <c r="F34" t="n">
         <v>9</v>
-      </c>
-      <c r="E34" t="n">
-        <v>156</v>
-      </c>
-      <c r="F34" t="n">
-        <v>8</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -6223,20 +6298,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>168</v>
+      </c>
+      <c r="F35" t="n">
         <v>9</v>
-      </c>
-      <c r="E35" t="n">
-        <v>202</v>
-      </c>
-      <c r="F35" t="n">
-        <v>8</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -6248,17 +6323,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>192</v>
+        <v>156</v>
       </c>
       <c r="F36" t="n">
         <v>8</v>
@@ -6273,17 +6348,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -6298,17 +6373,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -6323,17 +6398,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -6348,20 +6423,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -6373,20 +6448,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -6398,17 +6473,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="F42" t="n">
         <v>7</v>
@@ -6423,17 +6498,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
         <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="F43" t="n">
         <v>7</v>
@@ -6448,17 +6523,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="n">
         <v>11</v>
       </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
       <c r="E44" t="n">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="F44" t="n">
         <v>7</v>
@@ -6473,20 +6548,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E45" t="n">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -6498,20 +6573,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -6523,17 +6598,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="F47" t="n">
         <v>6</v>
@@ -6548,17 +6623,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F48" t="n">
         <v>6</v>
@@ -6573,17 +6648,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F49" t="n">
         <v>6</v>
@@ -6598,17 +6673,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -6623,17 +6698,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
         <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -6648,20 +6723,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -6673,14 +6748,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>120</v>
@@ -6698,17 +6773,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -6723,17 +6798,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -6748,17 +6823,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>68</v>
+        <v>192</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -6773,17 +6848,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
         <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6952,13 +7027,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E64" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F64" t="n">
         <v>4</v>
@@ -6973,17 +7048,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -6998,17 +7073,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E66" t="n">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -7023,17 +7098,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F67" t="n">
         <v>4</v>
@@ -7048,17 +7123,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E68" t="n">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="F68" t="n">
         <v>4</v>
@@ -7073,17 +7148,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F69" t="n">
         <v>4</v>
@@ -7098,20 +7173,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Akash Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E70" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -7123,17 +7198,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
         <v>3</v>
@@ -7148,17 +7223,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>270</v>
+        <v>42</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
@@ -7173,17 +7248,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>58</v>
+        <v>270</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
@@ -7198,20 +7273,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -7223,17 +7298,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F75" t="n">
         <v>2</v>
@@ -7248,17 +7323,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" t="n">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -7273,17 +7348,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7298,17 +7373,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>11</v>
+      </c>
+      <c r="D78" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="n">
-        <v>3</v>
-      </c>
       <c r="E78" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7323,17 +7398,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -7348,17 +7423,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -7373,17 +7448,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -7398,17 +7473,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -7423,17 +7498,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -7448,17 +7523,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -7473,17 +7548,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -7498,17 +7573,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Yash Thakur</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -7523,20 +7598,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7548,17 +7623,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F88" t="n">
         <v>1</v>
@@ -7573,17 +7648,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7598,17 +7673,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7623,17 +7698,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -7648,17 +7723,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -7673,17 +7748,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -7698,17 +7773,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -7723,17 +7798,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -7748,7 +7823,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -7758,7 +7833,7 @@
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F96" t="n">
         <v>1</v>
@@ -7773,17 +7848,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F97" t="n">
         <v>1</v>
@@ -7798,17 +7873,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
@@ -7864,6 +7939,56 @@
         <v>1</v>
       </c>
       <c r="G100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>66</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Donavon Ferreira</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>11</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" t="n">
+        <v>18</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
         <v>0</v>
       </c>
     </row>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -497,23 +497,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Rinku Singh</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>286</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G3" t="n">
         <v>5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F3" t="n">
-        <v>79</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -522,23 +522,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rinku Singh</t>
+          <t>Quinton de Kock</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>286</v>
+        <v>132</v>
       </c>
       <c r="F4" t="n">
-        <v>71.5</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -547,23 +547,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quinton de Kock</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>58</v>
+        <v>542</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>54.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -607,13 +607,13 @@
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="F7" t="n">
-        <v>54.2</v>
+        <v>50.45</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>508</v>
+        <v>430</v>
       </c>
       <c r="F8" t="n">
-        <v>50.8</v>
+        <v>47.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -651,16 +651,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>47.7</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>430</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>47.78</v>
+        <v>47.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>190</v>
+        <v>473</v>
       </c>
       <c r="F11" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>473</v>
+        <v>554</v>
       </c>
       <c r="F12" t="n">
-        <v>47.3</v>
+        <v>46.17</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F13" t="n">
-        <v>46.17</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>552</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>481</v>
+        <v>296</v>
       </c>
       <c r="F19" t="n">
-        <v>43.73</v>
+        <v>42.29</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>296</v>
+        <v>507</v>
       </c>
       <c r="F20" t="n">
-        <v>42.29</v>
+        <v>42.25</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="F27" t="n">
-        <v>39.4</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>467</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>38.92</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1147,20 +1147,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="F29" t="n">
-        <v>38.92</v>
+        <v>37.69</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="F33" t="n">
-        <v>36.6</v>
+        <v>37.17</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
         <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="F34" t="n">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="F35" t="n">
         <v>36</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1322,20 +1322,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="F36" t="n">
-        <v>35.25</v>
+        <v>36</v>
       </c>
       <c r="G36" t="n">
         <v>2</v>
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>420</v>
+        <v>141</v>
       </c>
       <c r="F37" t="n">
-        <v>35</v>
+        <v>35.25</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="F39" t="n">
-        <v>34.86</v>
+        <v>34.5</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1807,13 +1807,13 @@
         <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="F55" t="n">
-        <v>30.6</v>
+        <v>30.33</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1822,23 +1822,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="F56" t="n">
-        <v>30.33</v>
+        <v>29.18</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="F57" t="n">
-        <v>30.08</v>
+        <v>29</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="F58" t="n">
-        <v>29</v>
+        <v>28.67</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E59" t="n">
-        <v>86</v>
+        <v>367</v>
       </c>
       <c r="F59" t="n">
-        <v>28.67</v>
+        <v>28.23</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1922,20 +1922,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" t="n">
         <v>11</v>
       </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
       <c r="E60" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="F60" t="n">
-        <v>28</v>
+        <v>27.89</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="F61" t="n">
-        <v>27.89</v>
+        <v>27.8</v>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>10</v>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>278</v>
+        <v>136</v>
       </c>
       <c r="F62" t="n">
-        <v>27.8</v>
+        <v>27.2</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E63" t="n">
-        <v>136</v>
+        <v>235</v>
       </c>
       <c r="F63" t="n">
-        <v>27.2</v>
+        <v>26.11</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2222,20 +2222,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="F72" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>161</v>
+        <v>251</v>
       </c>
       <c r="F73" t="n">
-        <v>23</v>
+        <v>22.82</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E74" t="n">
-        <v>251</v>
+        <v>132</v>
       </c>
       <c r="F74" t="n">
-        <v>22.82</v>
+        <v>22</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E75" t="n">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="F75" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2322,17 +2322,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="F76" t="n">
         <v>21.5</v>
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E79" t="n">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="F79" t="n">
-        <v>19.64</v>
+        <v>20.43</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="F80" t="n">
-        <v>19.33</v>
+        <v>20.17</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="F81" t="n">
-        <v>18.5</v>
+        <v>19.64</v>
       </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F82" t="n">
-        <v>18</v>
+        <v>19.33</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -2497,11 +2497,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
@@ -2513,7 +2513,7 @@
         <v>18</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F84" t="n">
         <v>18</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="F85" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>195</v>
       </c>
       <c r="F86" t="n">
-        <v>17.5</v>
+        <v>17.73</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F87" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="F88" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E89" t="n">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F89" t="n">
         <v>16.75</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="F90" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
@@ -3322,20 +3322,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E116" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
@@ -3347,14 +3347,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>8</v>
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F118" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -3397,20 +3397,20 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F119" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E120" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F120" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
@@ -3463,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>12</v>
       </c>
       <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="n">
         <v>7</v>
-      </c>
-      <c r="E122" t="n">
-        <v>21</v>
       </c>
       <c r="F122" t="n">
         <v>7</v>
       </c>
       <c r="G122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E123" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F123" t="n">
         <v>7</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>8</v>
       </c>
       <c r="D124" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F124" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E125" t="n">
         <v>13</v>
@@ -3563,7 +3563,7 @@
         <v>6.5</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D132" t="n">
         <v>5</v>
@@ -3747,14 +3747,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133" t="n">
         <v>5</v>
@@ -3763,7 +3763,7 @@
         <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -3772,11 +3772,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134" t="n">
         <v>1</v>
@@ -3788,7 +3788,7 @@
         <v>5</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F135" t="n">
         <v>5</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -3822,20 +3822,20 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F136" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ravi Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
@@ -3863,7 +3863,7 @@
         <v>4</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -3872,20 +3872,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ravi Singh</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F138" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -3897,20 +3897,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F139" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -3922,23 +3922,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E140" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E141" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F141" t="n">
         <v>3</v>
@@ -3972,14 +3972,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>3</v>
@@ -3997,11 +3997,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
         <v>2</v>
@@ -4013,7 +4013,7 @@
         <v>3</v>
       </c>
       <c r="G143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -4022,23 +4022,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -4063,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D148" t="n">
         <v>2</v>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -5527,16 +5527,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5573,20 +5573,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -5623,17 +5623,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
@@ -5648,17 +5648,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -5723,17 +5723,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>300</v>
+        <v>204</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
@@ -5748,17 +5748,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
@@ -5773,20 +5773,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5798,17 +5798,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>158</v>
+        <v>258</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -5823,17 +5823,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
@@ -5852,16 +5852,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -5873,20 +5873,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -5898,17 +5898,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="F19" t="n">
         <v>12</v>
@@ -6023,23 +6023,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6048,23 +6048,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F25" t="n">
         <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -6073,17 +6073,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F26" t="n">
         <v>10</v>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -6123,17 +6123,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
         <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>246</v>
+        <v>282</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
@@ -6148,17 +6148,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
@@ -6173,17 +6173,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="F30" t="n">
         <v>10</v>
@@ -6198,17 +6198,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
@@ -6348,17 +6348,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
-        <v>227</v>
+        <v>148</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -6373,17 +6373,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -6423,17 +6423,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="F40" t="n">
         <v>8</v>
@@ -6448,17 +6448,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
@@ -6473,20 +6473,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -6498,20 +6498,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -6523,17 +6523,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>260</v>
+        <v>144</v>
       </c>
       <c r="F44" t="n">
         <v>7</v>
@@ -6548,17 +6548,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C45" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" t="n">
         <v>11</v>
       </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
       <c r="E45" t="n">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="F45" t="n">
         <v>7</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" t="n">
-        <v>126</v>
+        <v>198</v>
       </c>
       <c r="F46" t="n">
         <v>7</v>
@@ -6598,20 +6598,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E47" t="n">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -6623,20 +6623,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="F49" t="n">
         <v>6</v>
@@ -6673,17 +6673,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
@@ -6748,20 +6748,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E53" t="n">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -6773,20 +6773,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>96</v>
+      </c>
+      <c r="F54" t="n">
         <v>6</v>
-      </c>
-      <c r="D54" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>120</v>
-      </c>
-      <c r="F54" t="n">
-        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -7773,17 +7773,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -7798,17 +7798,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -7877,13 +7877,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>430</v>
+        <v>194</v>
       </c>
       <c r="F8" t="n">
-        <v>47.78</v>
+        <v>48.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>477</v>
+        <v>430</v>
       </c>
       <c r="F9" t="n">
-        <v>47.7</v>
+        <v>47.78</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>190</v>
+        <v>477</v>
       </c>
       <c r="F10" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>473</v>
+        <v>190</v>
       </c>
       <c r="F11" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>554</v>
+        <v>473</v>
       </c>
       <c r="F12" t="n">
-        <v>46.17</v>
+        <v>47.3</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>46.17</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>552</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>134</v>
-      </c>
-      <c r="F15" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -847,7 +847,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -857,13 +857,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>533</v>
+        <v>579</v>
       </c>
       <c r="F17" t="n">
-        <v>44.42</v>
+        <v>44.54</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,23 +872,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>397</v>
+        <v>533</v>
       </c>
       <c r="F18" t="n">
-        <v>44.11</v>
+        <v>44.42</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -897,7 +897,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -907,13 +907,13 @@
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>296</v>
+        <v>397</v>
       </c>
       <c r="F19" t="n">
-        <v>42.29</v>
+        <v>44.11</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -922,7 +922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -932,13 +932,13 @@
         <v>13</v>
       </c>
       <c r="E20" t="n">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="F20" t="n">
-        <v>42.25</v>
+        <v>43.31</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
         <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>422</v>
+        <v>296</v>
       </c>
       <c r="F21" t="n">
-        <v>42.2</v>
+        <v>42.29</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="F22" t="n">
-        <v>40.5</v>
+        <v>42.25</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>121</v>
+        <v>422</v>
       </c>
       <c r="F23" t="n">
-        <v>40.33</v>
+        <v>42.2</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1022,23 +1022,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>40.12</v>
+        <v>40.33</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>441</v>
+        <v>321</v>
       </c>
       <c r="F25" t="n">
-        <v>40.09</v>
+        <v>40.12</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>316</v>
+        <v>441</v>
       </c>
       <c r="F26" t="n">
-        <v>39.5</v>
+        <v>40.09</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1097,23 +1097,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>316</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>39.5</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>467</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>38.92</v>
+        <v>39</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1157,13 +1157,13 @@
         <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="F29" t="n">
-        <v>37.69</v>
+        <v>38.18</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1172,23 +1172,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>412</v>
+        <v>490</v>
       </c>
       <c r="F30" t="n">
-        <v>37.45</v>
+        <v>37.69</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1207,13 +1207,13 @@
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>262</v>
+        <v>412</v>
       </c>
       <c r="F31" t="n">
-        <v>37.43</v>
+        <v>37.45</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="F32" t="n">
-        <v>37.25</v>
+        <v>37.43</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="F33" t="n">
-        <v>37.17</v>
+        <v>37.25</v>
       </c>
       <c r="G33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="F34" t="n">
-        <v>36.6</v>
+        <v>37.17</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="F35" t="n">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="F36" t="n">
         <v>36</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="F37" t="n">
-        <v>35.25</v>
+        <v>36</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
@@ -1372,23 +1372,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="F38" t="n">
-        <v>35</v>
+        <v>35.57</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="F39" t="n">
-        <v>34.5</v>
+        <v>35.25</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>13</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>275</v>
+        <v>35</v>
       </c>
       <c r="F40" t="n">
-        <v>34.38</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>412</v>
+        <v>276</v>
       </c>
       <c r="F41" t="n">
-        <v>34.33</v>
+        <v>34.5</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1472,20 +1472,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>34.38</v>
       </c>
       <c r="G42" t="n">
         <v>4</v>
@@ -1497,23 +1497,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
-        <v>169</v>
+        <v>412</v>
       </c>
       <c r="F43" t="n">
-        <v>33.8</v>
+        <v>34.33</v>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="F44" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1547,23 +1547,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="F45" t="n">
-        <v>33.67</v>
+        <v>33.8</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F46" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ayush Mhatre</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1607,10 +1607,10 @@
         <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F47" t="n">
-        <v>33.5</v>
+        <v>33.67</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F48" t="n">
-        <v>33.36</v>
+        <v>33.64</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E49" t="n">
-        <v>233</v>
+        <v>336</v>
       </c>
       <c r="F49" t="n">
-        <v>33.29</v>
+        <v>33.6</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -1672,23 +1672,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Ayush Mhatre</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
-        <v>327</v>
+        <v>201</v>
       </c>
       <c r="F50" t="n">
-        <v>32.7</v>
+        <v>33.5</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1897,23 +1897,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travis Head</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>13</v>
       </c>
       <c r="D59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" t="n">
-        <v>367</v>
+        <v>286</v>
       </c>
       <c r="F59" t="n">
-        <v>28.23</v>
+        <v>28.6</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1922,23 +1922,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Travis Head</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D60" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E60" t="n">
-        <v>251</v>
+        <v>367</v>
       </c>
       <c r="F60" t="n">
-        <v>27.89</v>
+        <v>28.23</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
         <v>5</v>
@@ -2297,17 +2297,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="F75" t="n">
         <v>21.5</v>
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E76" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F76" t="n">
-        <v>21.5</v>
+        <v>20.86</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2347,23 +2347,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="F77" t="n">
-        <v>20.86</v>
+        <v>20.75</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D78" t="n">
         <v>7</v>
       </c>
       <c r="E78" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="F78" t="n">
-        <v>20.75</v>
+        <v>20.43</v>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C79" t="n">
+        <v>12</v>
+      </c>
+      <c r="D79" t="n">
         <v>10</v>
       </c>
-      <c r="D79" t="n">
-        <v>7</v>
-      </c>
       <c r="E79" t="n">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="F79" t="n">
-        <v>20.43</v>
+        <v>20.17</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="F80" t="n">
-        <v>20.17</v>
+        <v>19.33</v>
       </c>
       <c r="G80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2451,16 +2451,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E81" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="F81" t="n">
-        <v>19.64</v>
+        <v>19.33</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E82" t="n">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="F82" t="n">
-        <v>19.33</v>
+        <v>19.11</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E101" t="n">
         <v>79</v>
@@ -2963,7 +2963,7 @@
         <v>13.17</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="n">
         <v>2</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D123" t="n">
         <v>7</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
         <v>2</v>
@@ -3922,20 +3922,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F140" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -3947,23 +3947,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E141" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -3972,17 +3972,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E142" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F142" t="n">
         <v>3</v>
@@ -3997,14 +3997,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
@@ -4022,11 +4022,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D144" t="n">
         <v>2</v>
@@ -4038,7 +4038,7 @@
         <v>3</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -4047,23 +4047,23 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -4072,14 +4072,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -4088,7 +4088,7 @@
         <v>2</v>
       </c>
       <c r="G146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -4097,11 +4097,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D147" t="n">
         <v>2</v>
@@ -4122,11 +4122,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D148" t="n">
         <v>2</v>
@@ -4147,23 +4147,23 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F149" t="n">
         <v>2</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -4172,23 +4172,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F150" t="n">
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -4222,14 +4222,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4263,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -4272,23 +4272,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -4297,23 +4297,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
@@ -4338,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -4347,23 +4347,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -4372,11 +4372,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Akash Singh</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D159" t="n">
         <v>0</v>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C161" t="n">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,11 +4497,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4538,7 +4538,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -4572,11 +4572,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4597,14 +4597,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -4622,14 +4622,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -4647,14 +4647,14 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -5272,11 +5272,11 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sushant Mishra</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tripurana Vijay</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -5322,14 +5322,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Tripurana Vijay</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -5372,11 +5372,11 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D198" t="n">
         <v>0</v>
@@ -5397,22 +5397,47 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C199" t="n">
-        <v>13</v>
-      </c>
-      <c r="D199" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
+      <c r="C200" t="n">
+        <v>13</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5552,16 +5577,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5602,13 +5627,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
@@ -5948,23 +5973,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -5973,7 +5998,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5983,7 +6008,7 @@
         <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
@@ -5998,17 +6023,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -6023,17 +6048,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
@@ -6048,23 +6073,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6648,17 +6673,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F49" t="n">
         <v>6</v>
@@ -6673,17 +6698,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -6698,17 +6723,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -6723,17 +6748,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
@@ -6748,17 +6773,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="F53" t="n">
         <v>6</v>
@@ -6773,17 +6798,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="F54" t="n">
         <v>6</v>
@@ -6798,7 +6823,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6808,10 +6833,10 @@
         <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -6823,17 +6848,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>192</v>
+        <v>84</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -6848,17 +6873,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6873,17 +6898,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -6898,17 +6923,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
@@ -6973,17 +6998,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="F62" t="n">
         <v>5</v>
@@ -7023,20 +7048,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -7148,17 +7173,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F69" t="n">
         <v>4</v>
@@ -7173,17 +7198,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E70" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F70" t="n">
         <v>4</v>
@@ -7198,20 +7223,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Akash Singh</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -7802,13 +7827,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
@@ -7977,7 +8002,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D102" t="n">
         <v>3</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>430</v>
+        <v>477</v>
       </c>
       <c r="F9" t="n">
-        <v>47.78</v>
+        <v>47.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>477</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>190</v>
+        <v>473</v>
       </c>
       <c r="F11" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>473</v>
+        <v>554</v>
       </c>
       <c r="F12" t="n">
-        <v>47.3</v>
+        <v>46.17</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -747,23 +747,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F13" t="n">
-        <v>46.17</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>552</v>
+        <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -797,23 +797,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>90</v>
+        <v>579</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>44.54</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -822,20 +822,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>268</v>
+        <v>533</v>
       </c>
       <c r="F16" t="n">
-        <v>44.67</v>
+        <v>44.42</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>579</v>
+        <v>397</v>
       </c>
       <c r="F17" t="n">
-        <v>44.54</v>
+        <v>44.11</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>533</v>
+        <v>436</v>
       </c>
       <c r="F18" t="n">
-        <v>44.42</v>
+        <v>43.6</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>397</v>
+        <v>563</v>
       </c>
       <c r="F19" t="n">
-        <v>44.11</v>
+        <v>43.31</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>563</v>
+        <v>296</v>
       </c>
       <c r="F20" t="n">
-        <v>43.31</v>
+        <v>42.29</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>296</v>
+        <v>507</v>
       </c>
       <c r="F21" t="n">
-        <v>42.29</v>
+        <v>42.25</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>507</v>
+        <v>422</v>
       </c>
       <c r="F22" t="n">
-        <v>42.25</v>
+        <v>42.2</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -997,23 +997,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>422</v>
+        <v>283</v>
       </c>
       <c r="F23" t="n">
-        <v>42.2</v>
+        <v>40.43</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
         <v>12</v>
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bhuvneshwar Kumar</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>13</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E44" t="n">
-        <v>34</v>
+        <v>343</v>
       </c>
       <c r="F44" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -1547,20 +1547,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mukul Choudhary</t>
+          <t>Bhuvneshwar Kumar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="F45" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="G45" t="n">
         <v>4</v>
@@ -1572,23 +1572,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rajat Patidar</t>
+          <t>Mukul Choudhary</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>337</v>
+        <v>169</v>
       </c>
       <c r="F46" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1597,23 +1597,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Rajat Patidar</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>202</v>
+        <v>337</v>
       </c>
       <c r="F47" t="n">
-        <v>33.67</v>
+        <v>33.7</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -1622,23 +1622,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yashasvi Jaiswal</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>370</v>
+        <v>202</v>
       </c>
       <c r="F48" t="n">
-        <v>33.64</v>
+        <v>33.67</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1647,20 +1647,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Yashasvi Jaiswal</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49" t="n">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="F49" t="n">
-        <v>33.6</v>
+        <v>33.64</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>312</v>
+        <v>92</v>
       </c>
       <c r="F51" t="n">
-        <v>31.2</v>
+        <v>30.67</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="F53" t="n">
-        <v>30.67</v>
+        <v>30.6</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>153</v>
+        <v>364</v>
       </c>
       <c r="F54" t="n">
-        <v>30.6</v>
+        <v>30.33</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E55" t="n">
-        <v>364</v>
+        <v>321</v>
       </c>
       <c r="F55" t="n">
-        <v>30.33</v>
+        <v>29.18</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -1822,20 +1822,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Xavier Bartlett</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="F56" t="n">
-        <v>29.18</v>
+        <v>29</v>
       </c>
       <c r="G56" t="n">
         <v>2</v>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Xavier Bartlett</t>
+          <t>Abishek Porel</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
         <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="F57" t="n">
-        <v>29</v>
+        <v>28.67</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1872,23 +1872,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abishek Porel</t>
+          <t>Rishabh Pant</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>86</v>
+        <v>286</v>
       </c>
       <c r="F58" t="n">
-        <v>28.67</v>
+        <v>28.6</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -1897,20 +1897,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rishabh Pant</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>13</v>
       </c>
       <c r="D59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E59" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="F59" t="n">
-        <v>28.6</v>
+        <v>28.36</v>
       </c>
       <c r="G59" t="n">
         <v>2</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D73" t="n">
         <v>12</v>
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="F75" t="n">
-        <v>21.5</v>
+        <v>21.86</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="F76" t="n">
-        <v>20.86</v>
+        <v>21.5</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="F86" t="n">
-        <v>17.73</v>
+        <v>17.5</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E87" t="n">
-        <v>35</v>
+        <v>210</v>
       </c>
       <c r="F87" t="n">
         <v>17.5</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
         <v>2</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D100" t="n">
         <v>4</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D103" t="n">
         <v>5</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D122" t="n">
         <v>2</v>
@@ -3701,7 +3701,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D131" t="n">
         <v>2</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D185" t="n">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D197" t="n">
         <v>1</v>
@@ -5677,13 +5677,13 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
-        <v>11</v>
-      </c>
       <c r="E9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="n">
         <v>9</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
         <v>4</v>
@@ -6648,17 +6648,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Romario Shepherd</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F48" t="n">
         <v>7</v>
@@ -6673,20 +6673,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Romario Shepherd</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -6698,17 +6698,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F50" t="n">
         <v>6</v>
@@ -6723,17 +6723,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F51" t="n">
         <v>6</v>
@@ -6748,17 +6748,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="F52" t="n">
         <v>6</v>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F53" t="n">
         <v>6</v>
@@ -6798,17 +6798,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="F54" t="n">
         <v>6</v>
@@ -6823,17 +6823,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="F55" t="n">
         <v>6</v>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6858,10 +6858,10 @@
         <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -6873,17 +6873,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -6898,17 +6898,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E58" t="n">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -6923,17 +6923,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
@@ -6948,17 +6948,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D70" t="n">
         <v>8</v>
@@ -7248,17 +7248,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
         <v>3</v>
       </c>
       <c r="E72" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
@@ -7273,17 +7273,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>270</v>
+        <v>42</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
@@ -7298,17 +7298,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E74" t="n">
-        <v>58</v>
+        <v>270</v>
       </c>
       <c r="F74" t="n">
         <v>3</v>
@@ -7323,20 +7323,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -7348,17 +7348,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="F76" t="n">
         <v>2</v>
@@ -7373,17 +7373,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="F77" t="n">
         <v>2</v>
@@ -7398,17 +7398,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -7423,17 +7423,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C79" t="n">
+        <v>11</v>
+      </c>
+      <c r="D79" t="n">
         <v>4</v>
       </c>
-      <c r="D79" t="n">
-        <v>3</v>
-      </c>
       <c r="E79" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
         <v>2</v>
@@ -7448,17 +7448,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -7473,17 +7473,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -7498,17 +7498,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -7523,17 +7523,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E83" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -7548,17 +7548,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E84" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -7573,17 +7573,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -7598,17 +7598,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -7623,17 +7623,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Yash Thakur</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -7648,20 +7648,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7673,17 +7673,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
@@ -7698,17 +7698,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7723,17 +7723,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -7748,17 +7748,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -7773,17 +7773,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
         <v>4</v>

--- a/ipl_stats_2026.xlsx
+++ b/ipl_stats_2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,16 +504,16 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F3" t="n">
-        <v>71.5</v>
+        <v>73.75</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -547,14 +547,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Anshul Kamboj</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>58</v>
@@ -563,7 +563,7 @@
         <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -572,23 +572,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Virat Kohli</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>542</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>54.2</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Virat Kohli</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -607,13 +607,13 @@
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="F7" t="n">
-        <v>50.45</v>
+        <v>54.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -622,23 +622,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Josh Inglis</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>194</v>
+        <v>555</v>
       </c>
       <c r="F8" t="n">
-        <v>48.5</v>
+        <v>50.45</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -647,23 +647,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sanju Samson</t>
+          <t>B Sai Sudharshan</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>477</v>
+        <v>638</v>
       </c>
       <c r="F9" t="n">
-        <v>47.7</v>
+        <v>49.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -672,23 +672,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Josh Inglis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F10" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cooper Connolly</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>473</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -722,23 +722,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B Sai Sudharshan</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>554</v>
+        <v>190</v>
       </c>
       <c r="F12" t="n">
-        <v>46.17</v>
+        <v>47.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>552</v>
+        <v>616</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>47.38</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -772,23 +772,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prashant Veer</t>
+          <t>Cooper Connolly</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>90</v>
+        <v>473</v>
       </c>
       <c r="F14" t="n">
-        <v>45</v>
+        <v>47.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -797,20 +797,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vaibhav Suryavanshi</t>
+          <t>Manish Pandey</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>579</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>44.54</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -822,23 +822,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lokesh Rahul</t>
+          <t>Prashant Veer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>533</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>44.42</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -847,23 +847,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shreyas Iyer</t>
+          <t>Vaibhav Suryavanshi</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>397</v>
+        <v>579</v>
       </c>
       <c r="F17" t="n">
-        <v>44.11</v>
+        <v>44.54</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -872,20 +872,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Lokesh Rahul</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E18" t="n">
-        <v>436</v>
+        <v>533</v>
       </c>
       <c r="F18" t="n">
-        <v>43.6</v>
+        <v>44.42</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -897,23 +897,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Shreyas Iyer</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>563</v>
+        <v>397</v>
       </c>
       <c r="F19" t="n">
-        <v>43.31</v>
+        <v>44.11</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -922,23 +922,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>296</v>
+        <v>436</v>
       </c>
       <c r="F20" t="n">
-        <v>42.29</v>
+        <v>43.6</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -947,23 +947,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abhishek Sharma</t>
+          <t>Sanju Samson</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="F21" t="n">
-        <v>42.25</v>
+        <v>43.36</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -972,23 +972,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Angkrish Raghuvanshi</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>13</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>422</v>
+        <v>563</v>
       </c>
       <c r="F22" t="n">
-        <v>42.2</v>
+        <v>43.31</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -997,20 +997,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Abhishek Sharma</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>507</v>
       </c>
       <c r="F23" t="n">
-        <v>40.43</v>
+        <v>42.25</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rovman Powell</t>
+          <t>Angkrish Raghuvanshi</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>121</v>
+        <v>422</v>
       </c>
       <c r="F24" t="n">
-        <v>40.33</v>
+        <v>42.2</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
@@ -1047,20 +1047,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Rohit Sharma</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>321</v>
+        <v>283</v>
       </c>
       <c r="F25" t="n">
-        <v>40.12</v>
+        <v>40.43</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Prabhsimran Singh</t>
+          <t>Rovman Powell</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>441</v>
+        <v>161</v>
       </c>
       <c r="F26" t="n">
-        <v>40.09</v>
+        <v>40.25</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Prabhsimran Singh</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1107,13 +1107,13 @@
         <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>316</v>
+        <v>441</v>
       </c>
       <c r="F27" t="n">
-        <v>39.5</v>
+        <v>40.09</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anshul Kamboj</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>469</v>
       </c>
       <c r="F28" t="n">
-        <v>39</v>
+        <v>39.08</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1147,23 +1147,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dhruv Chand Jurel</t>
+          <t>Shivam Dube</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>420</v>
+        <v>270</v>
       </c>
       <c r="F29" t="n">
-        <v>38.18</v>
+        <v>38.57</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Dhruv Chand Jurel</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1182,13 +1182,13 @@
         <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="F30" t="n">
-        <v>37.69</v>
+        <v>38.18</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1197,23 +1197,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Devdutt Padikkal</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" t="n">
-        <v>412</v>
+        <v>303</v>
       </c>
       <c r="F31" t="n">
-        <v>37.45</v>
+        <v>37.88</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1222,23 +1222,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>262</v>
+        <v>490</v>
       </c>
       <c r="F32" t="n">
-        <v>37.43</v>
+        <v>37.69</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1247,23 +1247,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Devdutt Padikkal</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>149</v>
+        <v>412</v>
       </c>
       <c r="F33" t="n">
-        <v>37.25</v>
+        <v>37.45</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="C34" t="n">
+        <v>13</v>
+      </c>
+      <c r="D34" t="n">
         <v>12</v>
       </c>
-      <c r="D34" t="n">
-        <v>11</v>
-      </c>
       <c r="E34" t="n">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="F34" t="n">
-        <v>37.17</v>
+        <v>37.43</v>
       </c>
       <c r="G34" t="n">
         <v>5</v>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="F35" t="n">
-        <v>36.6</v>
+        <v>37.25</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="F36" t="n">
-        <v>36</v>
+        <v>36.6</v>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1347,23 +1347,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>252</v>
+        <v>329</v>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>36.56</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1372,20 +1372,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Donavon Ferreira</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>12</v>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="F38" t="n">
-        <v>35.57</v>
+        <v>36</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -1397,20 +1397,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>141</v>
+        <v>252</v>
       </c>
       <c r="F39" t="n">
-        <v>35.25</v>
+        <v>36</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -1422,23 +1422,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kagiso Rabada</t>
+          <t>Donavon Ferreira</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="F40" t="n">
-        <v>35</v>
+        <v>35.57</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1447,23 +1447,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="F41" t="n">
-        <v>34.5</v>
+        <v>35.56</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>275</v>
+        <v>141</v>
       </c>
       <c r="F42" t="n">
-        <v>34.38</v>
+        <v>35.25</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Kagiso Rabada</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D43" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>412</v>
+        <v>35</v>
       </c>
       <c r="F43" t="n">
-        <v>34.33</v>
+        <v>35</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -1522,23 +1522,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>13</v>
       </c>
       <c r="D44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" t="n">
-        <v>343</v>
+        <v>275</v>
       </c>
       <c r="F44" t="n">
-        <v>34.3</v>
+        <v>34.38</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>92</v>
+        <v>295</v>
       </c>
       <c r="F51" t="n">
-        <v>30.67</v>
+        <v>32.78</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -1722,20 +1722,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E52" t="n">
-        <v>92</v>
+        <v>356</v>
       </c>
       <c r="F52" t="n">
-        <v>30.67</v>
+        <v>32.36</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -1747,20 +1747,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="F53" t="n">
-        <v>30.6</v>
+        <v>30.67</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>364</v>
+        <v>153</v>
       </c>
       <c r="F54" t="n">
-        <v>30.33</v>
+        <v>30.6</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -1797,23 +1797,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ruturaj Gaikwad</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="F55" t="n">
-        <v>29.18</v>
+        <v>30.33</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pathum Nissanka</t>
+          <t>Ruturaj Gaikwad</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E61" t="n">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="F61" t="n">
-        <v>27.8</v>
+        <v>28.08</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Pathum Nissanka</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>10</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="F62" t="n">
-        <v>27.2</v>
+        <v>27.8</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1997,23 +1997,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D63" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="F63" t="n">
-        <v>26.11</v>
+        <v>27.2</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2022,23 +2022,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Azmatullah</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="F64" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2047,20 +2047,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E65" t="n">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="F65" t="n">
-        <v>26</v>
+        <v>26.11</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
@@ -2072,23 +2072,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Riyan Parag</t>
+          <t>Azmatullah</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>258</v>
+        <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2097,20 +2097,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>231</v>
+        <v>26</v>
       </c>
       <c r="F67" t="n">
-        <v>25.67</v>
+        <v>26</v>
       </c>
       <c r="G67" t="n">
         <v>2</v>
@@ -2122,23 +2122,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shubham Badriprasad Dubey</t>
+          <t>Riyan Parag</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E68" t="n">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="F68" t="n">
-        <v>25.33</v>
+        <v>25.8</v>
       </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -2147,23 +2147,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nitish Rana</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>25.67</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -2172,20 +2172,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Shubham Badriprasad Dubey</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="F70" t="n">
-        <v>24.6</v>
+        <v>25.33</v>
       </c>
       <c r="G70" t="n">
         <v>2</v>
@@ -2197,23 +2197,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rahul Tewatia</t>
+          <t>Nitish Rana</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="F71" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="G71" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sarfaraz Khan</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2232,13 +2232,13 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="F72" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ajinkya Rahane</t>
+          <t>Sarfaraz Khan</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="F73" t="n">
-        <v>22.82</v>
+        <v>23</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2272,23 +2272,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Ajinkya Rahane</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D74" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>132</v>
+        <v>272</v>
       </c>
       <c r="F74" t="n">
-        <v>22</v>
+        <v>22.67</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
         <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="F75" t="n">
-        <v>21.86</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -2322,23 +2322,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="F76" t="n">
         <v>21.5</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2372,23 +2372,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Salil Arora</t>
         </is>
       </c>
       <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="n">
         <v>10</v>
       </c>
-      <c r="D78" t="n">
-        <v>7</v>
-      </c>
       <c r="E78" t="n">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="F78" t="n">
-        <v>20.43</v>
+        <v>20.17</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -2397,23 +2397,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Salil Arora</t>
+          <t>Matt Short</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="F79" t="n">
-        <v>20.17</v>
+        <v>20</v>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2422,23 +2422,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Rahul Tewatia</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>13</v>
+      </c>
+      <c r="D80" t="n">
+        <v>12</v>
+      </c>
+      <c r="E80" t="n">
+        <v>98</v>
+      </c>
+      <c r="F80" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G80" t="n">
         <v>7</v>
-      </c>
-      <c r="D80" t="n">
-        <v>5</v>
-      </c>
-      <c r="E80" t="n">
-        <v>58</v>
-      </c>
-      <c r="F80" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -2447,23 +2447,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E81" t="n">
-        <v>232</v>
+        <v>58</v>
       </c>
       <c r="F81" t="n">
         <v>19.33</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -2472,23 +2472,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ayush Badoni</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="F82" t="n">
-        <v>19.11</v>
+        <v>19.33</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -2497,20 +2497,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Ayush Badoni</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E83" t="n">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>19.11</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2522,23 +2522,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E84" t="n">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="F84" t="n">
-        <v>18</v>
+        <v>18.88</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2547,20 +2547,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Matt Short</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E85" t="n">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="F85" t="n">
-        <v>18</v>
+        <v>18.43</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2572,23 +2572,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F86" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2597,23 +2597,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Suryakumar Yadav</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>210</v>
+        <v>18</v>
       </c>
       <c r="F87" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2622,23 +2622,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Arshin Kulkarni</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F88" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -2647,23 +2647,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Suryakumar Yadav</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E89" t="n">
-        <v>134</v>
+        <v>210</v>
       </c>
       <c r="F89" t="n">
-        <v>16.75</v>
+        <v>17.5</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Glenn Phillips</t>
+          <t>Arshin Kulkarni</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F90" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="G90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2697,23 +2697,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="F91" t="n">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -2722,20 +2722,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E92" t="n">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="F92" t="n">
-        <v>16</v>
+        <v>16.75</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
@@ -2747,23 +2747,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Glenn Phillips</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="F93" t="n">
-        <v>16</v>
+        <v>16.75</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -2772,20 +2772,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="F94" t="n">
-        <v>15</v>
+        <v>16.4</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -2797,23 +2797,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vishnu Vinod</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2822,23 +2822,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Akshat Raghuwanshi</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -2847,23 +2847,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Vishnu Vinod</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -2872,23 +2872,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Akshat Raghuwanshi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2897,20 +2897,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Jacob Bethell</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="F99" t="n">
-        <v>13.71</v>
+        <v>14.5</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -2922,23 +2922,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E100" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F100" t="n">
-        <v>13.33</v>
+        <v>14.33</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -2947,20 +2947,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Abdul Samad</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="F101" t="n">
-        <v>13.17</v>
+        <v>14</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -2972,23 +2972,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Aniket Verma</t>
+          <t>Jacob Bethell</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D102" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E102" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F102" t="n">
-        <v>13.17</v>
+        <v>13.71</v>
       </c>
       <c r="G102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2997,23 +2997,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E103" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F103" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -3022,23 +3022,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dasun Shanaka</t>
+          <t>Abdul Samad</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="F104" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -3047,23 +3047,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shimron Hetmyer</t>
+          <t>Aniket Verma</t>
         </is>
       </c>
       <c r="C105" t="n">
+        <v>10</v>
+      </c>
+      <c r="D105" t="n">
         <v>8</v>
       </c>
-      <c r="D105" t="n">
-        <v>7</v>
-      </c>
       <c r="E105" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F105" t="n">
-        <v>13</v>
+        <v>13.17</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -3072,11 +3072,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Dasun Shanaka</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
         <v>2</v>
@@ -3097,20 +3097,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Shimron Hetmyer</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E107" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="F107" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -3122,20 +3122,20 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nishant Sindhu</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F108" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3147,23 +3147,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F109" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -3172,20 +3172,20 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nehal Wadhera</t>
+          <t>Nishant Sindhu</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="F110" t="n">
-        <v>10.83</v>
+        <v>12.67</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3197,23 +3197,23 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Shahrukh Khan</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F111" t="n">
-        <v>10.75</v>
+        <v>12</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3222,20 +3222,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Tejasvi Dahiya</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3247,23 +3247,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jitesh Sharma</t>
+          <t>Nehal Wadhera</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E113" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="F113" t="n">
-        <v>10</v>
+        <v>10.83</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3272,20 +3272,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Shahrukh Khan</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E114" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F114" t="n">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -3297,20 +3297,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Karun Nair</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E115" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F115" t="n">
-        <v>9</v>
+        <v>10.33</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3322,20 +3322,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ravichandran Smaran</t>
+          <t>Jitesh Sharma</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E116" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="F116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
@@ -3347,20 +3347,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -3372,23 +3372,23 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Karun Nair</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3397,23 +3397,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Ravichandran Smaran</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E119" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F119" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -3422,23 +3422,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sahil Parakh</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F120" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -3447,23 +3447,23 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F121" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -3472,23 +3472,23 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D122" t="n">
         <v>2</v>
       </c>
       <c r="E122" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F122" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3497,23 +3497,23 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Sahil Parakh</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E123" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F123" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="G123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3522,23 +3522,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D124" t="n">
         <v>2</v>
       </c>
       <c r="E124" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F124" t="n">
         <v>7</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -3547,23 +3547,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E125" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F125" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -3572,20 +3572,20 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F126" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E127" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F127" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128">
@@ -3622,23 +3622,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3647,23 +3647,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E129" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F129" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -3672,14 +3672,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Robin Minz</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E130" t="n">
         <v>6</v>
@@ -3688,7 +3688,7 @@
         <v>6</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -3697,23 +3697,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F131" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -3722,23 +3722,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Robin Minz</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F132" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -3747,23 +3747,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F133" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3772,23 +3772,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E134" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F134" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="G134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3797,14 +3797,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Mayank Yadav</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" t="n">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>5</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -3822,17 +3822,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F136" t="n">
         <v>5</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Mayank Yadav</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -3857,13 +3857,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ravi Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -3888,7 +3888,7 @@
         <v>4</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -3897,20 +3897,20 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Ravi Singh</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F139" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -3922,23 +3922,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D140" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E140" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F140" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -3947,20 +3947,20 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Harshal Patel</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D141" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F141" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -3972,23 +3972,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D142" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Harshal Patel</t>
         </is>
       </c>
       <c r="C143" t="n">
+        <v>4</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" t="n">
         <v>10</v>
       </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>3</v>
-      </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -4022,17 +4022,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F144" t="n">
         <v>3</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
         <v>3</v>
@@ -4063,7 +4063,7 @@
         <v>3</v>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -4072,20 +4072,20 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -4097,20 +4097,20 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D147" t="n">
         <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G147" t="n">
         <v>2</v>
@@ -4122,14 +4122,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4138,7 +4138,7 @@
         <v>2</v>
       </c>
       <c r="G148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -4147,11 +4147,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D149" t="n">
         <v>2</v>
@@ -4172,23 +4172,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F150" t="n">
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -4197,11 +4197,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D151" t="n">
         <v>2</v>
@@ -4222,20 +4222,20 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -4247,23 +4247,23 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -4272,23 +4272,23 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -4297,23 +4297,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Danish Malewar</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F155" t="n">
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
         <v>1</v>
@@ -4338,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157">
@@ -4347,14 +4347,14 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -4372,20 +4372,20 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Danish Malewar</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4397,23 +4397,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Abhinandan Singh</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -4422,23 +4422,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Akash Singh</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Anrich Nortje</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -4472,11 +4472,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Abhinandan Singh</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -4522,14 +4522,14 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>Anrich Nortje</t>
         </is>
       </c>
       <c r="C164" t="n">
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Dushmantha Chameera</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -4572,11 +4572,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4597,11 +4597,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4622,11 +4622,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Josh Hazlewood</t>
+          <t>Dushmantha Chameera</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
         <v>1</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -4647,11 +4647,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Khaleel Ahmed</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D169" t="n">
         <v>0</v>
@@ -4672,11 +4672,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D170" t="n">
         <v>0</v>
@@ -4697,14 +4697,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Josh Hazlewood</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -4722,11 +4722,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Manimaran Siddharth</t>
+          <t>Khaleel Ahmed</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4747,11 +4747,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Manish Pandey</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -4772,11 +4772,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Matheesha Pathirana</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D174" t="n">
         <v>0</v>
@@ -4797,11 +4797,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mayank Markande</t>
+          <t>Manimaran Siddharth</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D175" t="n">
         <v>0</v>
@@ -4822,14 +4822,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>Matheesha Pathirana</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -4847,14 +4847,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Mayank Markande</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -4872,11 +4872,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D178" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -4897,11 +4897,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D179" t="n">
         <v>2</v>
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -4922,14 +4922,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -4947,14 +4947,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -4972,11 +4972,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -4997,11 +4997,11 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D183" t="n">
         <v>0</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -5072,11 +5072,11 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Rahul Chahar</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D186" t="n">
         <v>0</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>Rahul Chahar</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -5122,14 +5122,14 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -5147,14 +5147,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ravisrinivasan Sai Kishore</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
@@ -5172,11 +5172,11 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Ravisrinivasan Sai Kishore</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -5197,11 +5197,11 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D191" t="n">
         <v>0</v>
@@ -5222,11 +5222,11 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -5247,11 +5247,11 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D193" t="n">
         <v>0</v>
@@ -5272,14 +5272,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Sushant Mishra</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Sushant Mishra</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -5322,11 +5322,11 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tripurana Vijay</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -5347,14 +5347,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Tripurana Vijay</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -5372,14 +5372,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
@@ -5397,11 +5397,11 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Yash Raj Punja</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D199" t="n">
         <v>0</v>
@@ -5422,22 +5422,47 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
+          <t>Yash Thakur</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
           <t>Yuzvendra Chahal</t>
         </is>
       </c>
-      <c r="C200" t="n">
-        <v>13</v>
-      </c>
-      <c r="D200" t="n">
-        <v>0</v>
-      </c>
-      <c r="E200" t="n">
-        <v>0</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
+      <c r="C201" t="n">
+        <v>13</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5527,16 +5552,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -5552,16 +5577,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -5573,20 +5598,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -5598,7 +5623,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Eshan Malinga</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5608,10 +5633,10 @@
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -5623,20 +5648,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -5648,20 +5673,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -5673,20 +5698,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>Eshan Malinga</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5698,7 +5723,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5708,10 +5733,10 @@
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5723,17 +5748,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Sunil Narine</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>282</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
@@ -5748,17 +5773,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
@@ -5773,17 +5798,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>300</v>
+        <v>204</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
@@ -5798,17 +5823,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prasidh Krishna</t>
+          <t>AM Ghazanfar</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="F14" t="n">
         <v>14</v>
@@ -5823,20 +5848,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sunil Narine</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5848,20 +5873,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jason Holder</t>
+          <t>Prasidh Krishna</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="F16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5873,17 +5898,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jason Holder</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>288</v>
+        <v>170</v>
       </c>
       <c r="F17" t="n">
         <v>13</v>
@@ -5898,17 +5923,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AM Ghazanfar</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>191</v>
+        <v>306</v>
       </c>
       <c r="F18" t="n">
         <v>13</v>
@@ -5998,17 +6023,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Corbin Bosch</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
@@ -6023,17 +6048,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -6048,17 +6073,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vaibhav Arora</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
         <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="F24" t="n">
         <v>11</v>
@@ -6073,17 +6098,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Praful Hinge</t>
+          <t>Vaibhav Arora</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
@@ -6098,20 +6123,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Axar Patel</t>
+          <t>Praful Hinge</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -6123,17 +6148,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lungi Ngidi</t>
+          <t>Axar Patel</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F27" t="n">
         <v>10</v>
@@ -6148,17 +6173,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>Lungi Ngidi</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="F28" t="n">
         <v>10</v>
@@ -6173,17 +6198,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Krunal Pandya</t>
+          <t>Varun Chakravarthy</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="F29" t="n">
         <v>10</v>
@@ -6198,17 +6223,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Varun Chakravarthy</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="F30" t="n">
         <v>10</v>
@@ -6223,17 +6248,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yuzvendra Chahal</t>
+          <t>Krunal Pandya</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="F31" t="n">
         <v>10</v>
@@ -6248,17 +6273,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shardul Thakur</t>
+          <t>Yuzvendra Chahal</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="F32" t="n">
         <v>10</v>
@@ -6273,20 +6298,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nandre Burger</t>
+          <t>Shardul Thakur</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>108</v>
+      </c>
+      <c r="F33" t="n">
         <v>10</v>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="n">
-        <v>195</v>
-      </c>
-      <c r="F33" t="n">
-        <v>9</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6298,17 +6323,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mitchell Starc</t>
+          <t>Nandre Burger</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="F34" t="n">
         <v>9</v>
@@ -6323,17 +6348,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>Mitchell Starc</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="F35" t="n">
         <v>9</v>
@@ -6348,20 +6373,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ravindra Jadeja</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>168</v>
+      </c>
+      <c r="F36" t="n">
         <v>9</v>
-      </c>
-      <c r="E36" t="n">
-        <v>156</v>
-      </c>
-      <c r="F36" t="n">
-        <v>8</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -6373,17 +6398,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Akeal Hosein</t>
+          <t>Ravindra Jadeja</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
@@ -6398,17 +6423,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pat Cummins</t>
+          <t>Akeal Hosein</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
@@ -6423,17 +6448,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Pat Cummins</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="F39" t="n">
         <v>8</v>
@@ -6448,17 +6473,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="F40" t="n">
         <v>8</v>
@@ -6473,17 +6498,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Anukul Roy</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
         <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>151</v>
+        <v>227</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
@@ -6498,17 +6523,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Corbin Bosch</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="F42" t="n">
         <v>8</v>
@@ -6523,17 +6548,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Anukul Roy</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
@@ -6548,20 +6573,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -6598,17 +6623,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Cameron Green</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="F46" t="n">
         <v>7</v>
@@ -6623,17 +6648,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nitish Kumar Reddy</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="F47" t="n">
         <v>7</v>
@@ -6648,17 +6673,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cameron Green</t>
+          <t>Nitish Kumar Reddy</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E48" t="n">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="F48" t="n">
         <v>7</v>
@@ -6773,17 +6798,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Deepak Chahar</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E53" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F53" t="n">
         <v>6</v>
@@ -6798,17 +6823,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" t="n">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="F54" t="n">
         <v>6</v>
@@ -6823,17 +6848,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="F55" t="n">
         <v>6</v>
@@ -6848,17 +6873,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jacob Duffy</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="F56" t="n">
         <v>6</v>
@@ -6873,7 +6898,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jacob Duffy</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -6883,10 +6908,10 @@
         <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -6898,17 +6923,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Digvesh Rathi</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -6923,17 +6948,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Digvesh Rathi</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
@@ -6948,17 +6973,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deepak Chahar</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
@@ -7073,17 +7098,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Madhav Tiwari</t>
+          <t>Jasprit Bumrah</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E65" t="n">
-        <v>48</v>
+        <v>294</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
@@ -7098,17 +7123,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>Madhav Tiwari</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="F66" t="n">
         <v>4</v>
@@ -7123,17 +7148,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blessing Muzarabani</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="F67" t="n">
         <v>4</v>
@@ -7148,17 +7173,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jaydev Unadkat</t>
+          <t>Blessing Muzarabani</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F68" t="n">
         <v>4</v>
@@ -7173,17 +7198,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Akash Singh</t>
+          <t>Jaydev Unadkat</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="F69" t="n">
         <v>4</v>
@@ -7198,17 +7223,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hardik Pandya</t>
+          <t>Akash Singh</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F70" t="n">
         <v>4</v>
@@ -7223,17 +7248,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tushar Deshpande</t>
+          <t>Hardik Pandya</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F71" t="n">
         <v>4</v>
@@ -7248,20 +7273,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Saurabh Dubey</t>
+          <t>Tushar Deshpande</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -7298,17 +7323,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jasprit Bumrah</t>
+          <t>Saurabh Dubey</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>270</v>
+        <v>53</v>
       </c>
       <c r="F74" t="n">
         <v>3</v>
@@ -7448,17 +7473,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Manav Suthar</t>
+          <t>Spencer Johnson</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
         <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="F80" t="n">
         <v>2</v>
@@ -7473,17 +7498,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Manav Suthar</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F81" t="n">
         <v>2</v>
@@ -7498,17 +7523,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Raj Angad Bawa</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E82" t="n">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="F82" t="n">
         <v>2</v>
@@ -7523,17 +7548,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Raj Angad Bawa</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="F83" t="n">
         <v>2</v>
@@ -7548,17 +7573,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vipraj Nigam</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -7573,17 +7598,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kyle Jamieson</t>
+          <t>Vipraj Nigam</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F85" t="n">
         <v>2</v>
@@ -7598,17 +7623,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Kyle Jamieson</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
@@ -7623,17 +7648,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Yash Thakur</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
@@ -7648,17 +7673,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>David Payne</t>
+          <t>Yash Thakur</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
@@ -7673,20 +7698,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ramakrishna Ghosh</t>
+          <t>David Payne</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7698,17 +7723,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>Ramakrishna Ghosh</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="F90" t="n">
         <v>1</v>
@@ -7727,7 +7752,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D91" t="n">
         <v>4</v>
@@ -7748,17 +7773,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>George Linde</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -7773,17 +7798,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dilshan Madushanka</t>
+          <t>George Linde</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F93" t="n">
         <v>1</v>
@@ -7798,17 +7823,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Spencer Johnson</t>
+          <t>Dilshan Madushanka</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F94" t="n">
         <v>1</v>
@@ -7898,17 +7923,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Shivam Dube</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v